--- a/research/traditional_assets/database/data/gibraltar/gibraltar_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/gibraltar/gibraltar_hotel_gaming.xlsx
@@ -644,10 +644,10 @@
         <v>-1.152838427947598</v>
       </c>
       <c r="X2">
-        <v>0.2864795193987015</v>
+        <v>0.2863803774743061</v>
       </c>
       <c r="Y2">
-        <v>-1.4393179473463</v>
+        <v>-1.439218805421904</v>
       </c>
       <c r="Z2">
         <v>1.072292178798977</v>
@@ -656,10 +656,10 @@
         <v>0.02448201474941053</v>
       </c>
       <c r="AB2">
-        <v>0.1021846912721664</v>
+        <v>0.1021715106868582</v>
       </c>
       <c r="AC2">
-        <v>-0.07770267652275589</v>
+        <v>-0.07768949593744764</v>
       </c>
       <c r="AD2">
         <v>2242.2</v>
@@ -775,10 +775,10 @@
         <v>-1.152838427947598</v>
       </c>
       <c r="X3">
-        <v>0.2864795193987015</v>
+        <v>0.2863803774743061</v>
       </c>
       <c r="Y3">
-        <v>-1.4393179473463</v>
+        <v>-1.439218805421904</v>
       </c>
       <c r="Z3">
         <v>1.072292178798977</v>
@@ -787,10 +787,10 @@
         <v>0.02448201474941053</v>
       </c>
       <c r="AB3">
-        <v>0.1021846912721664</v>
+        <v>0.1021715106868582</v>
       </c>
       <c r="AC3">
-        <v>-0.07770267652275589</v>
+        <v>-0.07768949593744764</v>
       </c>
       <c r="AD3">
         <v>2242.2</v>
@@ -1127,49 +1127,49 @@
         <v>0.206517139229793</v>
       </c>
       <c r="F2">
-        <v>4.5768891186134</v>
+        <v>4.61519364576658</v>
       </c>
       <c r="G2">
         <v>11.5577319587629</v>
       </c>
       <c r="H2">
-        <v>4.13226804123711</v>
+        <v>4.26556701030928</v>
       </c>
       <c r="I2">
         <v>0.867053364269141</v>
       </c>
       <c r="J2">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="K2">
         <v>343.8</v>
       </c>
       <c r="L2">
-        <v>2812.09497119071</v>
+        <v>2846.31763161852</v>
       </c>
       <c r="M2">
         <v>2278.1</v>
       </c>
       <c r="N2">
-        <v>3305.85497119071</v>
+        <v>3365.93763161852</v>
       </c>
       <c r="O2">
         <v>2242.2</v>
       </c>
       <c r="P2">
-        <v>801.66</v>
+        <v>827.52</v>
       </c>
       <c r="Q2">
-        <v>0.102184691272166</v>
+        <v>0.102171510686858</v>
       </c>
       <c r="R2">
-        <v>0.0846552935039545</v>
+        <v>0.0839527979869254</v>
       </c>
       <c r="S2">
         <v>0.07392647973443441</v>
       </c>
       <c r="T2">
-        <v>0.0497793252308225</v>
+        <v>0.0478234809408103</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.286479519398701</v>
+        <v>0.286380377474306</v>
       </c>
       <c r="X2">
-        <v>0.100324206786086</v>
+        <v>0.100954829538038</v>
       </c>
       <c r="Y2">
         <v>4.41798664709768</v>
       </c>
       <c r="Z2">
-        <v>1.00086296551671</v>
+        <v>1.01285608984476</v>
       </c>
       <c r="AA2">
         <v>2242.2</v>
@@ -1224,7 +1224,7 @@
         <v>343.8</v>
       </c>
       <c r="AK2">
-        <v>0.05447719484548731</v>
+        <v>0.05445475432397499</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08655155145709351</v>
+        <v>0.08653476487199627</v>
       </c>
       <c r="C2">
-        <v>3459.926379225456</v>
+        <v>3460.488186019354</v>
       </c>
       <c r="D2">
-        <v>3152.026379225456</v>
+        <v>3152.588186019354</v>
       </c>
       <c r="E2">
         <v>-2242.2</v>
@@ -1460,19 +1460,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08655155145709351</v>
+        <v>0.08653476487199627</v>
       </c>
       <c r="T2">
         <v>0.7480479046815168</v>
       </c>
       <c r="U2">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V2">
         <v>0.2477521961491617</v>
       </c>
       <c r="W2">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08644374248186318</v>
+        <v>0.08641646601664527</v>
       </c>
       <c r="C3">
-        <v>3442.42724151551</v>
+        <v>3443.810362864733</v>
       </c>
       <c r="D3">
-        <v>3160.38724151551</v>
+        <v>3161.770362864733</v>
       </c>
       <c r="E3">
         <v>-2216.34</v>
@@ -1524,37 +1524,37 @@
         <v>242.8</v>
       </c>
       <c r="M3">
-        <v>1.550930357801877</v>
+        <v>1.514726357801877</v>
       </c>
       <c r="N3">
-        <v>241.2490696421981</v>
+        <v>241.2852736421981</v>
       </c>
       <c r="O3">
-        <v>59.76998682279665</v>
+        <v>59.77895644330603</v>
       </c>
       <c r="P3">
-        <v>181.4790828194015</v>
+        <v>181.5063171988921</v>
       </c>
       <c r="Q3">
-        <v>326.6790828194015</v>
+        <v>326.7063171988921</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08686120059938758</v>
+        <v>0.0868442864620502</v>
       </c>
       <c r="T3">
         <v>0.7537319187569904</v>
       </c>
       <c r="U3">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V3">
         <v>0.2477521961491617</v>
       </c>
       <c r="W3">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>156.551194435396</v>
+        <v>160.2929788271088</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,13 +1573,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08633593350663285</v>
+        <v>0.08629816716129425</v>
       </c>
       <c r="C4">
-        <v>3424.972576741922</v>
+        <v>3427.186183669166</v>
       </c>
       <c r="D4">
-        <v>3168.792576741922</v>
+        <v>3171.006183669165</v>
       </c>
       <c r="E4">
         <v>-2190.48</v>
@@ -1606,37 +1606,37 @@
         <v>242.8</v>
       </c>
       <c r="M4">
-        <v>3.101860715603755</v>
+        <v>3.029452715603755</v>
       </c>
       <c r="N4">
-        <v>239.6981392843963</v>
+        <v>239.7705472843963</v>
       </c>
       <c r="O4">
-        <v>59.38574042057683</v>
+        <v>59.4036796615956</v>
       </c>
       <c r="P4">
-        <v>180.3123988638194</v>
+        <v>180.3668676228007</v>
       </c>
       <c r="Q4">
-        <v>325.5123988638194</v>
+        <v>325.5668676228007</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08717716911193256</v>
+        <v>0.08716012481924809</v>
       </c>
       <c r="T4">
         <v>0.7595319331197188</v>
       </c>
       <c r="U4">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V4">
         <v>0.2477521961491617</v>
       </c>
       <c r="W4">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>78.27559721769801</v>
+        <v>80.14648941355441</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08622812453140254</v>
+        <v>0.08617986830594325</v>
       </c>
       <c r="C5">
-        <v>3407.562740690305</v>
+        <v>3410.61611990662</v>
       </c>
       <c r="D5">
-        <v>3177.242740690304</v>
+        <v>3180.29611990662</v>
       </c>
       <c r="E5">
         <v>-2164.62</v>
@@ -1688,37 +1688,37 @@
         <v>242.8</v>
       </c>
       <c r="M5">
-        <v>4.652791073405632</v>
+        <v>4.544179073405632</v>
       </c>
       <c r="N5">
-        <v>238.1472089265944</v>
+        <v>238.2558209265944</v>
       </c>
       <c r="O5">
-        <v>59.00149401835701</v>
+        <v>59.02840287988516</v>
       </c>
       <c r="P5">
-        <v>179.1457149082374</v>
+        <v>179.2274180467092</v>
       </c>
       <c r="Q5">
-        <v>324.3457149082374</v>
+        <v>324.4274180467092</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08749965243916918</v>
+        <v>0.08748247530752223</v>
       </c>
       <c r="T5">
         <v>0.7654515354074517</v>
       </c>
       <c r="U5">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V5">
         <v>0.2477521961491617</v>
       </c>
       <c r="W5">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.18373147846533</v>
+        <v>53.43099294236961</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,13 +1737,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08612031555617219</v>
+        <v>0.08606156945059222</v>
       </c>
       <c r="C6">
-        <v>3390.198092951491</v>
+        <v>3394.100648592317</v>
       </c>
       <c r="D6">
-        <v>3185.738092951491</v>
+        <v>3189.640648592317</v>
       </c>
       <c r="E6">
         <v>-2138.76</v>
@@ -1770,37 +1770,37 @@
         <v>242.8</v>
       </c>
       <c r="M6">
-        <v>6.20372143120751</v>
+        <v>6.05890543120751</v>
       </c>
       <c r="N6">
-        <v>236.5962785687925</v>
+        <v>236.7410945687925</v>
       </c>
       <c r="O6">
-        <v>58.61724761613719</v>
+        <v>58.65312609817472</v>
       </c>
       <c r="P6">
-        <v>177.9790309526553</v>
+        <v>178.0879684706178</v>
       </c>
       <c r="Q6">
-        <v>323.1790309526553</v>
+        <v>323.2879684706178</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08782885416905656</v>
+        <v>0.08781154143096874</v>
       </c>
       <c r="T6">
         <v>0.7714944627428457</v>
       </c>
       <c r="U6">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V6">
         <v>0.2477521961491617</v>
       </c>
       <c r="W6">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.137798608849</v>
+        <v>40.07324470677721</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,13 +1819,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08601250658094184</v>
+        <v>0.08594327059524122</v>
       </c>
       <c r="C7">
-        <v>3372.878996972534</v>
+        <v>3377.640252364368</v>
       </c>
       <c r="D7">
-        <v>3194.278996972534</v>
+        <v>3199.040252364368</v>
       </c>
       <c r="E7">
         <v>-2112.9</v>
@@ -1852,37 +1852,37 @@
         <v>242.8</v>
       </c>
       <c r="M7">
-        <v>7.754651789009388</v>
+        <v>7.573631789009388</v>
       </c>
       <c r="N7">
-        <v>235.0453482109906</v>
+        <v>235.2263682109906</v>
       </c>
       <c r="O7">
-        <v>58.23300121391737</v>
+        <v>58.27784931646428</v>
       </c>
       <c r="P7">
-        <v>176.8123469970733</v>
+        <v>176.9485188945263</v>
       </c>
       <c r="Q7">
-        <v>322.0123469970732</v>
+        <v>322.1485188945263</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0881649864616784</v>
+        <v>0.08814753526227728</v>
       </c>
       <c r="T7">
         <v>0.7776646096010901</v>
       </c>
       <c r="U7">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V7">
         <v>0.2477521961491617</v>
       </c>
       <c r="W7">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.3102388870792</v>
+        <v>32.05859576542176</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,13 +1901,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08590469760571151</v>
+        <v>0.08582497173989022</v>
       </c>
       <c r="C8">
-        <v>3355.605820108543</v>
+        <v>3361.23541956688</v>
       </c>
       <c r="D8">
-        <v>3202.865820108543</v>
+        <v>3208.49541956688</v>
       </c>
       <c r="E8">
         <v>-2087.04</v>
@@ -1934,37 +1934,37 @@
         <v>242.8</v>
       </c>
       <c r="M8">
-        <v>9.305582146811265</v>
+        <v>9.088358146811265</v>
       </c>
       <c r="N8">
-        <v>233.4944178531887</v>
+        <v>233.7116418531888</v>
       </c>
       <c r="O8">
-        <v>57.84875481169755</v>
+        <v>57.90257253475385</v>
       </c>
       <c r="P8">
-        <v>175.6456630414912</v>
+        <v>175.8090693184349</v>
       </c>
       <c r="Q8">
-        <v>320.8456630414912</v>
+        <v>321.0090693184349</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08850827050520711</v>
+        <v>0.08849067789850729</v>
       </c>
       <c r="T8">
         <v>0.7839660361797227</v>
       </c>
       <c r="U8">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V8">
         <v>0.2477521961491617</v>
       </c>
       <c r="W8">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.09186573923267</v>
+        <v>26.7154964711848</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08579688863048117</v>
+        <v>0.08570667288453919</v>
       </c>
       <c r="C9">
-        <v>3338.378933675358</v>
+        <v>3344.886644334526</v>
       </c>
       <c r="D9">
-        <v>3211.498933675358</v>
+        <v>3218.006644334526</v>
       </c>
       <c r="E9">
         <v>-2061.18</v>
@@ -2016,37 +2016,37 @@
         <v>242.8</v>
       </c>
       <c r="M9">
-        <v>10.85651250461314</v>
+        <v>10.60308450461314</v>
       </c>
       <c r="N9">
-        <v>231.9434874953869</v>
+        <v>232.1969154953869</v>
       </c>
       <c r="O9">
-        <v>57.46450840947773</v>
+        <v>57.52729575304341</v>
       </c>
       <c r="P9">
-        <v>174.4789790859091</v>
+        <v>174.6696197423435</v>
       </c>
       <c r="Q9">
-        <v>319.6789790859091</v>
+        <v>319.8696197423434</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0888589370012848</v>
+        <v>0.08884119994626911</v>
       </c>
       <c r="T9">
         <v>0.7904029773084333</v>
       </c>
       <c r="U9">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V9">
         <v>0.2477521961491617</v>
       </c>
       <c r="W9">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.36445634791371</v>
+        <v>22.89899697530126</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08568907965525085</v>
+        <v>0.0855883740291882</v>
       </c>
       <c r="C10">
-        <v>3321.198713003062</v>
+        <v>3328.59442667862</v>
       </c>
       <c r="D10">
-        <v>3220.178713003062</v>
+        <v>3227.57442667862</v>
       </c>
       <c r="E10">
         <v>-2035.32</v>
@@ -2098,37 +2098,37 @@
         <v>242.8</v>
       </c>
       <c r="M10">
-        <v>12.40744286241502</v>
+        <v>12.11781086241502</v>
       </c>
       <c r="N10">
-        <v>230.392557137585</v>
+        <v>230.682189137585</v>
       </c>
       <c r="O10">
-        <v>57.08026200725791</v>
+        <v>57.15201897133298</v>
       </c>
       <c r="P10">
-        <v>173.3122951303271</v>
+        <v>173.530170166252</v>
       </c>
       <c r="Q10">
-        <v>318.5122951303271</v>
+        <v>318.730170166252</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08921722668205986</v>
+        <v>0.08919934203854751</v>
       </c>
       <c r="T10">
         <v>0.7969798519399423</v>
       </c>
       <c r="U10">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V10">
         <v>0.2477521961491617</v>
       </c>
       <c r="W10">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.5688993044245</v>
+        <v>20.0366223533886</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,13 +2147,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08558127068002053</v>
+        <v>0.08547007517383719</v>
       </c>
       <c r="C11">
-        <v>3304.065537490389</v>
+        <v>3312.359272574756</v>
       </c>
       <c r="D11">
-        <v>3228.905537490388</v>
+        <v>3237.199272574755</v>
       </c>
       <c r="E11">
         <v>-2009.46</v>
@@ -2180,37 +2180,37 @@
         <v>242.8</v>
       </c>
       <c r="M11">
-        <v>13.9583732202169</v>
+        <v>13.6325372202169</v>
       </c>
       <c r="N11">
-        <v>228.8416267797831</v>
+        <v>229.1674627797831</v>
       </c>
       <c r="O11">
-        <v>56.69601560503809</v>
+        <v>56.77674218962254</v>
       </c>
       <c r="P11">
-        <v>172.145611174745</v>
+        <v>172.3907205901606</v>
       </c>
       <c r="Q11">
-        <v>317.345611174745</v>
+        <v>317.5907205901606</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08958339086131348</v>
+        <v>0.08956535538560126</v>
       </c>
       <c r="T11">
         <v>0.803701273266649</v>
       </c>
       <c r="U11">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V11">
         <v>0.2477521961491617</v>
       </c>
       <c r="W11">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.39457715948845</v>
+        <v>17.81033098078987</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,13 +2229,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08547346170479019</v>
+        <v>0.08535177631848619</v>
       </c>
       <c r="C12">
-        <v>3286.979790659992</v>
+        <v>3296.181694051985</v>
       </c>
       <c r="D12">
-        <v>3237.679790659992</v>
+        <v>3246.881694051985</v>
       </c>
       <c r="E12">
         <v>-1983.6</v>
@@ -2262,37 +2262,37 @@
         <v>242.8</v>
       </c>
       <c r="M12">
-        <v>15.50930357801878</v>
+        <v>15.14726357801878</v>
       </c>
       <c r="N12">
-        <v>227.2906964219812</v>
+        <v>227.6527364219812</v>
       </c>
       <c r="O12">
-        <v>56.31176920281827</v>
+        <v>56.40146540791211</v>
       </c>
       <c r="P12">
-        <v>170.978927219163</v>
+        <v>171.2512710140691</v>
       </c>
       <c r="Q12">
-        <v>316.178927219163</v>
+        <v>316.4512710140691</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08995769202232828</v>
+        <v>0.08993950236258953</v>
       </c>
       <c r="T12">
         <v>0.8105720595117271</v>
       </c>
       <c r="U12">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V12">
         <v>0.2477521961491617</v>
       </c>
       <c r="W12">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.6551194435396</v>
+        <v>16.02929788271088</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08536565272955986</v>
+        <v>0.0852334774631352</v>
       </c>
       <c r="C13">
-        <v>3269.941860214635</v>
+        <v>3280.06220928363</v>
       </c>
       <c r="D13">
-        <v>3246.501860214635</v>
+        <v>3256.62220928363</v>
       </c>
       <c r="E13">
         <v>-1957.74</v>
@@ -2344,37 +2344,37 @@
         <v>242.8</v>
       </c>
       <c r="M13">
-        <v>17.06023393582065</v>
+        <v>16.66198993582065</v>
       </c>
       <c r="N13">
-        <v>225.7397660641793</v>
+        <v>226.1380100641794</v>
       </c>
       <c r="O13">
-        <v>55.92752280059844</v>
+        <v>56.02618862620167</v>
       </c>
       <c r="P13">
-        <v>169.8122432635809</v>
+        <v>170.1118214379777</v>
       </c>
       <c r="Q13">
-        <v>315.0122432635809</v>
+        <v>315.3118214379776</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09034040444538838</v>
+        <v>0.0903220571368135</v>
       </c>
       <c r="T13">
         <v>0.8175972454477058</v>
       </c>
       <c r="U13">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V13">
         <v>0.2477521961491617</v>
       </c>
       <c r="W13">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.23192676685418</v>
+        <v>14.57208898428262</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,13 +2393,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08525784375432954</v>
+        <v>0.08511517860778417</v>
       </c>
       <c r="C14">
-        <v>3252.952138094293</v>
+        <v>3264.001342679726</v>
       </c>
       <c r="D14">
-        <v>3255.372138094293</v>
+        <v>3266.421342679726</v>
       </c>
       <c r="E14">
         <v>-1931.88</v>
@@ -2426,37 +2426,37 @@
         <v>242.8</v>
       </c>
       <c r="M14">
-        <v>18.61116429362253</v>
+        <v>18.17671629362253</v>
       </c>
       <c r="N14">
-        <v>224.1888357063775</v>
+        <v>224.6232837063775</v>
       </c>
       <c r="O14">
-        <v>55.54327639837862</v>
+        <v>55.65091184449124</v>
       </c>
       <c r="P14">
-        <v>168.6455593079989</v>
+        <v>168.9723718618862</v>
       </c>
       <c r="Q14">
-        <v>313.8455593079989</v>
+        <v>314.1723718618862</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09073181487806348</v>
+        <v>0.09071330633772437</v>
       </c>
       <c r="T14">
         <v>0.8247820947004112</v>
       </c>
       <c r="U14">
-        <v>0.059974105096747</v>
+        <v>0.058574105096747</v>
       </c>
       <c r="V14">
         <v>0.2477521961491617</v>
       </c>
       <c r="W14">
-        <v>0.0451153888469473</v>
+        <v>0.04406224192155612</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.04593286961633</v>
+        <v>13.3577482355924</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08525760621504987</v>
+        <v>0.08514356807418408</v>
       </c>
       <c r="C15">
-        <v>3227.111735805025</v>
+        <v>3235.78436380122</v>
       </c>
       <c r="D15">
-        <v>3255.391735805025</v>
+        <v>3264.064363801219</v>
       </c>
       <c r="E15">
         <v>-1906.02</v>
@@ -2508,37 +2508,37 @@
         <v>242.8</v>
       </c>
       <c r="M15">
-        <v>20.53189265142441</v>
+        <v>20.1957126514244</v>
       </c>
       <c r="N15">
-        <v>222.2681073485756</v>
+        <v>222.6042873485756</v>
       </c>
       <c r="O15">
-        <v>55.06741172952724</v>
+        <v>55.15070106282867</v>
       </c>
       <c r="P15">
-        <v>167.2006956190484</v>
+        <v>167.453586285747</v>
       </c>
       <c r="Q15">
-        <v>312.4006956190483</v>
+        <v>312.6535862857469</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.0911322232517196</v>
+        <v>0.09111354977313893</v>
       </c>
       <c r="T15">
         <v>0.8321321129014547</v>
       </c>
       <c r="U15">
-        <v>0.061074105096747</v>
+        <v>0.060074105096747</v>
       </c>
       <c r="V15">
         <v>0.2477521961491617</v>
       </c>
       <c r="W15">
-        <v>0.04594286143118322</v>
+        <v>0.04519061362733237</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.82550503853115</v>
+        <v>12.02235366439893</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,13 +2557,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0851580719656619</v>
+        <v>0.08503655293589084</v>
       </c>
       <c r="C16">
-        <v>3209.484430058184</v>
+        <v>3218.826886402044</v>
       </c>
       <c r="D16">
-        <v>3263.624430058184</v>
+        <v>3272.966886402044</v>
       </c>
       <c r="E16">
         <v>-1880.16</v>
@@ -2590,37 +2590,37 @@
         <v>242.8</v>
       </c>
       <c r="M16">
-        <v>22.11126900922628</v>
+        <v>21.74922900922628</v>
       </c>
       <c r="N16">
-        <v>220.6887309907737</v>
+        <v>221.0507709907737</v>
       </c>
       <c r="O16">
-        <v>54.67611776833576</v>
+        <v>54.7658139734296</v>
       </c>
       <c r="P16">
-        <v>166.012613222438</v>
+        <v>166.2849570173441</v>
       </c>
       <c r="Q16">
-        <v>311.212613222438</v>
+        <v>311.4849570173441</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09154194344801889</v>
+        <v>0.09152310119542362</v>
       </c>
       <c r="T16">
         <v>0.8396530617583365</v>
       </c>
       <c r="U16">
-        <v>0.061074105096747</v>
+        <v>0.060074105096747</v>
       </c>
       <c r="V16">
         <v>0.2477521961491617</v>
       </c>
       <c r="W16">
-        <v>0.04594286143118322</v>
+        <v>0.04519061362733237</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.9808261072075</v>
+        <v>11.16361411694186</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,13 +2639,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08505853771627392</v>
+        <v>0.0849295377975976</v>
       </c>
       <c r="C17">
-        <v>3191.898869882658</v>
+        <v>3201.918103914227</v>
       </c>
       <c r="D17">
-        <v>3271.898869882658</v>
+        <v>3281.918103914227</v>
       </c>
       <c r="E17">
         <v>-1854.3</v>
@@ -2672,37 +2672,37 @@
         <v>242.8</v>
       </c>
       <c r="M17">
-        <v>23.69064536702816</v>
+        <v>23.30274536702816</v>
       </c>
       <c r="N17">
-        <v>219.1093546329718</v>
+        <v>219.4972546329718</v>
       </c>
       <c r="O17">
-        <v>54.28482380714428</v>
+        <v>54.38092688403054</v>
       </c>
       <c r="P17">
-        <v>164.8245308258276</v>
+        <v>165.1163277489413</v>
       </c>
       <c r="Q17">
-        <v>310.0245308258276</v>
+        <v>310.3163277489413</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09196130411952522</v>
+        <v>0.09194228912176204</v>
       </c>
       <c r="T17">
         <v>0.8473509741177331</v>
       </c>
       <c r="U17">
-        <v>0.061074105096747</v>
+        <v>0.060074105096747</v>
       </c>
       <c r="V17">
         <v>0.2477521961491617</v>
       </c>
       <c r="W17">
-        <v>0.04594286143118322</v>
+        <v>0.04519061362733237</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.24877103339366</v>
+        <v>10.4193731758124</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08522379469384143</v>
+        <v>0.08502713406195178</v>
       </c>
       <c r="C18">
-        <v>3152.32369805959</v>
+        <v>3167.892762384241</v>
       </c>
       <c r="D18">
-        <v>3258.18369805959</v>
+        <v>3273.752762384241</v>
       </c>
       <c r="E18">
         <v>-1828.44</v>
@@ -2754,37 +2754,37 @@
         <v>242.8</v>
       </c>
       <c r="M18">
-        <v>26.18029372483004</v>
+        <v>25.55965372483004</v>
       </c>
       <c r="N18">
-        <v>216.61970627517</v>
+        <v>217.24034627517</v>
       </c>
       <c r="O18">
-        <v>53.6680079588597</v>
+        <v>53.82177288187772</v>
       </c>
       <c r="P18">
-        <v>162.9516983163103</v>
+        <v>163.4185733932923</v>
       </c>
       <c r="Q18">
-        <v>308.1516983163102</v>
+        <v>308.6185733932923</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09239064956892457</v>
+        <v>0.09237145771301331</v>
       </c>
       <c r="T18">
         <v>0.8552321701047344</v>
       </c>
       <c r="U18">
-        <v>0.063274105096747</v>
+        <v>0.061774105096747</v>
       </c>
       <c r="V18">
         <v>0.2477521961491617</v>
       </c>
       <c r="W18">
-        <v>0.04759780659965506</v>
+        <v>0.0464694348938788</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.274151105864885</v>
+        <v>9.499346220177111</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,13 +2803,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0851408098961382</v>
+        <v>0.084932907136324</v>
       </c>
       <c r="C19">
-        <v>3133.33645222447</v>
+        <v>3149.915531149422</v>
       </c>
       <c r="D19">
-        <v>3265.05645222447</v>
+        <v>3281.635531149422</v>
       </c>
       <c r="E19">
         <v>-1802.58</v>
@@ -2836,37 +2836,37 @@
         <v>242.8</v>
       </c>
       <c r="M19">
-        <v>27.81656208263191</v>
+        <v>27.15713208263191</v>
       </c>
       <c r="N19">
-        <v>214.9834379173681</v>
+        <v>215.6428679173681</v>
       </c>
       <c r="O19">
-        <v>53.26261887972491</v>
+        <v>53.42599411043155</v>
       </c>
       <c r="P19">
-        <v>161.7208190376432</v>
+        <v>162.2168738069365</v>
       </c>
       <c r="Q19">
-        <v>306.9208190376432</v>
+        <v>307.4168738069366</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09283034069180342</v>
+        <v>0.09281096771610194</v>
       </c>
       <c r="T19">
         <v>0.863303274428772</v>
       </c>
       <c r="U19">
-        <v>0.063274105096747</v>
+        <v>0.061774105096747</v>
       </c>
       <c r="V19">
         <v>0.2477521961491617</v>
       </c>
       <c r="W19">
-        <v>0.04759780659965506</v>
+        <v>0.0464694348938788</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.728612805519891</v>
+        <v>8.940561148401986</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,13 +2885,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08505782509843493</v>
+        <v>0.08483868021069624</v>
       </c>
       <c r="C20">
-        <v>3114.37826220753</v>
+        <v>3131.976352894987</v>
       </c>
       <c r="D20">
-        <v>3271.95826220753</v>
+        <v>3289.556352894987</v>
       </c>
       <c r="E20">
         <v>-1776.72</v>
@@ -2918,37 +2918,37 @@
         <v>242.8</v>
       </c>
       <c r="M20">
-        <v>29.45283044043379</v>
+        <v>28.75461044043379</v>
       </c>
       <c r="N20">
-        <v>213.3471695595662</v>
+        <v>214.0453895595662</v>
       </c>
       <c r="O20">
-        <v>52.85722980059012</v>
+        <v>53.03021533898538</v>
       </c>
       <c r="P20">
-        <v>160.4899397589761</v>
+        <v>161.0151742205808</v>
       </c>
       <c r="Q20">
-        <v>305.6899397589761</v>
+        <v>306.2151742205808</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.093280755988411</v>
+        <v>0.09326119747536346</v>
       </c>
       <c r="T20">
         <v>0.8715712349558346</v>
       </c>
       <c r="U20">
-        <v>0.063274105096747</v>
+        <v>0.061774105096747</v>
       </c>
       <c r="V20">
         <v>0.2477521961491617</v>
       </c>
       <c r="W20">
-        <v>0.04759780659965506</v>
+        <v>0.0464694348938788</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.243689871879898</v>
+        <v>8.443863306824099</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,13 +2967,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08497484030073169</v>
+        <v>0.08474445328506845</v>
       </c>
       <c r="C21">
-        <v>3095.449312657216</v>
+        <v>3114.075503830904</v>
       </c>
       <c r="D21">
-        <v>3278.889312657216</v>
+        <v>3297.515503830904</v>
       </c>
       <c r="E21">
         <v>-1750.86</v>
@@ -3000,37 +3000,37 @@
         <v>242.8</v>
       </c>
       <c r="M21">
-        <v>31.08909879823567</v>
+        <v>30.35208879823567</v>
       </c>
       <c r="N21">
-        <v>211.7109012017643</v>
+        <v>212.4479112017643</v>
       </c>
       <c r="O21">
-        <v>52.45184072145531</v>
+        <v>52.6344365675392</v>
       </c>
       <c r="P21">
-        <v>159.259060480309</v>
+        <v>159.8134746342251</v>
       </c>
       <c r="Q21">
-        <v>304.459060480309</v>
+        <v>305.0134746342251</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09374229265036693</v>
+        <v>0.09372254401880428</v>
       </c>
       <c r="T21">
         <v>0.880043342656405</v>
       </c>
       <c r="U21">
-        <v>0.063274105096747</v>
+        <v>0.061774105096747</v>
       </c>
       <c r="V21">
         <v>0.2477521961491617</v>
       </c>
       <c r="W21">
-        <v>0.04759780659965506</v>
+        <v>0.0464694348938788</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.809811457570429</v>
+        <v>7.999449448570197</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,13 +3049,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08511752984418368</v>
+        <v>0.08465022635944065</v>
       </c>
       <c r="C22">
-        <v>3057.689703986304</v>
+        <v>3096.213262846804</v>
       </c>
       <c r="D22">
-        <v>3266.989703986304</v>
+        <v>3305.513262846804</v>
       </c>
       <c r="E22">
         <v>-1725</v>
@@ -3082,45 +3082,45 @@
         <v>242.8</v>
       </c>
       <c r="M22">
-        <v>33.50116715603755</v>
+        <v>31.94956715603755</v>
       </c>
       <c r="N22">
-        <v>209.2988328439625</v>
+        <v>210.8504328439625</v>
       </c>
       <c r="O22">
-        <v>51.854245488548</v>
+        <v>52.23865779609304</v>
       </c>
       <c r="P22">
-        <v>157.4445873554145</v>
+        <v>158.6117750478694</v>
       </c>
       <c r="Q22">
-        <v>302.6445873554144</v>
+        <v>303.8117750478694</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09421536772887176</v>
+        <v>0.09419542422583112</v>
       </c>
       <c r="T22">
         <v>0.8887272530494899</v>
       </c>
       <c r="U22">
-        <v>0.064774105096747</v>
+        <v>0.061774105096747</v>
       </c>
       <c r="V22">
         <v>0.2477521961491617</v>
       </c>
       <c r="W22">
-        <v>0.04872617830543131</v>
+        <v>0.0464694348938788</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.247508687357563</v>
+        <v>7.599476976141688</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08504582876353819</v>
+        <v>0.08468237706485982</v>
       </c>
       <c r="C23">
-        <v>3037.79840689343</v>
+        <v>3067.620030179582</v>
       </c>
       <c r="D23">
-        <v>3272.95840689343</v>
+        <v>3302.780030179582</v>
       </c>
       <c r="E23">
         <v>-1699.14</v>
@@ -3164,37 +3164,37 @@
         <v>242.8</v>
       </c>
       <c r="M23">
-        <v>35.17622551383942</v>
+        <v>33.98149351383942</v>
       </c>
       <c r="N23">
-        <v>207.6237744861606</v>
+        <v>208.8185064861606</v>
       </c>
       <c r="O23">
-        <v>51.43924610172458</v>
+        <v>51.73524357853426</v>
       </c>
       <c r="P23">
-        <v>156.184528384436</v>
+        <v>157.0832629076263</v>
       </c>
       <c r="Q23">
-        <v>301.384528384436</v>
+        <v>302.2832629076263</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09470041939164255</v>
+        <v>0.09468027608366877</v>
       </c>
       <c r="T23">
         <v>0.897631009275311</v>
       </c>
       <c r="U23">
-        <v>0.064774105096747</v>
+        <v>0.06257410509674699</v>
       </c>
       <c r="V23">
         <v>0.2477521961491617</v>
       </c>
       <c r="W23">
-        <v>0.04872617830543131</v>
+        <v>0.04707123313695947</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.902389226054823</v>
+        <v>7.145065589925188</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,13 +3213,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0849741276828927</v>
+        <v>0.08459416812166284</v>
       </c>
       <c r="C24">
-        <v>3017.928959040032</v>
+        <v>3049.269786160444</v>
       </c>
       <c r="D24">
-        <v>3278.948959040032</v>
+        <v>3310.289786160444</v>
       </c>
       <c r="E24">
         <v>-1673.28</v>
@@ -3246,37 +3246,37 @@
         <v>242.8</v>
       </c>
       <c r="M24">
-        <v>36.8512838716413</v>
+        <v>35.59965987164129</v>
       </c>
       <c r="N24">
-        <v>205.9487161283587</v>
+        <v>207.2003401283587</v>
       </c>
       <c r="O24">
-        <v>51.02424671490115</v>
+        <v>51.33433930965415</v>
       </c>
       <c r="P24">
-        <v>154.9244694134576</v>
+        <v>155.8660008187046</v>
       </c>
       <c r="Q24">
-        <v>300.1244694134575</v>
+        <v>301.0660008187045</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09519790827653565</v>
+        <v>0.09517756004042534</v>
       </c>
       <c r="T24">
         <v>0.9067630669428198</v>
       </c>
       <c r="U24">
-        <v>0.064774105096747</v>
+        <v>0.06257410509674699</v>
       </c>
       <c r="V24">
         <v>0.2477521961491617</v>
       </c>
       <c r="W24">
-        <v>0.04872617830543131</v>
+        <v>0.04707123313695947</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.588644261234149</v>
+        <v>6.820289881292227</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,13 +3295,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.0849024266022472</v>
+        <v>0.08450595917846587</v>
       </c>
       <c r="C25">
-        <v>2998.08148061922</v>
+        <v>3030.953770857131</v>
       </c>
       <c r="D25">
-        <v>3284.96148061922</v>
+        <v>3317.833770857131</v>
       </c>
       <c r="E25">
         <v>-1647.42</v>
@@ -3328,37 +3328,37 @@
         <v>242.8</v>
       </c>
       <c r="M25">
-        <v>38.52634222944318</v>
+        <v>37.21782622944318</v>
       </c>
       <c r="N25">
-        <v>204.2736577705568</v>
+        <v>205.5821737705568</v>
       </c>
       <c r="O25">
-        <v>50.60924732807773</v>
+        <v>50.93343504077404</v>
       </c>
       <c r="P25">
-        <v>153.6644104424791</v>
+        <v>154.6487387297828</v>
       </c>
       <c r="Q25">
-        <v>298.8644104424791</v>
+        <v>299.8487387297828</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09570831895064676</v>
+        <v>0.09568776046359116</v>
       </c>
       <c r="T25">
         <v>0.9161323209133808</v>
       </c>
       <c r="U25">
-        <v>0.064774105096747</v>
+        <v>0.06257410509674699</v>
       </c>
       <c r="V25">
         <v>0.2477521961491617</v>
       </c>
       <c r="W25">
-        <v>0.04872617830543131</v>
+        <v>0.04707123313695947</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.302181467267447</v>
+        <v>6.523755538627346</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,13 +3377,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0850834807836956</v>
+        <v>0.08441775023526892</v>
       </c>
       <c r="C26">
-        <v>2957.081375921322</v>
+        <v>3012.672218820762</v>
       </c>
       <c r="D26">
-        <v>3269.821375921322</v>
+        <v>3325.412218820762</v>
       </c>
       <c r="E26">
         <v>-1621.56</v>
@@ -3410,45 +3410,45 @@
         <v>242.8</v>
       </c>
       <c r="M26">
-        <v>41.07029658724505</v>
+        <v>38.83599258724505</v>
       </c>
       <c r="N26">
-        <v>201.729703412755</v>
+        <v>203.964007412755</v>
       </c>
       <c r="O26">
-        <v>49.97897704902908</v>
+        <v>50.53253077189395</v>
       </c>
       <c r="P26">
-        <v>151.7507263637259</v>
+        <v>153.431476640861</v>
       </c>
       <c r="Q26">
-        <v>296.9507263637258</v>
+        <v>298.631476640861</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0962321614846029</v>
+        <v>0.09621138721368241</v>
       </c>
       <c r="T26">
         <v>0.9257481341989565</v>
       </c>
       <c r="U26">
-        <v>0.066174105096747</v>
+        <v>0.06257410509674699</v>
       </c>
       <c r="V26">
         <v>0.2477521961491617</v>
       </c>
       <c r="W26">
-        <v>0.04977932523082249</v>
+        <v>0.04707123313695947</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.911815111542314</v>
+        <v>6.25193239118454</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,13 +3459,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08502231117230402</v>
+        <v>0.08451760324303463</v>
       </c>
       <c r="C27">
-        <v>2936.320863863435</v>
+        <v>2978.235954168589</v>
       </c>
       <c r="D27">
-        <v>3274.920863863435</v>
+        <v>3316.835954168589</v>
       </c>
       <c r="E27">
         <v>-1595.7</v>
@@ -3492,37 +3492,37 @@
         <v>242.8</v>
       </c>
       <c r="M27">
-        <v>42.78155894504693</v>
+        <v>41.10065894504693</v>
       </c>
       <c r="N27">
-        <v>200.0184410549531</v>
+        <v>201.6993410549531</v>
       </c>
       <c r="O27">
-        <v>49.55500804169628</v>
+        <v>49.9714547082034</v>
       </c>
       <c r="P27">
-        <v>150.4634330132568</v>
+        <v>151.7278863467497</v>
       </c>
       <c r="Q27">
-        <v>295.6634330132568</v>
+        <v>296.9278863467497</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09676997315279785</v>
+        <v>0.09674897734377608</v>
       </c>
       <c r="T27">
         <v>0.9356203691721475</v>
       </c>
       <c r="U27">
-        <v>0.066174105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V27">
         <v>0.2477521961491617</v>
       </c>
       <c r="W27">
-        <v>0.04977932523082249</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.675342507080621</v>
+        <v>5.907447866581225</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08496114156091243</v>
+        <v>0.08443691677787617</v>
       </c>
       <c r="C28">
-        <v>2915.576282581991</v>
+        <v>2959.302587838426</v>
       </c>
       <c r="D28">
-        <v>3280.036282581991</v>
+        <v>3323.762587838426</v>
       </c>
       <c r="E28">
         <v>-1569.84</v>
@@ -3574,37 +3574,37 @@
         <v>242.8</v>
       </c>
       <c r="M28">
-        <v>44.49282130284881</v>
+        <v>42.74468530284881</v>
       </c>
       <c r="N28">
-        <v>198.3071786971512</v>
+        <v>200.0553146971512</v>
       </c>
       <c r="O28">
-        <v>49.13103903436347</v>
+        <v>49.56414356753088</v>
       </c>
       <c r="P28">
-        <v>149.1761396627877</v>
+        <v>150.4911711296203</v>
       </c>
       <c r="Q28">
-        <v>294.3761396627877</v>
+        <v>295.6911711296203</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09732232027148457</v>
+        <v>0.09730109693684526</v>
       </c>
       <c r="T28">
         <v>0.9457594213067763</v>
       </c>
       <c r="U28">
-        <v>0.066174105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V28">
         <v>0.2477521961491617</v>
       </c>
       <c r="W28">
-        <v>0.04977932523082249</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.457060102962135</v>
+        <v>5.680238333251177</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,13 +3623,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08489997194952084</v>
+        <v>0.0843562303127177</v>
       </c>
       <c r="C29">
-        <v>2894.847706845284</v>
+        <v>2940.398212184051</v>
       </c>
       <c r="D29">
-        <v>3285.167706845284</v>
+        <v>3330.718212184051</v>
       </c>
       <c r="E29">
         <v>-1543.98</v>
@@ -3656,37 +3656,37 @@
         <v>242.8</v>
       </c>
       <c r="M29">
-        <v>46.20408366065069</v>
+        <v>44.38871166065069</v>
       </c>
       <c r="N29">
-        <v>196.5959163393493</v>
+        <v>198.4112883393493</v>
       </c>
       <c r="O29">
-        <v>48.70707002703066</v>
+        <v>49.15683242685835</v>
       </c>
       <c r="P29">
-        <v>147.8888463123187</v>
+        <v>149.254455912491</v>
       </c>
       <c r="Q29">
-        <v>293.0888463123187</v>
+        <v>294.454455912491</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09788980018794353</v>
+        <v>0.09786834309410811</v>
       </c>
       <c r="T29">
         <v>0.9561762556916688</v>
       </c>
       <c r="U29">
-        <v>0.066174105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V29">
         <v>0.2477521961491617</v>
       </c>
       <c r="W29">
-        <v>0.04977932523082249</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.254946765815389</v>
+        <v>5.469859135723356</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08483880233812927</v>
+        <v>0.08427554384755924</v>
       </c>
       <c r="C30">
-        <v>2874.135211890223</v>
+        <v>2921.523009593148</v>
       </c>
       <c r="D30">
-        <v>3290.315211890223</v>
+        <v>3337.703009593148</v>
       </c>
       <c r="E30">
         <v>-1518.12</v>
@@ -3738,37 +3738,37 @@
         <v>242.8</v>
       </c>
       <c r="M30">
-        <v>47.91534601845257</v>
+        <v>46.03273801845256</v>
       </c>
       <c r="N30">
-        <v>194.8846539815474</v>
+        <v>196.7672619815474</v>
       </c>
       <c r="O30">
-        <v>48.28310101969785</v>
+        <v>48.74952128618583</v>
       </c>
       <c r="P30">
-        <v>146.6015529618496</v>
+        <v>148.0177406953616</v>
       </c>
       <c r="Q30">
-        <v>291.8015529618496</v>
+        <v>293.2177406953616</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09847304343541524</v>
+        <v>0.09845134608907272</v>
       </c>
       <c r="T30">
         <v>0.9668824465872526</v>
       </c>
       <c r="U30">
-        <v>0.066174105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V30">
         <v>0.2477521961491617</v>
       </c>
       <c r="W30">
-        <v>0.04977932523082249</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.067270095607697</v>
+        <v>5.274507023733237</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,13 +3787,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08477763272673769</v>
+        <v>0.08419485738240078</v>
       </c>
       <c r="C31">
-        <v>2853.438873426011</v>
+        <v>2902.677163986551</v>
       </c>
       <c r="D31">
-        <v>3295.478873426011</v>
+        <v>3344.717163986551</v>
       </c>
       <c r="E31">
         <v>-1492.26</v>
@@ -3820,37 +3820,37 @@
         <v>242.8</v>
       </c>
       <c r="M31">
-        <v>49.62660837625444</v>
+        <v>47.67676437625443</v>
       </c>
       <c r="N31">
-        <v>193.1733916237456</v>
+        <v>195.1232356237456</v>
       </c>
       <c r="O31">
-        <v>47.85913201236504</v>
+        <v>48.34221014551331</v>
       </c>
       <c r="P31">
-        <v>145.3142596113805</v>
+        <v>146.7810254782323</v>
       </c>
       <c r="Q31">
-        <v>290.5142596113805</v>
+        <v>291.9810254782323</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09907271607013968</v>
+        <v>0.09905077170361379</v>
       </c>
       <c r="T31">
         <v>0.9778902203249658</v>
       </c>
       <c r="U31">
-        <v>0.066174105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V31">
         <v>0.2477521961491617</v>
       </c>
       <c r="W31">
-        <v>0.04977932523082249</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.892536644035018</v>
+        <v>5.092627471190712</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,13 +3869,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08471646311534611</v>
+        <v>0.08411417091724231</v>
       </c>
       <c r="C32">
-        <v>2832.758767637854</v>
+        <v>2883.860860834378</v>
       </c>
       <c r="D32">
-        <v>3300.658767637854</v>
+        <v>3351.760860834378</v>
       </c>
       <c r="E32">
         <v>-1466.4</v>
@@ -3902,37 +3902,37 @@
         <v>242.8</v>
       </c>
       <c r="M32">
-        <v>51.33787073405632</v>
+        <v>49.32079073405631</v>
       </c>
       <c r="N32">
-        <v>191.4621292659437</v>
+        <v>193.4792092659437</v>
       </c>
       <c r="O32">
-        <v>47.43516300503224</v>
+        <v>47.93489900484079</v>
       </c>
       <c r="P32">
-        <v>144.0269662609115</v>
+        <v>145.5443102611029</v>
       </c>
       <c r="Q32">
-        <v>289.2269662609115</v>
+        <v>290.7443102611029</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09968952220871338</v>
+        <v>0.0996673237642846</v>
       </c>
       <c r="T32">
         <v>0.9892125018837563</v>
       </c>
       <c r="U32">
-        <v>0.066174105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V32">
         <v>0.2477521961491617</v>
       </c>
       <c r="W32">
-        <v>0.04977932523082249</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.729452089233851</v>
+        <v>4.922873222151021</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,13 +3951,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08465529350395452</v>
+        <v>0.08403348445208385</v>
       </c>
       <c r="C33">
-        <v>2812.094971190715</v>
+        <v>2865.074287172388</v>
       </c>
       <c r="D33">
-        <v>3305.854971190714</v>
+        <v>3358.834287172388</v>
       </c>
       <c r="E33">
         <v>-1440.54</v>
@@ -3984,37 +3984,37 @@
         <v>242.8</v>
       </c>
       <c r="M33">
-        <v>53.0491330918582</v>
+        <v>50.96481709185819</v>
       </c>
       <c r="N33">
-        <v>189.7508669081418</v>
+        <v>191.8351829081418</v>
       </c>
       <c r="O33">
-        <v>47.01119399769943</v>
+        <v>47.52758786416826</v>
       </c>
       <c r="P33">
-        <v>142.7396729104424</v>
+        <v>144.3075950439735</v>
       </c>
       <c r="Q33">
-        <v>287.9396729104424</v>
+        <v>289.5075950439735</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1003242067860863</v>
+        <v>0.1003017468991778</v>
       </c>
       <c r="T33">
         <v>1.000862965516715</v>
       </c>
       <c r="U33">
-        <v>0.066174105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V33">
         <v>0.2477521961491617</v>
       </c>
       <c r="W33">
-        <v>0.04977932523082249</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.576889118613403</v>
+        <v>4.764070860146148</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,13 +4033,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08521999406536684</v>
+        <v>0.08395279798692538</v>
       </c>
       <c r="C34">
-        <v>2738.877831687255</v>
+        <v>2846.317631618524</v>
       </c>
       <c r="D34">
-        <v>3258.497831687255</v>
+        <v>3365.937631618523</v>
       </c>
       <c r="E34">
         <v>-1414.68</v>
@@ -4066,45 +4066,45 @@
         <v>242.8</v>
       </c>
       <c r="M34">
-        <v>56.91194744966008</v>
+        <v>52.60884344966007</v>
       </c>
       <c r="N34">
-        <v>185.8880525503399</v>
+        <v>190.1911565503399</v>
       </c>
       <c r="O34">
-        <v>46.05417325723749</v>
+        <v>47.12027672349574</v>
       </c>
       <c r="P34">
-        <v>139.8338792931024</v>
+        <v>143.0708798268442</v>
       </c>
       <c r="Q34">
-        <v>285.0338792931024</v>
+        <v>288.2708798268442</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1009775585569114</v>
+        <v>0.1009548295380384</v>
       </c>
       <c r="T34">
         <v>1.01285608984476</v>
       </c>
       <c r="U34">
-        <v>0.068774105096747</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V34">
         <v>0.2477521961491617</v>
       </c>
       <c r="W34">
-        <v>0.05173516952083467</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.266239531071436</v>
+        <v>4.615193645766581</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,13 +4115,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08517838289687539</v>
+        <v>0.08449271595994384</v>
       </c>
       <c r="C35">
-        <v>2716.461088934726</v>
+        <v>2773.489354042677</v>
       </c>
       <c r="D35">
-        <v>3261.941088934726</v>
+        <v>3318.969354042677</v>
       </c>
       <c r="E35">
         <v>-1388.82</v>
@@ -4148,37 +4148,37 @@
         <v>242.8</v>
       </c>
       <c r="M35">
-        <v>58.69044580746196</v>
+        <v>56.38631980746195</v>
       </c>
       <c r="N35">
-        <v>184.109554192538</v>
+        <v>186.4136801925381</v>
       </c>
       <c r="O35">
-        <v>45.6135463832444</v>
+        <v>46.18439865994879</v>
       </c>
       <c r="P35">
-        <v>138.4960078092936</v>
+        <v>140.2292815325893</v>
       </c>
       <c r="Q35">
-        <v>283.6960078092936</v>
+        <v>285.4292815325892</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1016504133656716</v>
+        <v>0.101627407181044</v>
       </c>
       <c r="T35">
         <v>1.025207217884091</v>
       </c>
       <c r="U35">
-        <v>0.068774105096747</v>
+        <v>0.06607410509674699</v>
       </c>
       <c r="V35">
         <v>0.2477521961491617</v>
       </c>
       <c r="W35">
-        <v>0.05173516952083467</v>
+        <v>0.0497041004504374</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.136959545281393</v>
+        <v>4.306008989930015</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,13 +4197,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08513677172838394</v>
+        <v>0.08443083568988165</v>
       </c>
       <c r="C36">
-        <v>2694.051630865267</v>
+        <v>2752.945799216295</v>
       </c>
       <c r="D36">
-        <v>3265.391630865267</v>
+        <v>3324.285799216295</v>
       </c>
       <c r="E36">
         <v>-1362.96</v>
@@ -4230,37 +4230,37 @@
         <v>242.8</v>
       </c>
       <c r="M36">
-        <v>60.46894416526384</v>
+        <v>58.09499616526383</v>
       </c>
       <c r="N36">
-        <v>182.3310558347362</v>
+        <v>184.7050038347362</v>
       </c>
       <c r="O36">
-        <v>45.17291950925131</v>
+        <v>45.76107033979522</v>
       </c>
       <c r="P36">
-        <v>137.1581363254849</v>
+        <v>138.9439334949409</v>
       </c>
       <c r="Q36">
-        <v>282.3581363254848</v>
+        <v>284.1439334949409</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1023436577140911</v>
+        <v>0.1023203659647469</v>
       </c>
       <c r="T36">
         <v>1.037932622530674</v>
       </c>
       <c r="U36">
-        <v>0.068774105096747</v>
+        <v>0.06607410509674699</v>
       </c>
       <c r="V36">
         <v>0.2477521961491617</v>
       </c>
       <c r="W36">
-        <v>0.05173516952083467</v>
+        <v>0.0497041004504374</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.015284264537822</v>
+        <v>4.179361666696779</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,13 +4279,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08580603473453151</v>
+        <v>0.08436895541981945</v>
       </c>
       <c r="C37">
-        <v>2613.564726858815</v>
+        <v>2732.419303864796</v>
       </c>
       <c r="D37">
-        <v>3210.764726858815</v>
+        <v>3329.619303864796</v>
       </c>
       <c r="E37">
         <v>-1337.1</v>
@@ -4312,45 +4312,45 @@
         <v>242.8</v>
       </c>
       <c r="M37">
-        <v>64.69121252306572</v>
+        <v>59.80367252306571</v>
       </c>
       <c r="N37">
-        <v>178.1087874769343</v>
+        <v>182.9963274769343</v>
       </c>
       <c r="O37">
-        <v>44.12684325087478</v>
+        <v>45.33774201964166</v>
       </c>
       <c r="P37">
-        <v>133.9819442260595</v>
+        <v>137.6585854572926</v>
       </c>
       <c r="Q37">
-        <v>279.1819442260595</v>
+        <v>282.8585854572926</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1030582326578467</v>
+        <v>0.103034646557179</v>
       </c>
       <c r="T37">
         <v>1.051049578089459</v>
       </c>
       <c r="U37">
-        <v>0.071474105096747</v>
+        <v>0.06607410509674699</v>
       </c>
       <c r="V37">
         <v>0.2477521961491617</v>
       </c>
       <c r="W37">
-        <v>0.05376623859123193</v>
+        <v>0.0497041004504374</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.753214548474098</v>
+        <v>4.059951333362585</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,13 +4361,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08578473425674403</v>
+        <v>0.08525490738260932</v>
       </c>
       <c r="C38">
-        <v>2589.415150199537</v>
+        <v>2631.793376042538</v>
       </c>
       <c r="D38">
-        <v>3212.475150199537</v>
+        <v>3254.853376042538</v>
       </c>
       <c r="E38">
         <v>-1311.24</v>
@@ -4394,37 +4394,37 @@
         <v>242.8</v>
       </c>
       <c r="M38">
-        <v>66.53953288086758</v>
+        <v>64.77070888086757</v>
       </c>
       <c r="N38">
-        <v>176.2604671191324</v>
+        <v>178.0292911191324</v>
       </c>
       <c r="O38">
-        <v>43.66891782304217</v>
+        <v>44.10714785364351</v>
       </c>
       <c r="P38">
-        <v>132.5915492960903</v>
+        <v>133.9221432654889</v>
       </c>
       <c r="Q38">
-        <v>277.7915492960902</v>
+        <v>279.1221432654889</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1037951380685946</v>
+        <v>0.1037712484181247</v>
       </c>
       <c r="T38">
         <v>1.064576438509456</v>
       </c>
       <c r="U38">
-        <v>0.071474105096747</v>
+        <v>0.069574105096747</v>
       </c>
       <c r="V38">
         <v>0.2477521961491617</v>
       </c>
       <c r="W38">
-        <v>0.05376623859123193</v>
+        <v>0.05233696776391534</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.648958588794263</v>
+        <v>3.748608038960648</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,13 +4443,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08576343377895654</v>
+        <v>0.08521935578568192</v>
       </c>
       <c r="C39">
-        <v>2565.267396848765</v>
+        <v>2608.868868847443</v>
       </c>
       <c r="D39">
-        <v>3214.187396848765</v>
+        <v>3257.788868847443</v>
       </c>
       <c r="E39">
         <v>-1285.38</v>
@@ -4476,37 +4476,37 @@
         <v>242.8</v>
       </c>
       <c r="M39">
-        <v>68.38785323866945</v>
+        <v>66.56989523866946</v>
       </c>
       <c r="N39">
-        <v>174.4121467613306</v>
+        <v>176.2301047613306</v>
       </c>
       <c r="O39">
-        <v>43.21099239520955</v>
+        <v>43.66139548221648</v>
       </c>
       <c r="P39">
-        <v>131.201154366121</v>
+        <v>132.5687092791141</v>
       </c>
       <c r="Q39">
-        <v>276.401154366121</v>
+        <v>277.7687092791141</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1045554373019059</v>
+        <v>0.1045312344651321</v>
       </c>
       <c r="T39">
         <v>1.078532723069771</v>
       </c>
       <c r="U39">
-        <v>0.071474105096747</v>
+        <v>0.069574105096747</v>
       </c>
       <c r="V39">
         <v>0.2477521961491617</v>
       </c>
       <c r="W39">
-        <v>0.05376623859123193</v>
+        <v>0.05233696776391534</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.550338086394418</v>
+        <v>3.647294308177927</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,13 +4525,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08708564787884665</v>
+        <v>0.0851838041887545</v>
       </c>
       <c r="C40">
-        <v>2436.469835876638</v>
+        <v>2585.949661366744</v>
       </c>
       <c r="D40">
-        <v>3111.249835876638</v>
+        <v>3260.729661366744</v>
       </c>
       <c r="E40">
         <v>-1259.52</v>
@@ -4558,45 +4558,45 @@
         <v>242.8</v>
       </c>
       <c r="M40">
-        <v>74.85476959647134</v>
+        <v>68.36908159647135</v>
       </c>
       <c r="N40">
-        <v>167.9452304035287</v>
+        <v>174.4309184035287</v>
       </c>
       <c r="O40">
-        <v>41.6087996652512</v>
+        <v>43.21564311078946</v>
       </c>
       <c r="P40">
-        <v>126.3364307382775</v>
+        <v>131.2152752927392</v>
       </c>
       <c r="Q40">
-        <v>271.5364307382775</v>
+        <v>276.4152752927392</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.105340262316937</v>
+        <v>0.1053157361910753</v>
       </c>
       <c r="T40">
         <v>1.092939210357838</v>
       </c>
       <c r="U40">
-        <v>0.07617410509674699</v>
+        <v>0.069574105096747</v>
       </c>
       <c r="V40">
         <v>0.2477521961491617</v>
       </c>
       <c r="W40">
-        <v>0.05730180326933087</v>
+        <v>0.05233696776391534</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.243614285487636</v>
+        <v>3.55131287901535</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,13 +4607,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08709970304784016</v>
+        <v>0.0859697071936322</v>
       </c>
       <c r="C41">
-        <v>2409.551011260548</v>
+        <v>2496.294891178122</v>
       </c>
       <c r="D41">
-        <v>3110.191011260548</v>
+        <v>3196.934891178122</v>
       </c>
       <c r="E41">
         <v>-1233.66</v>
@@ -4640,37 +4640,37 @@
         <v>242.8</v>
       </c>
       <c r="M41">
-        <v>76.82463195427322</v>
+        <v>72.99217995427321</v>
       </c>
       <c r="N41">
-        <v>165.9753680457268</v>
+        <v>169.8078200457268</v>
       </c>
       <c r="O41">
-        <v>41.12076193999421</v>
+        <v>42.07026033963046</v>
       </c>
       <c r="P41">
-        <v>124.8546061057326</v>
+        <v>127.7375597060963</v>
       </c>
       <c r="Q41">
-        <v>270.0546061057325</v>
+        <v>272.9375597060963</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.106150819299674</v>
+        <v>0.1061259592850821</v>
       </c>
       <c r="T41">
         <v>1.107818041491415</v>
       </c>
       <c r="U41">
-        <v>0.07617410509674699</v>
+        <v>0.07237410509674699</v>
       </c>
       <c r="V41">
         <v>0.2477521961491617</v>
       </c>
       <c r="W41">
-        <v>0.05730180326933087</v>
+        <v>0.05444326161469768</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.16044468842385</v>
+        <v>3.326383732505384</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,13 +4689,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08711375821683366</v>
+        <v>0.0859552185352126</v>
       </c>
       <c r="C42">
-        <v>2382.632907080437</v>
+        <v>2471.58839747986</v>
       </c>
       <c r="D42">
-        <v>3109.132907080437</v>
+        <v>3198.08839747986</v>
       </c>
       <c r="E42">
         <v>-1207.8</v>
@@ -4722,37 +4722,37 @@
         <v>242.8</v>
       </c>
       <c r="M42">
-        <v>78.79449431207509</v>
+        <v>74.86377431207509</v>
       </c>
       <c r="N42">
-        <v>164.0055056879249</v>
+        <v>167.9362256879249</v>
       </c>
       <c r="O42">
-        <v>40.63272421473724</v>
+        <v>41.60656872718467</v>
       </c>
       <c r="P42">
-        <v>123.3727814731877</v>
+        <v>126.3296569607403</v>
       </c>
       <c r="Q42">
-        <v>268.5727814731877</v>
+        <v>271.5296569607402</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1069883948485022</v>
+        <v>0.1069631898155559</v>
       </c>
       <c r="T42">
         <v>1.123192833662778</v>
       </c>
       <c r="U42">
-        <v>0.07617410509674699</v>
+        <v>0.07237410509674699</v>
       </c>
       <c r="V42">
         <v>0.2477521961491617</v>
       </c>
       <c r="W42">
-        <v>0.05730180326933087</v>
+        <v>0.05444326161469768</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.081433571213255</v>
+        <v>3.243224139192749</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,13 +4771,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08712781338582717</v>
+        <v>0.08594072987679302</v>
       </c>
       <c r="C43">
-        <v>2355.715522601265</v>
+        <v>2446.882736489861</v>
       </c>
       <c r="D43">
-        <v>3108.075522601264</v>
+        <v>3199.24273648986</v>
       </c>
       <c r="E43">
         <v>-1181.94</v>
@@ -4804,37 +4804,37 @@
         <v>242.8</v>
       </c>
       <c r="M43">
-        <v>80.76435666987696</v>
+        <v>76.73536866987696</v>
       </c>
       <c r="N43">
-        <v>162.035643330123</v>
+        <v>166.0646313301231</v>
       </c>
       <c r="O43">
-        <v>40.14468648948025</v>
+        <v>41.14287711473887</v>
       </c>
       <c r="P43">
-        <v>121.8909568406428</v>
+        <v>124.9217542153842</v>
       </c>
       <c r="Q43">
-        <v>267.0909568406428</v>
+        <v>270.1217542153842</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1078543627888161</v>
+        <v>0.1078288010419779</v>
       </c>
       <c r="T43">
         <v>1.139088805229781</v>
       </c>
       <c r="U43">
-        <v>0.07617410509674699</v>
+        <v>0.07237410509674699</v>
       </c>
       <c r="V43">
         <v>0.2477521961491617</v>
       </c>
       <c r="W43">
-        <v>0.05730180326933087</v>
+        <v>0.05444326161469768</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.0062766548422</v>
+        <v>3.164121111407561</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,13 +4853,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09008014847666204</v>
+        <v>0.08592624121837343</v>
       </c>
       <c r="C44">
-        <v>2122.627662126115</v>
+        <v>2422.177909110144</v>
       </c>
       <c r="D44">
-        <v>2900.847662126114</v>
+        <v>3200.397909110144</v>
       </c>
       <c r="E44">
         <v>-1156.08</v>
@@ -4886,45 +4886,45 @@
         <v>242.8</v>
       </c>
       <c r="M44">
-        <v>92.83513502767883</v>
+        <v>78.60696302767883</v>
       </c>
       <c r="N44">
-        <v>149.9648649723212</v>
+        <v>164.1930369723212</v>
       </c>
       <c r="O44">
-        <v>37.15412464210507</v>
+        <v>40.67918550229308</v>
       </c>
       <c r="P44">
-        <v>112.8107403302161</v>
+        <v>123.5138514700281</v>
       </c>
       <c r="Q44">
-        <v>258.0107403302161</v>
+        <v>268.7138514700281</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1087501916925891</v>
+        <v>0.10872426093138</v>
       </c>
       <c r="T44">
         <v>1.15553291374737</v>
       </c>
       <c r="U44">
-        <v>0.08547410509674699</v>
+        <v>0.07237410509674699</v>
       </c>
       <c r="V44">
         <v>0.2477521961491617</v>
       </c>
       <c r="W44">
-        <v>0.06429770784514366</v>
+        <v>0.05444326161469768</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.61538909732408</v>
+        <v>3.088784894469286</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,13 +4935,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09016416269141367</v>
+        <v>0.08591175255995384</v>
       </c>
       <c r="C45">
-        <v>2091.274209220381</v>
+        <v>2397.473916244027</v>
       </c>
       <c r="D45">
-        <v>2895.354209220381</v>
+        <v>3201.553916244027</v>
       </c>
       <c r="E45">
         <v>-1130.22</v>
@@ -4968,45 +4968,45 @@
         <v>242.8</v>
       </c>
       <c r="M45">
-        <v>95.04549538548072</v>
+        <v>80.47855738548073</v>
       </c>
       <c r="N45">
-        <v>147.7545046145193</v>
+        <v>162.3214426145193</v>
       </c>
       <c r="O45">
-        <v>36.60650300917861</v>
+        <v>40.21549388984728</v>
       </c>
       <c r="P45">
-        <v>111.1480016053407</v>
+        <v>122.105948724672</v>
       </c>
       <c r="Q45">
-        <v>256.3480016053407</v>
+        <v>267.305948724672</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.109677453189477</v>
+        <v>0.1096511404660243</v>
       </c>
       <c r="T45">
         <v>1.172554008528734</v>
       </c>
       <c r="U45">
-        <v>0.08547410509674699</v>
+        <v>0.07237410509674699</v>
       </c>
       <c r="V45">
         <v>0.2477521961491617</v>
       </c>
       <c r="W45">
-        <v>0.06429770784514366</v>
+        <v>0.05444326161469768</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.554566095060729</v>
+        <v>3.016952687621163</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,13 +5017,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09180382536452886</v>
+        <v>0.08847897836435033</v>
       </c>
       <c r="C46">
-        <v>1962.218351382739</v>
+        <v>2179.03405273882</v>
       </c>
       <c r="D46">
-        <v>2792.158351382739</v>
+        <v>3008.974052738819</v>
       </c>
       <c r="E46">
         <v>-1104.36</v>
@@ -5050,45 +5050,45 @@
         <v>242.8</v>
       </c>
       <c r="M46">
-        <v>102.6037037432826</v>
+        <v>91.22530374328259</v>
       </c>
       <c r="N46">
-        <v>140.1962962567174</v>
+        <v>151.5746962567174</v>
       </c>
       <c r="O46">
-        <v>34.73394028958024</v>
+        <v>37.55296387824386</v>
       </c>
       <c r="P46">
-        <v>105.4623559671372</v>
+        <v>114.0217323784735</v>
       </c>
       <c r="Q46">
-        <v>250.6623559671372</v>
+        <v>259.2217323784735</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1106378311683966</v>
+        <v>0.1106111228411915</v>
       </c>
       <c r="T46">
         <v>1.190182999552289</v>
       </c>
       <c r="U46">
-        <v>0.090174105096747</v>
+        <v>0.08017410509674699</v>
       </c>
       <c r="V46">
         <v>0.2477521961491617</v>
       </c>
       <c r="W46">
-        <v>0.06783327252324262</v>
+        <v>0.06031079448473423</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.366386311038952</v>
+        <v>2.661542248006805</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,13 +5099,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09192319522606147</v>
+        <v>0.08852316503463112</v>
       </c>
       <c r="C47">
-        <v>1929.132062003868</v>
+        <v>2150.062004643974</v>
       </c>
       <c r="D47">
-        <v>2784.932062003867</v>
+        <v>3005.862004643973</v>
       </c>
       <c r="E47">
         <v>-1078.5</v>
@@ -5132,45 +5132,45 @@
         <v>242.8</v>
       </c>
       <c r="M47">
-        <v>104.9356061010845</v>
+        <v>93.29860610108449</v>
       </c>
       <c r="N47">
-        <v>137.8643938989155</v>
+        <v>149.5013938989155</v>
       </c>
       <c r="O47">
-        <v>34.15620635922942</v>
+        <v>37.03929866581721</v>
       </c>
       <c r="P47">
-        <v>103.7081875396861</v>
+        <v>112.4620952330983</v>
       </c>
       <c r="Q47">
-        <v>248.9081875396861</v>
+        <v>257.6620952330983</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1116331319829132</v>
+        <v>0.1116060136663649</v>
       </c>
       <c r="T47">
         <v>1.208453044794883</v>
       </c>
       <c r="U47">
-        <v>0.090174105096747</v>
+        <v>0.08017410509674699</v>
       </c>
       <c r="V47">
         <v>0.2477521961491617</v>
       </c>
       <c r="W47">
-        <v>0.06783327252324262</v>
+        <v>0.06031079448473423</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.313799948571419</v>
+        <v>2.602396864717765</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,13 +5181,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09204256508759409</v>
+        <v>0.08856735170491188</v>
       </c>
       <c r="C48">
-        <v>1896.08308029428</v>
+        <v>2121.096387204177</v>
       </c>
       <c r="D48">
-        <v>2777.743080294279</v>
+        <v>3002.756387204177</v>
       </c>
       <c r="E48">
         <v>-1052.64</v>
@@ -5214,45 +5214,45 @@
         <v>242.8</v>
       </c>
       <c r="M48">
-        <v>107.2675084588864</v>
+        <v>95.37190845888635</v>
       </c>
       <c r="N48">
-        <v>135.5324915411136</v>
+        <v>147.4280915411136</v>
       </c>
       <c r="O48">
-        <v>33.57847242887859</v>
+        <v>36.52563345339055</v>
       </c>
       <c r="P48">
-        <v>101.954019112235</v>
+        <v>110.9024580877231</v>
       </c>
       <c r="Q48">
-        <v>247.154019112235</v>
+        <v>256.1024580877231</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1126652957905601</v>
+        <v>0.112637752299878</v>
       </c>
       <c r="T48">
         <v>1.227399758379795</v>
       </c>
       <c r="U48">
-        <v>0.090174105096747</v>
+        <v>0.08017410509674699</v>
       </c>
       <c r="V48">
         <v>0.2477521961491617</v>
       </c>
       <c r="W48">
-        <v>0.06783327252324262</v>
+        <v>0.06031079448473423</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.263499949689432</v>
+        <v>2.545823019832596</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,13 +5263,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09216193494912672</v>
+        <v>0.08999040859965123</v>
       </c>
       <c r="C49">
-        <v>1863.07111808149</v>
+        <v>1998.539087599049</v>
       </c>
       <c r="D49">
-        <v>2770.59111808149</v>
+        <v>2906.059087599049</v>
       </c>
       <c r="E49">
         <v>-1026.78</v>
@@ -5296,37 +5296,37 @@
         <v>242.8</v>
       </c>
       <c r="M49">
-        <v>109.5994108166882</v>
+        <v>102.1853488166882</v>
       </c>
       <c r="N49">
-        <v>133.2005891833118</v>
+        <v>140.6146511833118</v>
       </c>
       <c r="O49">
-        <v>33.00073849852777</v>
+        <v>34.83758864141381</v>
       </c>
       <c r="P49">
-        <v>100.199850684784</v>
+        <v>105.7770625418979</v>
       </c>
       <c r="Q49">
-        <v>245.399850684784</v>
+        <v>250.9770625418979</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1137364091758541</v>
+        <v>0.1137084244667312</v>
       </c>
       <c r="T49">
         <v>1.247061442288667</v>
       </c>
       <c r="U49">
-        <v>0.090174105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V49">
         <v>0.2477521961491617</v>
       </c>
       <c r="W49">
-        <v>0.06783327252324262</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.215340376291785</v>
+        <v>2.376074484372142</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,13 +5345,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09228130481065933</v>
+        <v>0.09006393293428219</v>
       </c>
       <c r="C50">
-        <v>1830.095890153272</v>
+        <v>1967.85199595468</v>
       </c>
       <c r="D50">
-        <v>2763.475890153271</v>
+        <v>2901.231995954679</v>
       </c>
       <c r="E50">
         <v>-1000.92</v>
@@ -5378,37 +5378,37 @@
         <v>242.8</v>
       </c>
       <c r="M50">
-        <v>111.9313131744901</v>
+        <v>104.3595051744901</v>
       </c>
       <c r="N50">
-        <v>130.8686868255099</v>
+        <v>138.4404948255099</v>
       </c>
       <c r="O50">
-        <v>32.42300456817694</v>
+        <v>34.29893662899674</v>
       </c>
       <c r="P50">
-        <v>98.44568225733295</v>
+        <v>104.1415581965132</v>
       </c>
       <c r="Q50">
-        <v>243.6456822573329</v>
+        <v>249.3415581965132</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1148487192298132</v>
+        <v>0.1148202763323096</v>
       </c>
       <c r="T50">
         <v>1.267479344809417</v>
       </c>
       <c r="U50">
-        <v>0.090174105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V50">
         <v>0.2477521961491617</v>
       </c>
       <c r="W50">
-        <v>0.06783327252324262</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.169187451785706</v>
+        <v>2.32657293261439</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,13 +5427,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09240067467219196</v>
+        <v>0.09013745726891315</v>
       </c>
       <c r="C51">
-        <v>1797.157114219729</v>
+        <v>1937.180913739955</v>
       </c>
       <c r="D51">
-        <v>2756.397114219729</v>
+        <v>2896.420913739955</v>
       </c>
       <c r="E51">
         <v>-975.0599999999999</v>
@@ -5460,37 +5460,37 @@
         <v>242.8</v>
       </c>
       <c r="M51">
-        <v>114.263215532292</v>
+        <v>106.533661532292</v>
       </c>
       <c r="N51">
-        <v>128.536784467708</v>
+        <v>136.266338467708</v>
       </c>
       <c r="O51">
-        <v>31.84527063782612</v>
+        <v>33.76028461657966</v>
       </c>
       <c r="P51">
-        <v>96.69151382988191</v>
+        <v>102.5060538511284</v>
       </c>
       <c r="Q51">
-        <v>241.8915138298819</v>
+        <v>247.7060538511284</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1160046492858884</v>
+        <v>0.1159757302318322</v>
       </c>
       <c r="T51">
         <v>1.288697949389805</v>
       </c>
       <c r="U51">
-        <v>0.090174105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V51">
         <v>0.2477521961491617</v>
       </c>
       <c r="W51">
-        <v>0.06783327252324262</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.12491832011661</v>
+        <v>2.279091852356953</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,13 +5509,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09252004453372457</v>
+        <v>0.0902109816035441</v>
       </c>
       <c r="C52">
-        <v>1764.25451087598</v>
+        <v>1906.525761441927</v>
       </c>
       <c r="D52">
-        <v>2749.35451087598</v>
+        <v>2891.625761441927</v>
       </c>
       <c r="E52">
         <v>-949.1999999999998</v>
@@ -5542,37 +5542,37 @@
         <v>242.8</v>
       </c>
       <c r="M52">
-        <v>116.5951178900939</v>
+        <v>108.7078178900939</v>
       </c>
       <c r="N52">
-        <v>126.2048821099061</v>
+        <v>134.0921821099062</v>
       </c>
       <c r="O52">
-        <v>31.2675367074753</v>
+        <v>33.22163260416259</v>
       </c>
       <c r="P52">
-        <v>94.93734540243084</v>
+        <v>100.8705495057436</v>
       </c>
       <c r="Q52">
-        <v>240.1373454024308</v>
+        <v>246.0705495057436</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1172068165442065</v>
+        <v>0.1171774022873357</v>
       </c>
       <c r="T52">
         <v>1.310765298153409</v>
       </c>
       <c r="U52">
-        <v>0.090174105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V52">
         <v>0.2477521961491617</v>
       </c>
       <c r="W52">
-        <v>0.06783327252324262</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.082419953714278</v>
+        <v>2.233510015309814</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,13 +5591,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09263941439525721</v>
+        <v>0.09028450593817507</v>
       </c>
       <c r="C53">
-        <v>1731.387803565382</v>
+        <v>1875.886460073327</v>
       </c>
       <c r="D53">
-        <v>2742.347803565382</v>
+        <v>2886.846460073327</v>
       </c>
       <c r="E53">
         <v>-923.3399999999997</v>
@@ -5624,37 +5624,37 @@
         <v>242.8</v>
       </c>
       <c r="M53">
-        <v>118.9270202478958</v>
+        <v>110.8819742478958</v>
       </c>
       <c r="N53">
-        <v>123.8729797521042</v>
+        <v>131.9180257521043</v>
       </c>
       <c r="O53">
-        <v>30.68980277712447</v>
+        <v>32.6829805917455</v>
       </c>
       <c r="P53">
-        <v>93.18317697497977</v>
+        <v>99.23504516035877</v>
       </c>
       <c r="Q53">
-        <v>238.3831769749798</v>
+        <v>244.4350451603588</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1184580518538846</v>
+        <v>0.1184281221818394</v>
       </c>
       <c r="T53">
         <v>1.333733355029813</v>
       </c>
       <c r="U53">
-        <v>0.090174105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V53">
         <v>0.2477521961491617</v>
       </c>
       <c r="W53">
-        <v>0.06783327252324262</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.041588189915958</v>
+        <v>2.189715701284131</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,13 +5673,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09275878425678982</v>
+        <v>0.09035803027280601</v>
       </c>
       <c r="C54">
-        <v>1698.556718543338</v>
+        <v>1845.262931168233</v>
       </c>
       <c r="D54">
-        <v>2735.376718543338</v>
+        <v>2882.082931168233</v>
       </c>
       <c r="E54">
         <v>-897.4799999999998</v>
@@ -5706,37 +5706,37 @@
         <v>242.8</v>
       </c>
       <c r="M54">
-        <v>121.2589226056976</v>
+        <v>113.0561306056976</v>
       </c>
       <c r="N54">
-        <v>121.5410773943024</v>
+        <v>129.7438693943024</v>
       </c>
       <c r="O54">
-        <v>30.11206884677365</v>
+        <v>32.14432857932843</v>
       </c>
       <c r="P54">
-        <v>91.42900854752872</v>
+        <v>97.59954081497398</v>
       </c>
       <c r="Q54">
-        <v>236.6290085475287</v>
+        <v>242.799540814974</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1197614219681326</v>
+        <v>0.1197309554052807</v>
       </c>
       <c r="T54">
         <v>1.357658414276067</v>
       </c>
       <c r="U54">
-        <v>0.090174105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V54">
         <v>0.2477521961491617</v>
       </c>
       <c r="W54">
-        <v>0.06783327252324262</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.002326878571421</v>
+        <v>2.147605783951744</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,13 +5755,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09937682289578982</v>
+        <v>0.09043155460743696</v>
       </c>
       <c r="C55">
-        <v>1334.811270375724</v>
+        <v>1814.655096777762</v>
       </c>
       <c r="D55">
-        <v>2397.491270375724</v>
+        <v>2877.335096777762</v>
       </c>
       <c r="E55">
         <v>-871.6199999999997</v>
@@ -5788,45 +5788,45 @@
         <v>242.8</v>
       </c>
       <c r="M55">
-        <v>145.9312789634995</v>
+        <v>115.2302869634995</v>
       </c>
       <c r="N55">
-        <v>96.86872103650049</v>
+        <v>127.5697130365005</v>
       </c>
       <c r="O55">
-        <v>23.9994383749535</v>
+        <v>31.60567656691135</v>
       </c>
       <c r="P55">
-        <v>72.86928266154699</v>
+        <v>95.96403646958916</v>
       </c>
       <c r="Q55">
-        <v>218.069282661547</v>
+        <v>241.1640364695891</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1211202546404337</v>
+        <v>0.1210892283403578</v>
       </c>
       <c r="T55">
         <v>1.382601561149821</v>
       </c>
       <c r="U55">
-        <v>0.106474105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V55">
         <v>0.2477521961491617</v>
       </c>
       <c r="W55">
-        <v>0.08009491172601127</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.663796834541068</v>
+        <v>2.107084920103598</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,13 +5837,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09961880914935015</v>
+        <v>0.09050507894206791</v>
       </c>
       <c r="C56">
-        <v>1298.171397323315</v>
+        <v>1784.062879465832</v>
       </c>
       <c r="D56">
-        <v>2386.711397323315</v>
+        <v>2872.602879465832</v>
       </c>
       <c r="E56">
         <v>-845.7599999999998</v>
@@ -5870,45 +5870,45 @@
         <v>242.8</v>
       </c>
       <c r="M56">
-        <v>148.6846993213014</v>
+        <v>117.4044433213014</v>
       </c>
       <c r="N56">
-        <v>94.11530067869862</v>
+        <v>125.3955566786986</v>
       </c>
       <c r="O56">
-        <v>23.31727243438627</v>
+        <v>31.06702455449427</v>
       </c>
       <c r="P56">
-        <v>70.79802824431235</v>
+        <v>94.32853212420436</v>
       </c>
       <c r="Q56">
-        <v>215.9980282443123</v>
+        <v>239.5285321242043</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1225381669941392</v>
+        <v>0.1225065566204382</v>
       </c>
       <c r="T56">
         <v>1.40862919267026</v>
       </c>
       <c r="U56">
-        <v>0.106474105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V56">
         <v>0.2477521961491617</v>
       </c>
       <c r="W56">
-        <v>0.08009491172601127</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.632985782049567</v>
+        <v>2.068064828990568</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,13 +5919,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09986079540291046</v>
+        <v>0.09057860327669889</v>
       </c>
       <c r="C57">
-        <v>1261.628029735704</v>
+        <v>1753.486202304942</v>
       </c>
       <c r="D57">
-        <v>2376.028029735704</v>
+        <v>2867.886202304942</v>
       </c>
       <c r="E57">
         <v>-819.8999999999996</v>
@@ -5952,45 +5952,45 @@
         <v>242.8</v>
       </c>
       <c r="M57">
-        <v>151.4381196791033</v>
+        <v>119.5785996791033</v>
       </c>
       <c r="N57">
-        <v>91.36188032089674</v>
+        <v>123.2214003208967</v>
       </c>
       <c r="O57">
-        <v>22.63510649381905</v>
+        <v>30.52837254207719</v>
       </c>
       <c r="P57">
-        <v>68.72677382707769</v>
+        <v>92.69302777881956</v>
       </c>
       <c r="Q57">
-        <v>213.9267738270777</v>
+        <v>237.8930277788195</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1240190976746761</v>
+        <v>0.1239868772685223</v>
       </c>
       <c r="T57">
         <v>1.43581360781383</v>
       </c>
       <c r="U57">
-        <v>0.106474105096747</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V57">
         <v>0.2477521961491617</v>
       </c>
       <c r="W57">
-        <v>0.08009491172601127</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.603295131466847</v>
+        <v>2.030463650281649</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,13 +6001,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1001027816564707</v>
+        <v>0.0966340021475517</v>
       </c>
       <c r="C58">
-        <v>1225.179877458215</v>
+        <v>1386.000634033447</v>
       </c>
       <c r="D58">
-        <v>2365.439877458215</v>
+        <v>2526.260634033447</v>
       </c>
       <c r="E58">
         <v>-794.0399999999997</v>
@@ -6034,37 +6034,37 @@
         <v>242.8</v>
       </c>
       <c r="M58">
-        <v>154.1915400369051</v>
+        <v>142.3166280369051</v>
       </c>
       <c r="N58">
-        <v>88.60845996309487</v>
+        <v>100.4833719630949</v>
       </c>
       <c r="O58">
-        <v>21.95294055325182</v>
+        <v>24.89497608032986</v>
       </c>
       <c r="P58">
-        <v>66.65551940984305</v>
+        <v>75.58839588276501</v>
       </c>
       <c r="Q58">
-        <v>211.8555194098431</v>
+        <v>220.788395882765</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1255673433861464</v>
+        <v>0.1255344852187919</v>
       </c>
       <c r="T58">
         <v>1.464233678191198</v>
       </c>
       <c r="U58">
-        <v>0.106474105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V58">
         <v>0.2477521961491617</v>
       </c>
       <c r="W58">
-        <v>0.08009491172601127</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.574664861262082</v>
+        <v>1.706055036218521</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,13 +6083,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1003447679100311</v>
+        <v>0.09681434567032948</v>
       </c>
       <c r="C59">
-        <v>1188.825673231103</v>
+        <v>1351.209915895052</v>
       </c>
       <c r="D59">
-        <v>2354.945673231103</v>
+        <v>2517.329915895052</v>
       </c>
       <c r="E59">
         <v>-768.1799999999996</v>
@@ -6116,37 +6116,37 @@
         <v>242.8</v>
       </c>
       <c r="M59">
-        <v>156.944960394707</v>
+        <v>144.857996394707</v>
       </c>
       <c r="N59">
-        <v>85.85503960529297</v>
+        <v>97.94200360529297</v>
       </c>
       <c r="O59">
-        <v>21.27077461268459</v>
+        <v>24.26534648846045</v>
       </c>
       <c r="P59">
-        <v>64.58426499260838</v>
+        <v>73.67665711683252</v>
       </c>
       <c r="Q59">
-        <v>209.7842649926084</v>
+        <v>218.8766571168325</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1271876005260573</v>
+        <v>0.1271540749341904</v>
       </c>
       <c r="T59">
         <v>1.493975612307049</v>
       </c>
       <c r="U59">
-        <v>0.106474105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V59">
         <v>0.2477521961491617</v>
       </c>
       <c r="W59">
-        <v>0.08009491172601127</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.547039161941695</v>
+        <v>1.676124246109424</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,13 +6165,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1005867541635914</v>
+        <v>0.09699468919310725</v>
       </c>
       <c r="C60">
-        <v>1152.56417218394</v>
+        <v>1316.482118235144</v>
       </c>
       <c r="D60">
-        <v>2344.54417218394</v>
+        <v>2508.462118235143</v>
       </c>
       <c r="E60">
         <v>-742.3199999999999</v>
@@ -6198,37 +6198,37 @@
         <v>242.8</v>
       </c>
       <c r="M60">
-        <v>159.6983807525089</v>
+        <v>147.3993647525089</v>
       </c>
       <c r="N60">
-        <v>83.10161924749113</v>
+        <v>95.40063524749112</v>
       </c>
       <c r="O60">
-        <v>20.58860867211737</v>
+        <v>23.63571689659105</v>
       </c>
       <c r="P60">
-        <v>62.51301057537376</v>
+        <v>71.76491835090007</v>
       </c>
       <c r="Q60">
-        <v>207.7130105753737</v>
+        <v>216.9649183509001</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1288850127678686</v>
+        <v>0.1288507879693698</v>
       </c>
       <c r="T60">
         <v>1.525133828999844</v>
       </c>
       <c r="U60">
-        <v>0.106474105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V60">
         <v>0.2477521961491617</v>
       </c>
       <c r="W60">
-        <v>0.08009491172601127</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.5203660729427</v>
+        <v>1.647225552210986</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,13 +6247,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1321584473546601</v>
+        <v>0.09717503271588504</v>
       </c>
       <c r="C61">
-        <v>269.5647545065178</v>
+        <v>1281.816578438041</v>
       </c>
       <c r="D61">
-        <v>1487.404754506518</v>
+        <v>2499.65657843804</v>
       </c>
       <c r="E61">
         <v>-716.4599999999998</v>
@@ -6280,45 +6280,45 @@
         <v>242.8</v>
       </c>
       <c r="M61">
-        <v>262.2351971103108</v>
+        <v>149.9407331103108</v>
       </c>
       <c r="N61">
-        <v>-19.43519711031075</v>
+        <v>92.85926688968925</v>
       </c>
       <c r="O61">
-        <v>-4.815112766671331</v>
+        <v>23.00608730472165</v>
       </c>
       <c r="P61">
-        <v>-14.62008434363942</v>
+        <v>69.85317958496761</v>
       </c>
       <c r="Q61">
-        <v>130.5799156563606</v>
+        <v>215.0531795849676</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.131742007596115</v>
+        <v>0.1306302674940701</v>
       </c>
       <c r="T61">
-        <v>1.577577697234058</v>
+        <v>1.557811958702044</v>
       </c>
       <c r="U61">
-        <v>0.171874105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V61">
-        <v>0.2293903865227986</v>
+        <v>0.2477521961491617</v>
       </c>
       <c r="W61">
-        <v>0.1324478376953441</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.9258863900632865</v>
+        <v>1.619306475054868</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,13 +6329,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1334191884056276</v>
+        <v>0.09735537623866282</v>
       </c>
       <c r="C62">
-        <v>222.3026818836893</v>
+        <v>1247.21264315953</v>
       </c>
       <c r="D62">
-        <v>1466.002681883689</v>
+        <v>2490.91264315953</v>
       </c>
       <c r="E62">
         <v>-690.5999999999999</v>
@@ -6362,45 +6362,45 @@
         <v>242.8</v>
       </c>
       <c r="M62">
-        <v>266.6798614681126</v>
+        <v>152.4821014681126</v>
       </c>
       <c r="N62">
-        <v>-23.87986146811261</v>
+        <v>90.31789853188738</v>
       </c>
       <c r="O62">
-        <v>-5.916288122462644</v>
+        <v>22.37645771285225</v>
       </c>
       <c r="P62">
-        <v>-17.96357334564996</v>
+        <v>67.94144081903514</v>
       </c>
       <c r="Q62">
-        <v>127.23642665435</v>
+        <v>213.1414408190351</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1338905577860178</v>
+        <v>0.1324987209950055</v>
       </c>
       <c r="T62">
-        <v>1.617017139664909</v>
+        <v>1.592123994889355</v>
       </c>
       <c r="U62">
-        <v>0.171874105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V62">
-        <v>0.2255672134140853</v>
+        <v>0.2477521961491617</v>
       </c>
       <c r="W62">
-        <v>0.1331049421520341</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9104549502288984</v>
+        <v>1.592318033803953</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,13 +6411,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1346799294565951</v>
+        <v>0.09753571976144058</v>
       </c>
       <c r="C63">
-        <v>175.6477760688526</v>
+        <v>1212.669668165261</v>
       </c>
       <c r="D63">
-        <v>1445.207776068853</v>
+        <v>2482.229668165261</v>
       </c>
       <c r="E63">
         <v>-664.7399999999998</v>
@@ -6444,45 +6444,45 @@
         <v>242.8</v>
       </c>
       <c r="M63">
-        <v>271.1245258259145</v>
+        <v>155.0234698259145</v>
       </c>
       <c r="N63">
-        <v>-28.32452582591452</v>
+        <v>87.77653017408548</v>
       </c>
       <c r="O63">
-        <v>-7.017463478253971</v>
+        <v>21.74682812098284</v>
       </c>
       <c r="P63">
-        <v>-21.30706234766055</v>
+        <v>66.02970205310264</v>
       </c>
       <c r="Q63">
-        <v>123.8929376523394</v>
+        <v>211.2297020531026</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1361492900369414</v>
+        <v>0.1344629926241939</v>
       </c>
       <c r="T63">
-        <v>1.658479117605036</v>
+        <v>1.628195622676015</v>
       </c>
       <c r="U63">
-        <v>0.171874105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V63">
-        <v>0.2218693902433626</v>
+        <v>0.2477521961491617</v>
       </c>
       <c r="W63">
-        <v>0.1337405022003081</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8955294592415394</v>
+        <v>1.566214459479298</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,13 +6493,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1359406705075626</v>
+        <v>0.09771606328421836</v>
       </c>
       <c r="C64">
-        <v>129.5745608774421</v>
+        <v>1178.187018172527</v>
       </c>
       <c r="D64">
-        <v>1424.994560877442</v>
+        <v>2473.607018172527</v>
       </c>
       <c r="E64">
         <v>-638.8799999999999</v>
@@ -6526,45 +6526,45 @@
         <v>242.8</v>
       </c>
       <c r="M64">
-        <v>275.5691901837164</v>
+        <v>157.5648381837164</v>
       </c>
       <c r="N64">
-        <v>-32.76919018371638</v>
+        <v>85.23516181628361</v>
       </c>
       <c r="O64">
-        <v>-8.118638834045285</v>
+        <v>21.11719852911343</v>
       </c>
       <c r="P64">
-        <v>-24.65055134967109</v>
+        <v>64.11796328717017</v>
       </c>
       <c r="Q64">
-        <v>120.5494486503289</v>
+        <v>209.3179632871702</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1385269029326504</v>
+        <v>0.136530646970708</v>
       </c>
       <c r="T64">
-        <v>1.702123304910431</v>
+        <v>1.666165757188288</v>
       </c>
       <c r="U64">
-        <v>0.171874105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V64">
-        <v>0.2182908516910503</v>
+        <v>0.2477521961491617</v>
       </c>
       <c r="W64">
-        <v>0.134355560311541</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8810854357053856</v>
+        <v>1.540952935939309</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,13 +6575,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1372014115585301</v>
+        <v>0.09789640680699614</v>
       </c>
       <c r="C65">
-        <v>84.05896574308076</v>
+        <v>1143.764066695322</v>
       </c>
       <c r="D65">
-        <v>1405.338965743081</v>
+        <v>2465.044066695322</v>
       </c>
       <c r="E65">
         <v>-613.0199999999998</v>
@@ -6608,45 +6608,45 @@
         <v>242.8</v>
       </c>
       <c r="M65">
-        <v>280.0138545415183</v>
+        <v>160.1062065415183</v>
       </c>
       <c r="N65">
-        <v>-37.21385454151829</v>
+        <v>82.69379345848174</v>
       </c>
       <c r="O65">
-        <v>-9.219814189836612</v>
+        <v>20.48756893724403</v>
       </c>
       <c r="P65">
-        <v>-27.99404035168168</v>
+        <v>62.2062245212377</v>
       </c>
       <c r="Q65">
-        <v>117.2059596483183</v>
+        <v>207.4062245212377</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1410330354443436</v>
+        <v>0.1387100664170337</v>
       </c>
       <c r="T65">
-        <v>1.748126637475578</v>
+        <v>1.706188331403928</v>
       </c>
       <c r="U65">
-        <v>0.171874105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V65">
-        <v>0.2148259175372241</v>
+        <v>0.2477521961491617</v>
       </c>
       <c r="W65">
-        <v>0.134951092768449</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8670999525989508</v>
+        <v>1.516493365527575</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,13 +6657,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1384621526094975</v>
+        <v>0.1270983792921679</v>
       </c>
       <c r="C66">
-        <v>39.07823009491267</v>
+        <v>232.47252873467</v>
       </c>
       <c r="D66">
-        <v>1386.218230094913</v>
+        <v>1579.61252873467</v>
       </c>
       <c r="E66">
         <v>-587.1599999999999</v>
@@ -6690,37 +6690,37 @@
         <v>242.8</v>
       </c>
       <c r="M66">
-        <v>284.4585188993202</v>
+        <v>256.6538468993202</v>
       </c>
       <c r="N66">
-        <v>-41.65851889932014</v>
+        <v>-13.85384689932016</v>
       </c>
       <c r="O66">
-        <v>-10.32098954562792</v>
+        <v>-3.432320994420824</v>
       </c>
       <c r="P66">
-        <v>-31.33752935369222</v>
+        <v>-10.42152590489934</v>
       </c>
       <c r="Q66">
-        <v>113.8624706463078</v>
+        <v>134.7784740951006</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1436783975400198</v>
+        <v>0.1419790272141041</v>
       </c>
       <c r="T66">
-        <v>1.796685710738788</v>
+        <v>1.766219100758279</v>
       </c>
       <c r="U66">
-        <v>0.171874105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V66">
-        <v>0.211469262575705</v>
+        <v>0.2343788489896031</v>
       </c>
       <c r="W66">
-        <v>0.1355280148360787</v>
+        <v>0.1187280148360787</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8535515158395922</v>
+        <v>0.9460212770364018</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,13 +6739,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.139722893660465</v>
+        <v>0.1281911203431353</v>
       </c>
       <c r="C67">
-        <v>-5.38918456373267</v>
+        <v>185.6623650813276</v>
       </c>
       <c r="D67">
-        <v>1367.610815436267</v>
+        <v>1558.662365081328</v>
       </c>
       <c r="E67">
         <v>-561.2999999999997</v>
@@ -6772,37 +6772,37 @@
         <v>242.8</v>
       </c>
       <c r="M67">
-        <v>288.9031832571221</v>
+        <v>260.6640632571221</v>
       </c>
       <c r="N67">
-        <v>-46.10318325712205</v>
+        <v>-17.86406325712204</v>
       </c>
       <c r="O67">
-        <v>-11.42216490141925</v>
+        <v>-4.425860904099532</v>
       </c>
       <c r="P67">
-        <v>-34.6810183557028</v>
+        <v>-13.43820235302251</v>
       </c>
       <c r="Q67">
-        <v>110.5189816442972</v>
+        <v>131.7617976469775</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1464749231840204</v>
+        <v>0.1447269994202214</v>
       </c>
       <c r="T67">
-        <v>1.848019588188468</v>
+        <v>1.816682503637087</v>
       </c>
       <c r="U67">
-        <v>0.171874105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V67">
-        <v>0.2082158893053095</v>
+        <v>0.2307730205436092</v>
       </c>
       <c r="W67">
-        <v>0.1360871854554736</v>
+        <v>0.1192871854554736</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8404199540574445</v>
+        <v>0.931467103543534</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1409836347114324</v>
+        <v>0.1292838613941028</v>
       </c>
       <c r="C68">
-        <v>-49.36367558936831</v>
+        <v>139.4006452461365</v>
       </c>
       <c r="D68">
-        <v>1349.496324410632</v>
+        <v>1538.260645246136</v>
       </c>
       <c r="E68">
         <v>-535.4399999999998</v>
@@ -6854,37 +6854,37 @@
         <v>242.8</v>
       </c>
       <c r="M68">
-        <v>293.3478476149239</v>
+        <v>264.6742796149239</v>
       </c>
       <c r="N68">
-        <v>-50.54784761492391</v>
+        <v>-21.87427961492392</v>
       </c>
       <c r="O68">
-        <v>-12.52334025721056</v>
+        <v>-5.419400813778241</v>
       </c>
       <c r="P68">
-        <v>-38.02450735771335</v>
+        <v>-16.45487880114568</v>
       </c>
       <c r="Q68">
-        <v>107.1754926422866</v>
+        <v>128.7451211988543</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1494359503364916</v>
+        <v>0.1476366170502279</v>
       </c>
       <c r="T68">
-        <v>1.902373105488129</v>
+        <v>1.870114341979354</v>
       </c>
       <c r="U68">
-        <v>0.171874105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V68">
-        <v>0.2050611031037139</v>
+        <v>0.2272764596262818</v>
       </c>
       <c r="W68">
-        <v>0.1366294115106444</v>
+        <v>0.1198294115106444</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8276863183899076</v>
+        <v>0.9173539656110562</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,13 +6903,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1422443757623999</v>
+        <v>0.1303766024450703</v>
       </c>
       <c r="C69">
-        <v>-92.86457378446516</v>
+        <v>93.66611132595585</v>
       </c>
       <c r="D69">
-        <v>1331.855426215535</v>
+        <v>1518.386111325956</v>
       </c>
       <c r="E69">
         <v>-509.5799999999997</v>
@@ -6936,37 +6936,37 @@
         <v>242.8</v>
       </c>
       <c r="M69">
-        <v>297.7925119727258</v>
+        <v>268.6844959727258</v>
       </c>
       <c r="N69">
-        <v>-54.99251197272577</v>
+        <v>-25.8844959727258</v>
       </c>
       <c r="O69">
-        <v>-13.62451561300188</v>
+        <v>-6.412940723456949</v>
       </c>
       <c r="P69">
-        <v>-41.36799635972389</v>
+        <v>-19.47155524926885</v>
       </c>
       <c r="Q69">
-        <v>103.8320036402761</v>
+        <v>125.7284447507311</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1525764336800216</v>
+        <v>0.150722575142659</v>
       </c>
       <c r="T69">
-        <v>1.960020775351406</v>
+        <v>1.926784473554486</v>
       </c>
       <c r="U69">
-        <v>0.171874105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V69">
-        <v>0.202000489624554</v>
+        <v>0.2238842736617104</v>
       </c>
       <c r="W69">
-        <v>0.1371554517134221</v>
+        <v>0.1203554517134221</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8153327912497598</v>
+        <v>0.9036621153780554</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1435051168133674</v>
+        <v>0.1314693434960377</v>
       </c>
       <c r="C70">
-        <v>-135.9102122090226</v>
+        <v>48.43859002422641</v>
       </c>
       <c r="D70">
-        <v>1314.669787790977</v>
+        <v>1499.018590024226</v>
       </c>
       <c r="E70">
         <v>-483.7199999999998</v>
@@ -7018,37 +7018,37 @@
         <v>242.8</v>
       </c>
       <c r="M70">
-        <v>302.2371763305277</v>
+        <v>272.6947123305277</v>
       </c>
       <c r="N70">
-        <v>-59.43717633052768</v>
+        <v>-29.89471233052768</v>
       </c>
       <c r="O70">
-        <v>-14.72569096879321</v>
+        <v>-7.406480633135658</v>
       </c>
       <c r="P70">
-        <v>-44.71148536173447</v>
+        <v>-22.48823169739202</v>
       </c>
       <c r="Q70">
-        <v>100.4885146382655</v>
+        <v>122.711768302608</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1559131972325223</v>
+        <v>0.1540014056158671</v>
       </c>
       <c r="T70">
-        <v>2.021271424581137</v>
+        <v>1.986996488353064</v>
       </c>
       <c r="U70">
-        <v>0.171874105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V70">
-        <v>0.1990298941888988</v>
+        <v>0.2205918578725676</v>
       </c>
       <c r="W70">
-        <v>0.1376660201455298</v>
+        <v>0.1208660201455298</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8033426031431455</v>
+        <v>0.8903729666224958</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,13 +7067,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1820687012841666</v>
+        <v>0.1325620845470052</v>
       </c>
       <c r="C71">
-        <v>-533.8173436112786</v>
+        <v>3.698924349579556</v>
       </c>
       <c r="D71">
-        <v>942.6226563887216</v>
+        <v>1480.13892434958</v>
       </c>
       <c r="E71">
         <v>-457.8599999999997</v>
@@ -7100,45 +7100,45 @@
         <v>242.8</v>
       </c>
       <c r="M71">
-        <v>399.8243886883296</v>
+        <v>276.7049286883296</v>
       </c>
       <c r="N71">
-        <v>-157.0243886883296</v>
+        <v>-33.90492868832956</v>
       </c>
       <c r="O71">
-        <v>-38.90313714651325</v>
+        <v>-8.400020542814365</v>
       </c>
       <c r="P71">
-        <v>-118.1212515418164</v>
+        <v>-25.50490814551519</v>
       </c>
       <c r="Q71">
-        <v>27.07874845818361</v>
+        <v>119.6950918544848</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1636098920459317</v>
+        <v>0.1574917735389596</v>
       </c>
       <c r="T71">
-        <v>2.162554301484755</v>
+        <v>2.051093149267679</v>
       </c>
       <c r="U71">
-        <v>0.224074105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V71">
-        <v>0.1504516355852113</v>
+        <v>0.2173948744251391</v>
       </c>
       <c r="W71">
-        <v>0.1903617894926489</v>
+        <v>0.1213617894926489</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.607266607213566</v>
+        <v>0.8774690105844886</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,13 +7149,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.183851442335134</v>
+        <v>0.1336548255979727</v>
       </c>
       <c r="C72">
-        <v>-571.8499951728372</v>
+        <v>-40.57108958833351</v>
       </c>
       <c r="D72">
-        <v>930.4500048271632</v>
+        <v>1461.728910411667</v>
       </c>
       <c r="E72">
         <v>-431.9999999999995</v>
@@ -7182,45 +7182,45 @@
         <v>242.8</v>
       </c>
       <c r="M72">
-        <v>405.6189450461315</v>
+        <v>280.7151450461315</v>
       </c>
       <c r="N72">
-        <v>-162.8189450461315</v>
+        <v>-37.9151450461315</v>
       </c>
       <c r="O72">
-        <v>-40.33875120986875</v>
+        <v>-9.393560452493089</v>
       </c>
       <c r="P72">
-        <v>-122.4801938362627</v>
+        <v>-28.52158459363841</v>
       </c>
       <c r="Q72">
-        <v>22.71980616373725</v>
+        <v>116.6784154063616</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1675368884474628</v>
+        <v>0.1612148326569249</v>
       </c>
       <c r="T72">
-        <v>2.23463944486758</v>
+        <v>2.119462920909935</v>
       </c>
       <c r="U72">
-        <v>0.224074105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V72">
-        <v>0.1483023265054226</v>
+        <v>0.2142892333619227</v>
       </c>
       <c r="W72">
-        <v>0.1908433940012789</v>
+        <v>0.1218433940012789</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5985913699676579</v>
+        <v>0.8649337390047099</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,13 +7231,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1856341833861015</v>
+        <v>0.1347475666489401</v>
       </c>
       <c r="C73">
-        <v>-609.572269327206</v>
+        <v>-84.38876112416028</v>
       </c>
       <c r="D73">
-        <v>918.5877306727941</v>
+        <v>1443.77123887584</v>
       </c>
       <c r="E73">
         <v>-406.1399999999999</v>
@@ -7264,45 +7264,45 @@
         <v>242.8</v>
       </c>
       <c r="M73">
-        <v>411.4135014039333</v>
+        <v>284.7253614039333</v>
       </c>
       <c r="N73">
-        <v>-168.6135014039333</v>
+        <v>-41.92536140393332</v>
       </c>
       <c r="O73">
-        <v>-41.77436527322424</v>
+        <v>-10.38710036217178</v>
       </c>
       <c r="P73">
-        <v>-126.8391361307091</v>
+        <v>-31.53826104176154</v>
       </c>
       <c r="Q73">
-        <v>18.36086386929094</v>
+        <v>113.6617389582384</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1717347121870304</v>
+        <v>0.1651946544726809</v>
       </c>
       <c r="T73">
-        <v>2.311695977449221</v>
+        <v>2.192547849217173</v>
       </c>
       <c r="U73">
-        <v>0.224074105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V73">
-        <v>0.1462135613433744</v>
+        <v>0.2112710751455577</v>
       </c>
       <c r="W73">
-        <v>0.1913114321857221</v>
+        <v>0.1223114321857221</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5901605056019164</v>
+        <v>0.8527515736666156</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,13 +7313,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.187416924437069</v>
+        <v>0.1358403076999076</v>
       </c>
       <c r="C74">
-        <v>-646.9958876086716</v>
+        <v>-127.7705593190756</v>
       </c>
       <c r="D74">
-        <v>907.0241123913282</v>
+        <v>1426.249440680924</v>
       </c>
       <c r="E74">
         <v>-380.28</v>
@@ -7346,45 +7346,45 @@
         <v>242.8</v>
       </c>
       <c r="M74">
-        <v>417.2080577617352</v>
+        <v>288.7355777617352</v>
       </c>
       <c r="N74">
-        <v>-174.4080577617352</v>
+        <v>-45.93557776173515</v>
       </c>
       <c r="O74">
-        <v>-43.20997933657974</v>
+        <v>-11.38064027185048</v>
       </c>
       <c r="P74">
-        <v>-131.1980784251554</v>
+        <v>-34.55493748988467</v>
       </c>
       <c r="Q74">
-        <v>14.00192157484457</v>
+        <v>110.6450625101153</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1762323804794244</v>
+        <v>0.1694587492752767</v>
       </c>
       <c r="T74">
-        <v>2.394256548072407</v>
+        <v>2.270853129546358</v>
       </c>
       <c r="U74">
-        <v>0.224074105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V74">
-        <v>0.1441828174358276</v>
+        <v>0.208336754657425</v>
       </c>
       <c r="W74">
-        <v>0.1917664693094863</v>
+        <v>0.1227664693094863</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5819638319130009</v>
+        <v>0.840907801810135</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,13 +7395,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1891996654880364</v>
+        <v>0.1369330487508751</v>
       </c>
       <c r="C75">
-        <v>-684.1319886642366</v>
+        <v>-170.7321633377435</v>
       </c>
       <c r="D75">
-        <v>895.7480113357633</v>
+        <v>1409.147836662257</v>
       </c>
       <c r="E75">
         <v>-354.4199999999998</v>
@@ -7428,45 +7428,45 @@
         <v>242.8</v>
       </c>
       <c r="M75">
-        <v>423.0026141195371</v>
+        <v>292.7457941195371</v>
       </c>
       <c r="N75">
-        <v>-180.2026141195371</v>
+        <v>-49.94579411953708</v>
       </c>
       <c r="O75">
-        <v>-44.64559339993525</v>
+        <v>-12.3741801815292</v>
       </c>
       <c r="P75">
-        <v>-135.5570207196018</v>
+        <v>-37.57161393800789</v>
       </c>
       <c r="Q75">
-        <v>9.642979280398151</v>
+        <v>107.6283860619921</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1810632093860697</v>
+        <v>0.1740387029521388</v>
       </c>
       <c r="T75">
-        <v>2.482932716519533</v>
+        <v>2.354958801011038</v>
       </c>
       <c r="U75">
-        <v>0.224074105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V75">
-        <v>0.1422077103476656</v>
+        <v>0.2054828265114328</v>
       </c>
       <c r="W75">
-        <v>0.1922090396627364</v>
+        <v>0.1232090396627365</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5739917246265214</v>
+        <v>0.8293885168538316</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,13 +7477,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1909824065390039</v>
+        <v>0.1380257898018425</v>
       </c>
       <c r="C76">
-        <v>-720.9911640409152</v>
+        <v>-213.2885092439301</v>
       </c>
       <c r="D76">
-        <v>884.7488359590847</v>
+        <v>1392.45149075607</v>
       </c>
       <c r="E76">
         <v>-328.5599999999999</v>
@@ -7510,45 +7510,45 @@
         <v>242.8</v>
       </c>
       <c r="M76">
-        <v>428.797170477339</v>
+        <v>296.7560104773389</v>
       </c>
       <c r="N76">
-        <v>-185.997170477339</v>
+        <v>-53.95601047733891</v>
       </c>
       <c r="O76">
-        <v>-46.08120746329075</v>
+        <v>-13.36772009120789</v>
       </c>
       <c r="P76">
-        <v>-139.9159630140482</v>
+        <v>-40.58829038613101</v>
       </c>
       <c r="Q76">
-        <v>5.284036985951786</v>
+        <v>104.611709613869</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1862656405163031</v>
+        <v>0.1789709607579903</v>
       </c>
       <c r="T76">
-        <v>2.578430128693361</v>
+        <v>2.445534139511463</v>
       </c>
       <c r="U76">
-        <v>0.224074105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V76">
-        <v>0.1402859845321565</v>
+        <v>0.2027060315585756</v>
       </c>
       <c r="W76">
-        <v>0.192639648655088</v>
+        <v>0.1236396486550879</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.566235079699136</v>
+        <v>0.8181805639233746</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,13 +7559,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1927651475899714</v>
+        <v>0.13911853085281</v>
       </c>
       <c r="C77">
-        <v>-757.5834913683475</v>
+        <v>-255.4538335083039</v>
       </c>
       <c r="D77">
-        <v>874.0165086316525</v>
+        <v>1376.146166491696</v>
       </c>
       <c r="E77">
         <v>-302.6999999999998</v>
@@ -7592,45 +7592,45 @@
         <v>242.8</v>
       </c>
       <c r="M77">
-        <v>434.5917268351408</v>
+        <v>300.7662268351409</v>
       </c>
       <c r="N77">
-        <v>-191.7917268351408</v>
+        <v>-57.96622683514084</v>
       </c>
       <c r="O77">
-        <v>-47.51682152664625</v>
+        <v>-14.36126000088662</v>
       </c>
       <c r="P77">
-        <v>-144.2749053084946</v>
+        <v>-43.60496683425423</v>
       </c>
       <c r="Q77">
-        <v>0.9250946915054215</v>
+        <v>101.5950331657458</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1918842661369553</v>
+        <v>0.1842977991883099</v>
       </c>
       <c r="T77">
-        <v>2.681567333841095</v>
+        <v>2.543355505091922</v>
       </c>
       <c r="U77">
-        <v>0.224074105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V77">
-        <v>0.1384155047383945</v>
+        <v>0.2000032844711279</v>
       </c>
       <c r="W77">
-        <v>0.1930587747409767</v>
+        <v>0.1240587747409767</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5586852786364809</v>
+        <v>0.8072714897377294</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,13 +7641,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1945478886409389</v>
+        <v>0.1828294540219931</v>
       </c>
       <c r="C78">
-        <v>-793.9185651552577</v>
+        <v>-720.2896710930463</v>
       </c>
       <c r="D78">
-        <v>863.5414348447424</v>
+        <v>937.170328906954</v>
       </c>
       <c r="E78">
         <v>-276.8399999999997</v>
@@ -7674,37 +7674,37 @@
         <v>242.8</v>
       </c>
       <c r="M78">
-        <v>440.3862831929428</v>
+        <v>410.9058831929427</v>
       </c>
       <c r="N78">
-        <v>-197.5862831929427</v>
+        <v>-168.1058831929427</v>
       </c>
       <c r="O78">
-        <v>-48.95243559000177</v>
+        <v>-41.64860174664601</v>
       </c>
       <c r="P78">
-        <v>-148.633847602941</v>
+        <v>-126.4572814462967</v>
       </c>
       <c r="Q78">
-        <v>-3.433847602941</v>
+        <v>18.74271855370328</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1979711105593285</v>
+        <v>0.1966442996470545</v>
       </c>
       <c r="T78">
-        <v>2.793299306084475</v>
+        <v>2.770085027830925</v>
       </c>
       <c r="U78">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V78">
-        <v>0.1365942480970998</v>
+        <v>0.1463941882690708</v>
       </c>
       <c r="W78">
-        <v>0.1934668711930264</v>
+        <v>0.1784668711930263</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5513341565491586</v>
+        <v>0.590889568465955</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,13 +7723,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1963306296919063</v>
+        <v>0.1844621950729605</v>
       </c>
       <c r="C79">
-        <v>-830.0055253975677</v>
+        <v>-757.1848091633033</v>
       </c>
       <c r="D79">
-        <v>853.3144746024323</v>
+        <v>926.1351908366968</v>
       </c>
       <c r="E79">
         <v>-250.9799999999998</v>
@@ -7756,37 +7756,37 @@
         <v>242.8</v>
       </c>
       <c r="M79">
-        <v>446.1808395507446</v>
+        <v>416.3125395507446</v>
       </c>
       <c r="N79">
-        <v>-203.3808395507446</v>
+        <v>-173.5125395507446</v>
       </c>
       <c r="O79">
-        <v>-50.38804965335726</v>
+        <v>-42.98811273311525</v>
       </c>
       <c r="P79">
-        <v>-152.9927898973874</v>
+        <v>-130.5244268176293</v>
       </c>
       <c r="Q79">
-        <v>-7.792789897387365</v>
+        <v>14.67557318237067</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2045872458010384</v>
+        <v>0.203202747457796</v>
       </c>
       <c r="T79">
-        <v>2.914747102001191</v>
+        <v>2.890523507301835</v>
       </c>
       <c r="U79">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V79">
-        <v>0.1348202968231115</v>
+        <v>0.1444929650447971</v>
       </c>
       <c r="W79">
-        <v>0.1938643677372305</v>
+        <v>0.1788643677372305</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5441739726978709</v>
+        <v>0.5832156779663971</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,13 +7805,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1981133707428738</v>
+        <v>0.186094936123928</v>
       </c>
       <c r="C80">
-        <v>-865.8530841774639</v>
+        <v>-793.8230951556714</v>
       </c>
       <c r="D80">
-        <v>843.3269158225363</v>
+        <v>915.3569048443289</v>
       </c>
       <c r="E80">
         <v>-225.1199999999997</v>
@@ -7838,37 +7838,37 @@
         <v>242.8</v>
       </c>
       <c r="M80">
-        <v>451.9753959085465</v>
+        <v>421.7191959085465</v>
       </c>
       <c r="N80">
-        <v>-209.1753959085465</v>
+        <v>-178.9191959085465</v>
       </c>
       <c r="O80">
-        <v>-51.82366371671278</v>
+        <v>-44.32762371958451</v>
       </c>
       <c r="P80">
-        <v>-157.3517321918337</v>
+        <v>-134.591572188962</v>
       </c>
       <c r="Q80">
-        <v>-12.15173219183376</v>
+        <v>10.60842781103798</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2118048478829037</v>
+        <v>0.2103574177967867</v>
       </c>
       <c r="T80">
-        <v>3.047235606637609</v>
+        <v>3.021910939451919</v>
       </c>
       <c r="U80">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V80">
-        <v>0.1330918314792254</v>
+        <v>0.1426404911339664</v>
       </c>
       <c r="W80">
-        <v>0.1942516720623525</v>
+        <v>0.1792516720623525</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5371973833043084</v>
+        <v>0.5757385538899047</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,13 +7887,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1998961117938413</v>
+        <v>0.1877276771748955</v>
       </c>
       <c r="C81">
-        <v>-901.4695504161059</v>
+        <v>-830.2133935764939</v>
       </c>
       <c r="D81">
-        <v>833.5704495838943</v>
+        <v>904.8266064235062</v>
       </c>
       <c r="E81">
         <v>-199.2599999999998</v>
@@ -7920,37 +7920,37 @@
         <v>242.8</v>
       </c>
       <c r="M81">
-        <v>457.7699522663484</v>
+        <v>427.1258522663484</v>
       </c>
       <c r="N81">
-        <v>-214.9699522663483</v>
+        <v>-184.3258522663484</v>
       </c>
       <c r="O81">
-        <v>-53.25927778006827</v>
+        <v>-45.66713470605374</v>
       </c>
       <c r="P81">
-        <v>-161.7106744862801</v>
+        <v>-138.6587175602946</v>
       </c>
       <c r="Q81">
-        <v>-16.5106744862801</v>
+        <v>6.541282439705356</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2197098406392326</v>
+        <v>0.2181934853109194</v>
       </c>
       <c r="T81">
-        <v>3.192342064096544</v>
+        <v>3.165811460378201</v>
       </c>
       <c r="U81">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V81">
-        <v>0.1314071247516403</v>
+        <v>0.1408349152968276</v>
       </c>
       <c r="W81">
-        <v>0.1946291712146866</v>
+        <v>0.1796291712146866</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5303974164270387</v>
+        <v>0.56845072409383</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,13 +7969,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2016788528448087</v>
+        <v>0.189360418225863</v>
       </c>
       <c r="C82">
-        <v>-936.8628529278078</v>
+        <v>-866.3641656609759</v>
       </c>
       <c r="D82">
-        <v>824.0371470721924</v>
+        <v>894.5358343390243</v>
       </c>
       <c r="E82">
         <v>-173.3999999999996</v>
@@ -8002,37 +8002,37 @@
         <v>242.8</v>
       </c>
       <c r="M82">
-        <v>463.5645086241503</v>
+        <v>432.5325086241502</v>
       </c>
       <c r="N82">
-        <v>-220.7645086241503</v>
+        <v>-189.7325086241502</v>
       </c>
       <c r="O82">
-        <v>-54.69489184342378</v>
+        <v>-47.00664569252299</v>
       </c>
       <c r="P82">
-        <v>-166.0696167807265</v>
+        <v>-142.7258629316272</v>
       </c>
       <c r="Q82">
-        <v>-20.86961678072649</v>
+        <v>2.474137068372755</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2284053326711942</v>
+        <v>0.2268131595764654</v>
       </c>
       <c r="T82">
-        <v>3.35195916730137</v>
+        <v>3.324102033397111</v>
       </c>
       <c r="U82">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V82">
-        <v>0.1297645356922448</v>
+        <v>0.1390744788556172</v>
       </c>
       <c r="W82">
-        <v>0.1949972328882124</v>
+        <v>0.1799972328882124</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5237674487217008</v>
+        <v>0.5613450900426572</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,13 +8051,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2034615938957762</v>
+        <v>0.1909931592768304</v>
       </c>
       <c r="C83">
-        <v>-972.0405619101161</v>
+        <v>-902.2834920477105</v>
       </c>
       <c r="D83">
-        <v>814.7194380898843</v>
+        <v>884.4765079522898</v>
       </c>
       <c r="E83">
         <v>-147.5399999999995</v>
@@ -8084,37 +8084,37 @@
         <v>242.8</v>
       </c>
       <c r="M83">
-        <v>469.3590649819522</v>
+        <v>437.9391649819522</v>
       </c>
       <c r="N83">
-        <v>-226.5590649819522</v>
+        <v>-195.1391649819521</v>
       </c>
       <c r="O83">
-        <v>-56.1305059067793</v>
+        <v>-48.34615667899224</v>
       </c>
       <c r="P83">
-        <v>-170.4285590751729</v>
+        <v>-146.7930083029599</v>
       </c>
       <c r="Q83">
-        <v>-25.22855907517291</v>
+        <v>-1.59300830295993</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2380161396538886</v>
+        <v>0.2363401679752267</v>
       </c>
       <c r="T83">
-        <v>3.528378070843548</v>
+        <v>3.499054771996959</v>
       </c>
       <c r="U83">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V83">
-        <v>0.1281625043874023</v>
+        <v>0.1373575099808566</v>
       </c>
       <c r="W83">
-        <v>0.1953562066191819</v>
+        <v>0.1803562066191819</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5173011839226673</v>
+        <v>0.5544149037458341</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2052443349467437</v>
+        <v>0.1926259003277979</v>
       </c>
       <c r="C84">
-        <v>-1007.009908992213</v>
+        <v>-937.9790939403326</v>
       </c>
       <c r="D84">
-        <v>805.6100910077874</v>
+        <v>874.6409060596674</v>
       </c>
       <c r="E84">
         <v>-121.6799999999998</v>
@@ -8166,37 +8166,37 @@
         <v>242.8</v>
       </c>
       <c r="M84">
-        <v>475.153621339754</v>
+        <v>443.345821339754</v>
       </c>
       <c r="N84">
-        <v>-232.353621339754</v>
+        <v>-200.545821339754</v>
       </c>
       <c r="O84">
-        <v>-57.56611997013478</v>
+        <v>-49.68566766546147</v>
       </c>
       <c r="P84">
-        <v>-174.7875013696192</v>
+        <v>-150.8601536742925</v>
       </c>
       <c r="Q84">
-        <v>-29.58750136961925</v>
+        <v>-5.660153674292502</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2486948140791046</v>
+        <v>0.2469257328627393</v>
       </c>
       <c r="T84">
-        <v>3.7243990747793</v>
+        <v>3.693446703774568</v>
       </c>
       <c r="U84">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V84">
-        <v>0.1265995470168242</v>
+        <v>0.1356824183957241</v>
       </c>
       <c r="W84">
-        <v>0.1957064248932986</v>
+        <v>0.1807064248932986</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5109926328992203</v>
+        <v>0.5476537463830802</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,13 +8215,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2070270759977111</v>
+        <v>0.1942586413787654</v>
       </c>
       <c r="C85">
-        <v>-1041.777805953227</v>
+        <v>-973.4583528727621</v>
       </c>
       <c r="D85">
-        <v>796.7021940467732</v>
+        <v>865.0216471272381</v>
       </c>
       <c r="E85">
         <v>-95.81999999999971</v>
@@ -8248,37 +8248,37 @@
         <v>242.8</v>
       </c>
       <c r="M85">
-        <v>480.9481776975559</v>
+        <v>448.7524776975559</v>
       </c>
       <c r="N85">
-        <v>-238.1481776975559</v>
+        <v>-205.9524776975559</v>
       </c>
       <c r="O85">
-        <v>-59.00173403349028</v>
+        <v>-51.02517865193072</v>
       </c>
       <c r="P85">
-        <v>-179.1464436640656</v>
+        <v>-154.9272990456251</v>
       </c>
       <c r="Q85">
-        <v>-33.94644366406561</v>
+        <v>-9.727299045625159</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2606298031425814</v>
+        <v>0.2587566583252535</v>
       </c>
       <c r="T85">
-        <v>3.94348137329573</v>
+        <v>3.910708274584838</v>
       </c>
       <c r="U85">
-        <v>0.224074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V85">
-        <v>0.1250742512696336</v>
+        <v>0.1340476904632456</v>
       </c>
       <c r="W85">
-        <v>0.1960482041728582</v>
+        <v>0.1810482041728582</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5048360951534465</v>
+        <v>0.5410555084748503</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,13 +8297,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2345093348867412</v>
+        <v>0.1958913824297329</v>
       </c>
       <c r="C86">
-        <v>-1183.663735287314</v>
+        <v>-1008.728329184369</v>
       </c>
       <c r="D86">
-        <v>680.6762647126857</v>
+        <v>855.6116708156312</v>
       </c>
       <c r="E86">
         <v>-69.96000000000004</v>
@@ -8330,45 +8330,45 @@
         <v>242.8</v>
       </c>
       <c r="M86">
-        <v>551.9099340553577</v>
+        <v>454.1591340553577</v>
       </c>
       <c r="N86">
-        <v>-309.1099340553577</v>
+        <v>-211.3591340553577</v>
       </c>
       <c r="O86">
-        <v>-76.58266501373741</v>
+        <v>-52.36468963839994</v>
       </c>
       <c r="P86">
-        <v>-232.5272690416202</v>
+        <v>-158.9944444169577</v>
       </c>
       <c r="Q86">
-        <v>-87.32726904162024</v>
+        <v>-13.79444441695776</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2771786523268844</v>
+        <v>0.2720664494705817</v>
       </c>
       <c r="T86">
-        <v>4.247257095067754</v>
+        <v>4.155127541746388</v>
       </c>
       <c r="U86">
-        <v>0.254074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V86">
-        <v>0.1089928437834259</v>
+        <v>0.1324518846243974</v>
       </c>
       <c r="W86">
-        <v>0.2263818458505235</v>
+        <v>0.1813818458505236</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.4399268522237665</v>
+        <v>0.5346143714691973</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,13 +8379,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2365920759377088</v>
+        <v>0.1975241234807003</v>
       </c>
       <c r="C87">
-        <v>-1216.954192720983</v>
+        <v>-1043.795779302248</v>
       </c>
       <c r="D87">
-        <v>673.2458072790173</v>
+        <v>846.4042206977516</v>
       </c>
       <c r="E87">
         <v>-44.09999999999991</v>
@@ -8412,45 +8412,45 @@
         <v>242.8</v>
       </c>
       <c r="M87">
-        <v>558.4802904131595</v>
+        <v>459.5657904131596</v>
       </c>
       <c r="N87">
-        <v>-315.6802904131595</v>
+        <v>-216.7657904131596</v>
       </c>
       <c r="O87">
-        <v>-78.21048523086543</v>
+        <v>-53.70420062486918</v>
       </c>
       <c r="P87">
-        <v>-237.4698051822941</v>
+        <v>-163.0615897882904</v>
       </c>
       <c r="Q87">
-        <v>-92.26980518229411</v>
+        <v>-17.86158978829039</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2926038958153435</v>
+        <v>0.2871508794352871</v>
       </c>
       <c r="T87">
-        <v>4.530407568072271</v>
+        <v>4.43213604452948</v>
       </c>
       <c r="U87">
-        <v>0.254074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V87">
-        <v>0.1077105750330326</v>
+        <v>0.130893627158228</v>
       </c>
       <c r="W87">
-        <v>0.2267076371357732</v>
+        <v>0.1817076371357732</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.4347512421976045</v>
+        <v>0.5283247906283833</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,13 +8461,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2386748169886762</v>
+        <v>0.1991568645316678</v>
       </c>
       <c r="C88">
-        <v>-1250.084175926173</v>
+        <v>-1078.667171919499</v>
       </c>
       <c r="D88">
-        <v>665.9758240738275</v>
+        <v>837.3928280805012</v>
       </c>
       <c r="E88">
         <v>-18.23999999999978</v>
@@ -8494,45 +8494,45 @@
         <v>242.8</v>
       </c>
       <c r="M88">
-        <v>565.0506467709614</v>
+        <v>464.9724467709615</v>
       </c>
       <c r="N88">
-        <v>-322.2506467709614</v>
+        <v>-222.1724467709615</v>
       </c>
       <c r="O88">
-        <v>-79.83830544799345</v>
+        <v>-55.04371161133844</v>
       </c>
       <c r="P88">
-        <v>-242.412341322968</v>
+        <v>-167.128735159623</v>
       </c>
       <c r="Q88">
-        <v>-97.21234132296797</v>
+        <v>-21.92873515962305</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3102327455164394</v>
+        <v>0.3043902279663791</v>
       </c>
       <c r="T88">
-        <v>4.854008108648862</v>
+        <v>4.748717190567301</v>
       </c>
       <c r="U88">
-        <v>0.254074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V88">
-        <v>0.1064581264861369</v>
+        <v>0.1293716082377835</v>
       </c>
       <c r="W88">
-        <v>0.2270258518795055</v>
+        <v>0.1820258518795055</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.4296959951953068</v>
+        <v>0.5221814791094486</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,13 +8543,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2407575580396437</v>
+        <v>0.2007896055826353</v>
       </c>
       <c r="C89">
-        <v>-1283.058827964789</v>
+        <v>-1113.34870315092</v>
       </c>
       <c r="D89">
-        <v>658.8611720352109</v>
+        <v>828.5712968490805</v>
       </c>
       <c r="E89">
         <v>7.620000000000346</v>
@@ -8576,45 +8576,45 @@
         <v>242.8</v>
       </c>
       <c r="M89">
-        <v>571.6210031287634</v>
+        <v>470.3791031287634</v>
       </c>
       <c r="N89">
-        <v>-328.8210031287634</v>
+        <v>-227.5791031287634</v>
       </c>
       <c r="O89">
-        <v>-81.46612566512151</v>
+        <v>-56.38322259780769</v>
       </c>
       <c r="P89">
-        <v>-247.3548774636419</v>
+        <v>-171.1958805309557</v>
       </c>
       <c r="Q89">
-        <v>-102.1548774636419</v>
+        <v>-25.9958805309557</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3305737259407809</v>
+        <v>0.3242817839637928</v>
       </c>
       <c r="T89">
-        <v>5.227393347775697</v>
+        <v>5.114003128303247</v>
       </c>
       <c r="U89">
-        <v>0.254074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V89">
-        <v>0.1052344698598594</v>
+        <v>0.1278845782580388</v>
       </c>
       <c r="W89">
-        <v>0.2273367513417726</v>
+        <v>0.1823367513417726</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.4247569607677745</v>
+        <v>0.5161793931426732</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,13 +8625,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2428402990906112</v>
+        <v>0.2024223466336027</v>
       </c>
       <c r="C90">
-        <v>-1315.88307444746</v>
+        <v>-1147.846310740746</v>
       </c>
       <c r="D90">
-        <v>651.8969255525396</v>
+        <v>819.933689259254</v>
       </c>
       <c r="E90">
         <v>33.48000000000002</v>
@@ -8658,45 +8658,45 @@
         <v>242.8</v>
       </c>
       <c r="M90">
-        <v>578.1913594865651</v>
+        <v>475.7857594865652</v>
       </c>
       <c r="N90">
-        <v>-335.3913594865651</v>
+        <v>-232.9857594865652</v>
       </c>
       <c r="O90">
-        <v>-83.0939458822495</v>
+        <v>-57.72273358427692</v>
       </c>
       <c r="P90">
-        <v>-252.2974136043156</v>
+        <v>-175.2630259022883</v>
       </c>
       <c r="Q90">
-        <v>-107.0974136043156</v>
+        <v>-30.0630259022883</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3543048697691794</v>
+        <v>0.3474885992941089</v>
       </c>
       <c r="T90">
-        <v>5.66300946009034</v>
+        <v>5.540170055661851</v>
       </c>
       <c r="U90">
-        <v>0.254074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V90">
-        <v>0.104038623611452</v>
+        <v>0.1264313444141975</v>
       </c>
       <c r="W90">
-        <v>0.22764058490717</v>
+        <v>0.1826405849071701</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.4199301771226862</v>
+        <v>0.5103137182205975</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2449230401415786</v>
+        <v>0.2040550876845702</v>
       </c>
       <c r="C91">
-        <v>-1348.56163490577</v>
+        <v>-1182.165687390886</v>
       </c>
       <c r="D91">
-        <v>645.0783650942301</v>
+        <v>811.4743126091136</v>
       </c>
       <c r="E91">
         <v>59.34000000000015</v>
@@ -8740,45 +8740,45 @@
         <v>242.8</v>
       </c>
       <c r="M91">
-        <v>584.761715844367</v>
+        <v>481.1924158443671</v>
       </c>
       <c r="N91">
-        <v>-341.961715844367</v>
+        <v>-238.3924158443671</v>
       </c>
       <c r="O91">
-        <v>-84.72176609937752</v>
+        <v>-59.06224457074616</v>
       </c>
       <c r="P91">
-        <v>-257.2399497449895</v>
+        <v>-179.3301712736209</v>
       </c>
       <c r="Q91">
-        <v>-112.0399497449895</v>
+        <v>-34.13017127362093</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3823507670209229</v>
+        <v>0.3749148355935734</v>
       </c>
       <c r="T91">
-        <v>6.177828501916733</v>
+        <v>6.043821878903837</v>
       </c>
       <c r="U91">
-        <v>0.254074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V91">
-        <v>0.1028696503124469</v>
+        <v>0.1250107675106672</v>
       </c>
       <c r="W91">
-        <v>0.2279375907519968</v>
+        <v>0.1829375907519968</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.4152118605258021</v>
+        <v>0.504579856218119</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,13 +8789,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2470057811925461</v>
+        <v>0.2378377323925509</v>
       </c>
       <c r="C92">
-        <v>-1381.099033458186</v>
+        <v>-1350.777572923929</v>
       </c>
       <c r="D92">
-        <v>638.4009665418146</v>
+        <v>668.7224270760707</v>
       </c>
       <c r="E92">
         <v>85.20000000000027</v>
@@ -8822,37 +8822,37 @@
         <v>242.8</v>
       </c>
       <c r="M92">
-        <v>591.332072202169</v>
+        <v>568.058072202169</v>
       </c>
       <c r="N92">
-        <v>-348.532072202169</v>
+        <v>-325.258072202169</v>
       </c>
       <c r="O92">
-        <v>-86.34958631650557</v>
+        <v>-80.58340170332998</v>
       </c>
       <c r="P92">
-        <v>-262.1824858856634</v>
+        <v>-244.674670498839</v>
       </c>
       <c r="Q92">
-        <v>-116.9824858856634</v>
+        <v>-99.47467049883903</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4160058437230152</v>
+        <v>0.4143253557230632</v>
       </c>
       <c r="T92">
-        <v>6.795611352108408</v>
+        <v>6.767551525998002</v>
       </c>
       <c r="U92">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V92">
-        <v>0.1017266541978641</v>
+        <v>0.1058945135517903</v>
       </c>
       <c r="W92">
-        <v>0.2282279964669384</v>
+        <v>0.2182279964669384</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4105983954088486</v>
+        <v>0.4274210892888936</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,13 +8871,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2490885222435135</v>
+        <v>0.2398204734435184</v>
       </c>
       <c r="C93">
-        <v>-1413.499608820336</v>
+        <v>-1383.471405376422</v>
       </c>
       <c r="D93">
-        <v>631.8603911796641</v>
+        <v>661.8885946235778</v>
       </c>
       <c r="E93">
         <v>111.0600000000004</v>
@@ -8904,37 +8904,37 @@
         <v>242.8</v>
       </c>
       <c r="M93">
-        <v>597.9024285599709</v>
+        <v>574.369828559971</v>
       </c>
       <c r="N93">
-        <v>-355.1024285599709</v>
+        <v>-331.569828559971</v>
       </c>
       <c r="O93">
-        <v>-87.97740653363358</v>
+        <v>-82.14715320253386</v>
       </c>
       <c r="P93">
-        <v>-267.1250220263373</v>
+        <v>-249.4226753574371</v>
       </c>
       <c r="Q93">
-        <v>-121.9250220263373</v>
+        <v>-104.2226753574371</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4571398263589059</v>
+        <v>0.4552726174700703</v>
       </c>
       <c r="T93">
-        <v>7.550679280120455</v>
+        <v>7.519501695553337</v>
       </c>
       <c r="U93">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V93">
-        <v>0.1006087788770085</v>
+        <v>0.1047308375786937</v>
       </c>
       <c r="W93">
-        <v>0.2285120196386946</v>
+        <v>0.2185120196386946</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4060863251296305</v>
+        <v>0.4227241542417628</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,13 +8953,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.251171263294481</v>
+        <v>0.2418032144944859</v>
       </c>
       <c r="C94">
-        <v>-1445.767523706185</v>
+        <v>-1416.026977646051</v>
       </c>
       <c r="D94">
-        <v>625.4524762938153</v>
+        <v>655.1930223539492</v>
       </c>
       <c r="E94">
         <v>136.9200000000001</v>
@@ -8986,37 +8986,37 @@
         <v>242.8</v>
       </c>
       <c r="M94">
-        <v>604.4727849177726</v>
+        <v>580.6815849177727</v>
       </c>
       <c r="N94">
-        <v>-361.6727849177726</v>
+        <v>-337.8815849177727</v>
       </c>
       <c r="O94">
-        <v>-89.60522675076157</v>
+        <v>-83.71090470173768</v>
       </c>
       <c r="P94">
-        <v>-272.067558167011</v>
+        <v>-254.1706802160351</v>
       </c>
       <c r="Q94">
-        <v>-126.8675581670111</v>
+        <v>-108.9706802160351</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5085573046537691</v>
+        <v>0.5064566946538291</v>
       </c>
       <c r="T94">
-        <v>8.494514190135513</v>
+        <v>8.459439407497506</v>
       </c>
       <c r="U94">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V94">
-        <v>0.09951520519356276</v>
+        <v>0.1035924589093601</v>
       </c>
       <c r="W94">
-        <v>0.2287898683936734</v>
+        <v>0.2187898683936734</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4016723433347433</v>
+        <v>0.4181293264782654</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,13 +9035,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2532540043454485</v>
+        <v>0.2437859555454533</v>
       </c>
       <c r="C95">
-        <v>-1477.906773662899</v>
+        <v>-1448.448443575034</v>
       </c>
       <c r="D95">
-        <v>619.1732263371008</v>
+        <v>648.6315564249663</v>
       </c>
       <c r="E95">
         <v>162.7800000000002</v>
@@ -9068,37 +9068,37 @@
         <v>242.8</v>
       </c>
       <c r="M95">
-        <v>611.0431412755746</v>
+        <v>586.9933412755746</v>
       </c>
       <c r="N95">
-        <v>-368.2431412755746</v>
+        <v>-344.1933412755746</v>
       </c>
       <c r="O95">
-        <v>-91.23304696788963</v>
+        <v>-85.27465620094152</v>
       </c>
       <c r="P95">
-        <v>-277.010094307685</v>
+        <v>-258.9186850746331</v>
       </c>
       <c r="Q95">
-        <v>-131.810094307685</v>
+        <v>-113.7186850746331</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5746654910328791</v>
+        <v>0.5722647938900907</v>
       </c>
       <c r="T95">
-        <v>9.708016217297731</v>
+        <v>9.667930751425724</v>
       </c>
       <c r="U95">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V95">
-        <v>0.09844514922373948</v>
+        <v>0.1024785615017326</v>
       </c>
       <c r="W95">
-        <v>0.2290617419066097</v>
+        <v>0.2190617419066097</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3973532858795309</v>
+        <v>0.4136333122150583</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,13 +9117,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.255336745396416</v>
+        <v>0.2457686965964208</v>
       </c>
       <c r="C96">
-        <v>-1509.921195378826</v>
+        <v>-1480.739792259935</v>
       </c>
       <c r="D96">
-        <v>613.0188046211744</v>
+        <v>642.2002077400655</v>
       </c>
       <c r="E96">
         <v>188.6400000000003</v>
@@ -9150,37 +9150,37 @@
         <v>242.8</v>
       </c>
       <c r="M96">
-        <v>617.6134976333765</v>
+        <v>593.3050976333766</v>
       </c>
       <c r="N96">
-        <v>-374.8134976333765</v>
+        <v>-350.5050976333766</v>
       </c>
       <c r="O96">
-        <v>-92.86086718501765</v>
+        <v>-86.8384077001454</v>
       </c>
       <c r="P96">
-        <v>-281.9526304483588</v>
+        <v>-263.6666899332312</v>
       </c>
       <c r="Q96">
-        <v>-136.7526304483588</v>
+        <v>-118.4666899332312</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6628097395383591</v>
+        <v>0.6600089262051059</v>
       </c>
       <c r="T96">
-        <v>11.32601892018069</v>
+        <v>11.27925254333001</v>
       </c>
       <c r="U96">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V96">
-        <v>0.09739786040221034</v>
+        <v>0.1013883640389482</v>
       </c>
       <c r="W96">
-        <v>0.2293278308767175</v>
+        <v>0.2193278308767175</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3931261232637913</v>
+        <v>0.4092329578297916</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,13 +9199,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2574194864473834</v>
+        <v>0.2477514376473883</v>
       </c>
       <c r="C97">
-        <v>-1541.814474500864</v>
+        <v>-1512.904856138951</v>
       </c>
       <c r="D97">
-        <v>606.985525499136</v>
+        <v>635.8951438610488</v>
       </c>
       <c r="E97">
         <v>214.5000000000005</v>
@@ -9232,37 +9232,37 @@
         <v>242.8</v>
       </c>
       <c r="M97">
-        <v>624.1838539911784</v>
+        <v>599.6168539911785</v>
       </c>
       <c r="N97">
-        <v>-381.3838539911783</v>
+        <v>-356.8168539911784</v>
       </c>
       <c r="O97">
-        <v>-94.48868740214567</v>
+        <v>-88.40215919934924</v>
       </c>
       <c r="P97">
-        <v>-286.8951665890327</v>
+        <v>-268.4146947918292</v>
       </c>
       <c r="Q97">
-        <v>-141.6951665890327</v>
+        <v>-123.2146947918292</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7862116874460312</v>
+        <v>0.7828507114461274</v>
       </c>
       <c r="T97">
-        <v>13.59122270421683</v>
+        <v>13.53510305199602</v>
       </c>
       <c r="U97">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V97">
-        <v>0.0963726197663976</v>
+        <v>0.1003211181016961</v>
       </c>
       <c r="W97">
-        <v>0.2295883179737704</v>
+        <v>0.2195883179737705</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3889879535452251</v>
+        <v>0.4049252424842149</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,13 +9281,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2595022274983509</v>
+        <v>0.2497341786983557</v>
       </c>
       <c r="C98">
-        <v>-1573.590152994715</v>
+        <v>-1544.947318607437</v>
       </c>
       <c r="D98">
-        <v>601.0698470052846</v>
+        <v>629.7126813925624</v>
       </c>
       <c r="E98">
         <v>240.3600000000001</v>
@@ -9314,37 +9314,37 @@
         <v>242.8</v>
       </c>
       <c r="M98">
-        <v>630.7542103489802</v>
+        <v>605.9286103489802</v>
       </c>
       <c r="N98">
-        <v>-387.9542103489802</v>
+        <v>-363.1286103489802</v>
       </c>
       <c r="O98">
-        <v>-96.11650761927369</v>
+        <v>-89.96591069855306</v>
       </c>
       <c r="P98">
-        <v>-291.8377027297065</v>
+        <v>-273.1626996504272</v>
       </c>
       <c r="Q98">
-        <v>-146.6377027297065</v>
+        <v>-127.9626996504272</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.971314609307537</v>
+        <v>0.9671133893076572</v>
       </c>
       <c r="T98">
-        <v>16.989028380271</v>
+        <v>16.91887881499499</v>
       </c>
       <c r="U98">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V98">
-        <v>0.09536873831049762</v>
+        <v>0.09927610645480342</v>
       </c>
       <c r="W98">
-        <v>0.2298433782563015</v>
+        <v>0.2198433782563015</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3849359956957956</v>
+        <v>0.4007072712083377</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,13 +9363,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2615849685493184</v>
+        <v>0.2517169197493232</v>
       </c>
       <c r="C99">
-        <v>-1605.251636078884</v>
+        <v>-1576.87072119345</v>
       </c>
       <c r="D99">
-        <v>595.2683639211165</v>
+        <v>623.6492788065498</v>
       </c>
       <c r="E99">
         <v>266.2200000000003</v>
@@ -9396,37 +9396,37 @@
         <v>242.8</v>
       </c>
       <c r="M99">
-        <v>637.3245667067821</v>
+        <v>612.2403667067822</v>
       </c>
       <c r="N99">
-        <v>-394.5245667067821</v>
+        <v>-369.4403667067822</v>
       </c>
       <c r="O99">
-        <v>-97.74432783640171</v>
+        <v>-91.52966219775693</v>
       </c>
       <c r="P99">
-        <v>-296.7802388703803</v>
+        <v>-277.9107045090253</v>
       </c>
       <c r="Q99">
-        <v>-151.5802388703804</v>
+        <v>-132.7107045090253</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.279819479076716</v>
+        <v>1.27421785241021</v>
       </c>
       <c r="T99">
-        <v>22.65203784036134</v>
+        <v>22.55850508665998</v>
       </c>
       <c r="U99">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V99">
-        <v>0.09438555544131724</v>
+        <v>0.09825264143980544</v>
       </c>
       <c r="W99">
-        <v>0.2300931795639349</v>
+        <v>0.2200931795639349</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3809675833690348</v>
+        <v>0.3965762684123754</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,13 +9445,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2636677096002858</v>
+        <v>0.2536996608002907</v>
       </c>
       <c r="C100">
-        <v>-1636.80219876096</v>
+        <v>-1608.678470322699</v>
       </c>
       <c r="D100">
-        <v>589.5778012390404</v>
+        <v>617.7015296773011</v>
       </c>
       <c r="E100">
         <v>292.0799999999999</v>
@@ -9478,37 +9478,37 @@
         <v>242.8</v>
       </c>
       <c r="M100">
-        <v>643.894923064584</v>
+        <v>618.552123064584</v>
       </c>
       <c r="N100">
-        <v>-401.094923064584</v>
+        <v>-375.7521230645839</v>
       </c>
       <c r="O100">
-        <v>-99.37214805352973</v>
+        <v>-93.09341369696075</v>
       </c>
       <c r="P100">
-        <v>-301.7227750110542</v>
+        <v>-282.6587093676232</v>
       </c>
       <c r="Q100">
-        <v>-156.5227750110543</v>
+        <v>-137.4587093676232</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.896829218615074</v>
+        <v>1.888426778615315</v>
       </c>
       <c r="T100">
-        <v>33.978056760542</v>
+        <v>33.83775762998998</v>
       </c>
       <c r="U100">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V100">
-        <v>0.09342243752865075</v>
+        <v>0.09725006346592989</v>
       </c>
       <c r="W100">
-        <v>0.2303378828856983</v>
+        <v>0.2203378828856983</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3770801590489427</v>
+        <v>0.3925295717959227</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9527,13 +9527,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2657504506512533</v>
+        <v>0.2556824018512581</v>
       </c>
       <c r="C101">
-        <v>-1668.244992002546</v>
+        <v>-1640.373843700046</v>
       </c>
       <c r="D101">
-        <v>583.9950079974541</v>
+        <v>611.8661562999537</v>
       </c>
       <c r="E101">
         <v>317.9400000000001</v>
@@ -9560,37 +9560,37 @@
         <v>242.8</v>
       </c>
       <c r="M101">
-        <v>650.4652794223858</v>
+        <v>624.8638794223858</v>
       </c>
       <c r="N101">
-        <v>-407.6652794223858</v>
+        <v>-382.0638794223858</v>
       </c>
       <c r="O101">
-        <v>-100.9999682706577</v>
+        <v>-94.6571651961646</v>
       </c>
       <c r="P101">
-        <v>-306.6653111517281</v>
+        <v>-287.4067142262212</v>
       </c>
       <c r="Q101">
-        <v>-161.4653111517281</v>
+        <v>-142.2067142262212</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.747858437230148</v>
+        <v>3.731053557230629</v>
       </c>
       <c r="T101">
-        <v>67.95611352108401</v>
+        <v>67.67551525997996</v>
       </c>
       <c r="U101">
-        <v>0.254074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V101">
-        <v>0.09247877654351286</v>
+        <v>0.09626773959253666</v>
       </c>
       <c r="W101">
-        <v>0.2305776427060119</v>
+        <v>0.220577642706012</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3732712685534988</v>
+        <v>0.3885646266262669</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/gibraltar/gibraltar_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/gibraltar/gibraltar_hotel_gaming.xlsx
@@ -1269,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1406,22 +1406,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08653476487199627</v>
+        <v>0.08641646601664527</v>
       </c>
       <c r="C2">
-        <v>3460.488186019354</v>
+        <v>3443.810362864733</v>
       </c>
       <c r="D2">
-        <v>3152.588186019354</v>
+        <v>3161.770362864733</v>
       </c>
       <c r="E2">
-        <v>-2242.2</v>
+        <v>-2216.34</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25.86</v>
       </c>
       <c r="G2">
         <v>307.9</v>
@@ -1442,28 +1442,28 @@
         <v>242.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.514726357801877</v>
       </c>
       <c r="N2">
-        <v>242.8</v>
+        <v>241.2852736421981</v>
       </c>
       <c r="O2">
-        <v>60.15423322501647</v>
+        <v>59.77895644330603</v>
       </c>
       <c r="P2">
-        <v>182.6457667749835</v>
+        <v>181.5063171988921</v>
       </c>
       <c r="Q2">
-        <v>327.8457667749835</v>
+        <v>326.7063171988921</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08653476487199627</v>
+        <v>0.0868442864620502</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7537319187569904</v>
       </c>
       <c r="U2">
         <v>0.058574105096747</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>160.2929788271088</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1488,22 +1488,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08641646601664527</v>
+        <v>0.08629816716129425</v>
       </c>
       <c r="C3">
-        <v>3443.810362864733</v>
+        <v>3427.186183669166</v>
       </c>
       <c r="D3">
-        <v>3161.770362864733</v>
+        <v>3171.006183669165</v>
       </c>
       <c r="E3">
-        <v>-2216.34</v>
+        <v>-2190.48</v>
       </c>
       <c r="F3">
-        <v>25.86</v>
+        <v>51.72</v>
       </c>
       <c r="G3">
         <v>307.9</v>
@@ -1524,28 +1524,28 @@
         <v>242.8</v>
       </c>
       <c r="M3">
-        <v>1.514726357801877</v>
+        <v>3.029452715603755</v>
       </c>
       <c r="N3">
-        <v>241.2852736421981</v>
+        <v>239.7705472843963</v>
       </c>
       <c r="O3">
-        <v>59.77895644330603</v>
+        <v>59.4036796615956</v>
       </c>
       <c r="P3">
-        <v>181.5063171988921</v>
+        <v>180.3668676228007</v>
       </c>
       <c r="Q3">
-        <v>326.7063171988921</v>
+        <v>325.5668676228007</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0868442864620502</v>
+        <v>0.08716012481924809</v>
       </c>
       <c r="T3">
-        <v>0.7537319187569904</v>
+        <v>0.7595319331197188</v>
       </c>
       <c r="U3">
         <v>0.058574105096747</v>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>160.2929788271088</v>
+        <v>80.14648941355441</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1570,22 +1570,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08629816716129425</v>
+        <v>0.08617986830594325</v>
       </c>
       <c r="C4">
-        <v>3427.186183669166</v>
+        <v>3410.61611990662</v>
       </c>
       <c r="D4">
-        <v>3171.006183669165</v>
+        <v>3180.29611990662</v>
       </c>
       <c r="E4">
-        <v>-2190.48</v>
+        <v>-2164.62</v>
       </c>
       <c r="F4">
-        <v>51.72</v>
+        <v>77.58</v>
       </c>
       <c r="G4">
         <v>307.9</v>
@@ -1606,28 +1606,28 @@
         <v>242.8</v>
       </c>
       <c r="M4">
-        <v>3.029452715603755</v>
+        <v>4.544179073405632</v>
       </c>
       <c r="N4">
-        <v>239.7705472843963</v>
+        <v>238.2558209265944</v>
       </c>
       <c r="O4">
-        <v>59.4036796615956</v>
+        <v>59.02840287988516</v>
       </c>
       <c r="P4">
-        <v>180.3668676228007</v>
+        <v>179.2274180467092</v>
       </c>
       <c r="Q4">
-        <v>325.5668676228007</v>
+        <v>324.4274180467092</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08716012481924809</v>
+        <v>0.08748247530752223</v>
       </c>
       <c r="T4">
-        <v>0.7595319331197188</v>
+        <v>0.7654515354074517</v>
       </c>
       <c r="U4">
         <v>0.058574105096747</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>80.14648941355441</v>
+        <v>53.43099294236961</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1652,22 +1652,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08617986830594325</v>
+        <v>0.08606156945059222</v>
       </c>
       <c r="C5">
-        <v>3410.61611990662</v>
+        <v>3394.100648592317</v>
       </c>
       <c r="D5">
-        <v>3180.29611990662</v>
+        <v>3189.640648592317</v>
       </c>
       <c r="E5">
-        <v>-2164.62</v>
+        <v>-2138.76</v>
       </c>
       <c r="F5">
-        <v>77.58</v>
+        <v>103.44</v>
       </c>
       <c r="G5">
         <v>307.9</v>
@@ -1688,28 +1688,28 @@
         <v>242.8</v>
       </c>
       <c r="M5">
-        <v>4.544179073405632</v>
+        <v>6.05890543120751</v>
       </c>
       <c r="N5">
-        <v>238.2558209265944</v>
+        <v>236.7410945687925</v>
       </c>
       <c r="O5">
-        <v>59.02840287988516</v>
+        <v>58.65312609817472</v>
       </c>
       <c r="P5">
-        <v>179.2274180467092</v>
+        <v>178.0879684706178</v>
       </c>
       <c r="Q5">
-        <v>324.4274180467092</v>
+        <v>323.2879684706178</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08748247530752223</v>
+        <v>0.08781154143096874</v>
       </c>
       <c r="T5">
-        <v>0.7654515354074517</v>
+        <v>0.7714944627428457</v>
       </c>
       <c r="U5">
         <v>0.058574105096747</v>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.43099294236961</v>
+        <v>40.07324470677721</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1734,22 +1734,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08606156945059222</v>
+        <v>0.08594327059524122</v>
       </c>
       <c r="C6">
-        <v>3394.100648592317</v>
+        <v>3377.640252364368</v>
       </c>
       <c r="D6">
-        <v>3189.640648592317</v>
+        <v>3199.040252364368</v>
       </c>
       <c r="E6">
-        <v>-2138.76</v>
+        <v>-2112.9</v>
       </c>
       <c r="F6">
-        <v>103.44</v>
+        <v>129.3</v>
       </c>
       <c r="G6">
         <v>307.9</v>
@@ -1770,28 +1770,28 @@
         <v>242.8</v>
       </c>
       <c r="M6">
-        <v>6.05890543120751</v>
+        <v>7.573631789009388</v>
       </c>
       <c r="N6">
-        <v>236.7410945687925</v>
+        <v>235.2263682109906</v>
       </c>
       <c r="O6">
-        <v>58.65312609817472</v>
+        <v>58.27784931646428</v>
       </c>
       <c r="P6">
-        <v>178.0879684706178</v>
+        <v>176.9485188945263</v>
       </c>
       <c r="Q6">
-        <v>323.2879684706178</v>
+        <v>322.1485188945263</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08781154143096874</v>
+        <v>0.08814753526227728</v>
       </c>
       <c r="T6">
-        <v>0.7714944627428457</v>
+        <v>0.7776646096010901</v>
       </c>
       <c r="U6">
         <v>0.058574105096747</v>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.07324470677721</v>
+        <v>32.05859576542176</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1816,22 +1816,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08594327059524122</v>
+        <v>0.08582497173989022</v>
       </c>
       <c r="C7">
-        <v>3377.640252364368</v>
+        <v>3361.23541956688</v>
       </c>
       <c r="D7">
-        <v>3199.040252364368</v>
+        <v>3208.49541956688</v>
       </c>
       <c r="E7">
-        <v>-2112.9</v>
+        <v>-2087.04</v>
       </c>
       <c r="F7">
-        <v>129.3</v>
+        <v>155.16</v>
       </c>
       <c r="G7">
         <v>307.9</v>
@@ -1852,28 +1852,28 @@
         <v>242.8</v>
       </c>
       <c r="M7">
-        <v>7.573631789009388</v>
+        <v>9.088358146811267</v>
       </c>
       <c r="N7">
-        <v>235.2263682109906</v>
+        <v>233.7116418531888</v>
       </c>
       <c r="O7">
-        <v>58.27784931646428</v>
+        <v>57.90257253475385</v>
       </c>
       <c r="P7">
-        <v>176.9485188945263</v>
+        <v>175.8090693184349</v>
       </c>
       <c r="Q7">
-        <v>322.1485188945263</v>
+        <v>321.0090693184349</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08814753526227728</v>
+        <v>0.08849067789850729</v>
       </c>
       <c r="T7">
-        <v>0.7776646096010901</v>
+        <v>0.7839660361797227</v>
       </c>
       <c r="U7">
         <v>0.058574105096747</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.05859576542176</v>
+        <v>26.7154964711848</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1898,22 +1898,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08582497173989022</v>
+        <v>0.0857066728845392</v>
       </c>
       <c r="C8">
-        <v>3361.23541956688</v>
+        <v>3344.886644334525</v>
       </c>
       <c r="D8">
-        <v>3208.49541956688</v>
+        <v>3218.006644334525</v>
       </c>
       <c r="E8">
-        <v>-2087.04</v>
+        <v>-2061.18</v>
       </c>
       <c r="F8">
-        <v>155.16</v>
+        <v>181.02</v>
       </c>
       <c r="G8">
         <v>307.9</v>
@@ -1934,28 +1934,28 @@
         <v>242.8</v>
       </c>
       <c r="M8">
-        <v>9.088358146811265</v>
+        <v>10.60308450461314</v>
       </c>
       <c r="N8">
-        <v>233.7116418531888</v>
+        <v>232.1969154953869</v>
       </c>
       <c r="O8">
-        <v>57.90257253475385</v>
+        <v>57.52729575304341</v>
       </c>
       <c r="P8">
-        <v>175.8090693184349</v>
+        <v>174.6696197423435</v>
       </c>
       <c r="Q8">
-        <v>321.0090693184349</v>
+        <v>319.8696197423434</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08849067789850729</v>
+        <v>0.08884119994626911</v>
       </c>
       <c r="T8">
-        <v>0.7839660361797227</v>
+        <v>0.7904029773084333</v>
       </c>
       <c r="U8">
         <v>0.058574105096747</v>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.7154964711848</v>
+        <v>22.89899697530126</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1980,22 +1980,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08570667288453919</v>
+        <v>0.0855883740291882</v>
       </c>
       <c r="C9">
-        <v>3344.886644334526</v>
+        <v>3328.59442667862</v>
       </c>
       <c r="D9">
-        <v>3218.006644334526</v>
+        <v>3227.57442667862</v>
       </c>
       <c r="E9">
-        <v>-2061.18</v>
+        <v>-2035.32</v>
       </c>
       <c r="F9">
-        <v>181.02</v>
+        <v>206.88</v>
       </c>
       <c r="G9">
         <v>307.9</v>
@@ -2016,28 +2016,28 @@
         <v>242.8</v>
       </c>
       <c r="M9">
-        <v>10.60308450461314</v>
+        <v>12.11781086241502</v>
       </c>
       <c r="N9">
-        <v>232.1969154953869</v>
+        <v>230.682189137585</v>
       </c>
       <c r="O9">
-        <v>57.52729575304341</v>
+        <v>57.15201897133298</v>
       </c>
       <c r="P9">
-        <v>174.6696197423435</v>
+        <v>173.530170166252</v>
       </c>
       <c r="Q9">
-        <v>319.8696197423434</v>
+        <v>318.730170166252</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08884119994626911</v>
+        <v>0.08919934203854751</v>
       </c>
       <c r="T9">
-        <v>0.7904029773084333</v>
+        <v>0.7969798519399423</v>
       </c>
       <c r="U9">
         <v>0.058574105096747</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.89899697530126</v>
+        <v>20.0366223533886</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2062,22 +2062,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0855883740291882</v>
+        <v>0.08547007517383719</v>
       </c>
       <c r="C10">
-        <v>3328.59442667862</v>
+        <v>3312.359272574756</v>
       </c>
       <c r="D10">
-        <v>3227.57442667862</v>
+        <v>3237.199272574755</v>
       </c>
       <c r="E10">
-        <v>-2035.32</v>
+        <v>-2009.46</v>
       </c>
       <c r="F10">
-        <v>206.88</v>
+        <v>232.74</v>
       </c>
       <c r="G10">
         <v>307.9</v>
@@ -2098,28 +2098,28 @@
         <v>242.8</v>
       </c>
       <c r="M10">
-        <v>12.11781086241502</v>
+        <v>13.6325372202169</v>
       </c>
       <c r="N10">
-        <v>230.682189137585</v>
+        <v>229.1674627797831</v>
       </c>
       <c r="O10">
-        <v>57.15201897133298</v>
+        <v>56.77674218962254</v>
       </c>
       <c r="P10">
-        <v>173.530170166252</v>
+        <v>172.3907205901606</v>
       </c>
       <c r="Q10">
-        <v>318.730170166252</v>
+        <v>317.5907205901606</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08919934203854751</v>
+        <v>0.08956535538560126</v>
       </c>
       <c r="T10">
-        <v>0.7969798519399423</v>
+        <v>0.803701273266649</v>
       </c>
       <c r="U10">
         <v>0.058574105096747</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.0366223533886</v>
+        <v>17.81033098078987</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2144,22 +2144,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08547007517383719</v>
+        <v>0.08535177631848619</v>
       </c>
       <c r="C11">
-        <v>3312.359272574756</v>
+        <v>3296.181694051985</v>
       </c>
       <c r="D11">
-        <v>3237.199272574755</v>
+        <v>3246.881694051985</v>
       </c>
       <c r="E11">
-        <v>-2009.46</v>
+        <v>-1983.6</v>
       </c>
       <c r="F11">
-        <v>232.74</v>
+        <v>258.6</v>
       </c>
       <c r="G11">
         <v>307.9</v>
@@ -2180,28 +2180,28 @@
         <v>242.8</v>
       </c>
       <c r="M11">
-        <v>13.6325372202169</v>
+        <v>15.14726357801877</v>
       </c>
       <c r="N11">
-        <v>229.1674627797831</v>
+        <v>227.6527364219812</v>
       </c>
       <c r="O11">
-        <v>56.77674218962254</v>
+        <v>56.40146540791211</v>
       </c>
       <c r="P11">
-        <v>172.3907205901606</v>
+        <v>171.2512710140691</v>
       </c>
       <c r="Q11">
-        <v>317.5907205901606</v>
+        <v>316.4512710140691</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08956535538560126</v>
+        <v>0.08993950236258953</v>
       </c>
       <c r="T11">
-        <v>0.803701273266649</v>
+        <v>0.8105720595117271</v>
       </c>
       <c r="U11">
         <v>0.058574105096747</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.81033098078987</v>
+        <v>16.02929788271089</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2226,22 +2226,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08535177631848619</v>
+        <v>0.0852334774631352</v>
       </c>
       <c r="C12">
-        <v>3296.181694051985</v>
+        <v>3280.06220928363</v>
       </c>
       <c r="D12">
-        <v>3246.881694051985</v>
+        <v>3256.62220928363</v>
       </c>
       <c r="E12">
-        <v>-1983.6</v>
+        <v>-1957.74</v>
       </c>
       <c r="F12">
-        <v>258.6</v>
+        <v>284.46</v>
       </c>
       <c r="G12">
         <v>307.9</v>
@@ -2262,28 +2262,28 @@
         <v>242.8</v>
       </c>
       <c r="M12">
-        <v>15.14726357801878</v>
+        <v>16.66198993582065</v>
       </c>
       <c r="N12">
-        <v>227.6527364219812</v>
+        <v>226.1380100641794</v>
       </c>
       <c r="O12">
-        <v>56.40146540791211</v>
+        <v>56.02618862620167</v>
       </c>
       <c r="P12">
-        <v>171.2512710140691</v>
+        <v>170.1118214379777</v>
       </c>
       <c r="Q12">
-        <v>316.4512710140691</v>
+        <v>315.3118214379776</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08993950236258953</v>
+        <v>0.0903220571368135</v>
       </c>
       <c r="T12">
-        <v>0.8105720595117271</v>
+        <v>0.8175972454477058</v>
       </c>
       <c r="U12">
         <v>0.058574105096747</v>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.02929788271088</v>
+        <v>14.57208898428262</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2308,22 +2308,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0852334774631352</v>
+        <v>0.08511517860778417</v>
       </c>
       <c r="C13">
-        <v>3280.06220928363</v>
+        <v>3264.001342679726</v>
       </c>
       <c r="D13">
-        <v>3256.62220928363</v>
+        <v>3266.421342679726</v>
       </c>
       <c r="E13">
-        <v>-1957.74</v>
+        <v>-1931.88</v>
       </c>
       <c r="F13">
-        <v>284.46</v>
+        <v>310.32</v>
       </c>
       <c r="G13">
         <v>307.9</v>
@@ -2344,28 +2344,28 @@
         <v>242.8</v>
       </c>
       <c r="M13">
-        <v>16.66198993582065</v>
+        <v>18.17671629362253</v>
       </c>
       <c r="N13">
-        <v>226.1380100641794</v>
+        <v>224.6232837063775</v>
       </c>
       <c r="O13">
-        <v>56.02618862620167</v>
+        <v>55.65091184449124</v>
       </c>
       <c r="P13">
-        <v>170.1118214379777</v>
+        <v>168.9723718618862</v>
       </c>
       <c r="Q13">
-        <v>315.3118214379776</v>
+        <v>314.1723718618862</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0903220571368135</v>
+        <v>0.09071330633772437</v>
       </c>
       <c r="T13">
-        <v>0.8175972454477058</v>
+        <v>0.8247820947004112</v>
       </c>
       <c r="U13">
         <v>0.058574105096747</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.57208898428262</v>
+        <v>13.3577482355924</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2390,22 +2390,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08511517860778417</v>
+        <v>0.08514356807418408</v>
       </c>
       <c r="C14">
-        <v>3264.001342679726</v>
+        <v>3235.78436380122</v>
       </c>
       <c r="D14">
-        <v>3266.421342679726</v>
+        <v>3264.064363801219</v>
       </c>
       <c r="E14">
-        <v>-1931.88</v>
+        <v>-1906.02</v>
       </c>
       <c r="F14">
-        <v>310.32</v>
+        <v>336.18</v>
       </c>
       <c r="G14">
         <v>307.9</v>
@@ -2426,45 +2426,45 @@
         <v>242.8</v>
       </c>
       <c r="M14">
-        <v>18.17671629362253</v>
+        <v>20.1957126514244</v>
       </c>
       <c r="N14">
-        <v>224.6232837063775</v>
+        <v>222.6042873485756</v>
       </c>
       <c r="O14">
-        <v>55.65091184449124</v>
+        <v>55.15070106282867</v>
       </c>
       <c r="P14">
-        <v>168.9723718618862</v>
+        <v>167.453586285747</v>
       </c>
       <c r="Q14">
-        <v>314.1723718618862</v>
+        <v>312.6535862857469</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09071330633772437</v>
+        <v>0.09111354977313893</v>
       </c>
       <c r="T14">
-        <v>0.8247820947004112</v>
+        <v>0.8321321129014547</v>
       </c>
       <c r="U14">
-        <v>0.058574105096747</v>
+        <v>0.060074105096747</v>
       </c>
       <c r="V14">
         <v>0.2477521961491617</v>
       </c>
       <c r="W14">
-        <v>0.04406224192155612</v>
+        <v>0.04519061362733237</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.3577482355924</v>
+        <v>12.02235366439893</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08514356807418408</v>
+        <v>0.08503655293589084</v>
       </c>
       <c r="C15">
-        <v>3235.78436380122</v>
+        <v>3218.826886402044</v>
       </c>
       <c r="D15">
-        <v>3264.064363801219</v>
+        <v>3272.966886402044</v>
       </c>
       <c r="E15">
-        <v>-1906.02</v>
+        <v>-1880.16</v>
       </c>
       <c r="F15">
-        <v>336.18</v>
+        <v>362.04</v>
       </c>
       <c r="G15">
         <v>307.9</v>
@@ -2508,28 +2508,28 @@
         <v>242.8</v>
       </c>
       <c r="M15">
-        <v>20.1957126514244</v>
+        <v>21.74922900922628</v>
       </c>
       <c r="N15">
-        <v>222.6042873485756</v>
+        <v>221.0507709907737</v>
       </c>
       <c r="O15">
-        <v>55.15070106282867</v>
+        <v>54.7658139734296</v>
       </c>
       <c r="P15">
-        <v>167.453586285747</v>
+        <v>166.2849570173441</v>
       </c>
       <c r="Q15">
-        <v>312.6535862857469</v>
+        <v>311.4849570173441</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09111354977313893</v>
+        <v>0.09152310119542362</v>
       </c>
       <c r="T15">
-        <v>0.8321321129014547</v>
+        <v>0.8396530617583365</v>
       </c>
       <c r="U15">
         <v>0.060074105096747</v>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.02235366439893</v>
+        <v>11.16361411694186</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2554,22 +2554,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08503655293589084</v>
+        <v>0.0849295377975976</v>
       </c>
       <c r="C16">
-        <v>3218.826886402044</v>
+        <v>3201.918103914227</v>
       </c>
       <c r="D16">
-        <v>3272.966886402044</v>
+        <v>3281.918103914227</v>
       </c>
       <c r="E16">
-        <v>-1880.16</v>
+        <v>-1854.3</v>
       </c>
       <c r="F16">
-        <v>362.04</v>
+        <v>387.9</v>
       </c>
       <c r="G16">
         <v>307.9</v>
@@ -2590,28 +2590,28 @@
         <v>242.8</v>
       </c>
       <c r="M16">
-        <v>21.74922900922628</v>
+        <v>23.30274536702816</v>
       </c>
       <c r="N16">
-        <v>221.0507709907737</v>
+        <v>219.4972546329718</v>
       </c>
       <c r="O16">
-        <v>54.7658139734296</v>
+        <v>54.38092688403054</v>
       </c>
       <c r="P16">
-        <v>166.2849570173441</v>
+        <v>165.1163277489413</v>
       </c>
       <c r="Q16">
-        <v>311.4849570173441</v>
+        <v>310.3163277489413</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09152310119542362</v>
+        <v>0.09194228912176204</v>
       </c>
       <c r="T16">
-        <v>0.8396530617583365</v>
+        <v>0.8473509741177331</v>
       </c>
       <c r="U16">
         <v>0.060074105096747</v>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.16361411694186</v>
+        <v>10.4193731758124</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2636,22 +2636,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0849295377975976</v>
+        <v>0.08502713406195178</v>
       </c>
       <c r="C17">
-        <v>3201.918103914227</v>
+        <v>3167.892762384241</v>
       </c>
       <c r="D17">
-        <v>3281.918103914227</v>
+        <v>3273.752762384241</v>
       </c>
       <c r="E17">
-        <v>-1854.3</v>
+        <v>-1828.44</v>
       </c>
       <c r="F17">
-        <v>387.9</v>
+        <v>413.76</v>
       </c>
       <c r="G17">
         <v>307.9</v>
@@ -2672,45 +2672,45 @@
         <v>242.8</v>
       </c>
       <c r="M17">
-        <v>23.30274536702816</v>
+        <v>25.55965372483004</v>
       </c>
       <c r="N17">
-        <v>219.4972546329718</v>
+        <v>217.24034627517</v>
       </c>
       <c r="O17">
-        <v>54.38092688403054</v>
+        <v>53.82177288187772</v>
       </c>
       <c r="P17">
-        <v>165.1163277489413</v>
+        <v>163.4185733932923</v>
       </c>
       <c r="Q17">
-        <v>310.3163277489413</v>
+        <v>308.6185733932923</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09194228912176204</v>
+        <v>0.09237145771301331</v>
       </c>
       <c r="T17">
-        <v>0.8473509741177331</v>
+        <v>0.8552321701047344</v>
       </c>
       <c r="U17">
-        <v>0.060074105096747</v>
+        <v>0.061774105096747</v>
       </c>
       <c r="V17">
         <v>0.2477521961491617</v>
       </c>
       <c r="W17">
-        <v>0.04519061362733237</v>
+        <v>0.0464694348938788</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.4193731758124</v>
+        <v>9.499346220177111</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2718,22 +2718,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08502713406195178</v>
+        <v>0.084932907136324</v>
       </c>
       <c r="C18">
-        <v>3167.892762384241</v>
+        <v>3149.915531149422</v>
       </c>
       <c r="D18">
-        <v>3273.752762384241</v>
+        <v>3281.635531149422</v>
       </c>
       <c r="E18">
-        <v>-1828.44</v>
+        <v>-1802.58</v>
       </c>
       <c r="F18">
-        <v>413.76</v>
+        <v>439.62</v>
       </c>
       <c r="G18">
         <v>307.9</v>
@@ -2754,28 +2754,28 @@
         <v>242.8</v>
       </c>
       <c r="M18">
-        <v>25.55965372483004</v>
+        <v>27.15713208263191</v>
       </c>
       <c r="N18">
-        <v>217.24034627517</v>
+        <v>215.6428679173681</v>
       </c>
       <c r="O18">
-        <v>53.82177288187772</v>
+        <v>53.42599411043155</v>
       </c>
       <c r="P18">
-        <v>163.4185733932923</v>
+        <v>162.2168738069365</v>
       </c>
       <c r="Q18">
-        <v>308.6185733932923</v>
+        <v>307.4168738069366</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09237145771301331</v>
+        <v>0.09281096771610194</v>
       </c>
       <c r="T18">
-        <v>0.8552321701047344</v>
+        <v>0.863303274428772</v>
       </c>
       <c r="U18">
         <v>0.061774105096747</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.499346220177111</v>
+        <v>8.940561148401986</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2800,22 +2800,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.084932907136324</v>
+        <v>0.08483868021069621</v>
       </c>
       <c r="C19">
-        <v>3149.915531149422</v>
+        <v>3131.976352894989</v>
       </c>
       <c r="D19">
-        <v>3281.635531149422</v>
+        <v>3289.556352894989</v>
       </c>
       <c r="E19">
-        <v>-1802.58</v>
+        <v>-1776.72</v>
       </c>
       <c r="F19">
-        <v>439.62</v>
+        <v>465.4800000000001</v>
       </c>
       <c r="G19">
         <v>307.9</v>
@@ -2836,28 +2836,28 @@
         <v>242.8</v>
       </c>
       <c r="M19">
-        <v>27.15713208263191</v>
+        <v>28.7546104404338</v>
       </c>
       <c r="N19">
-        <v>215.6428679173681</v>
+        <v>214.0453895595662</v>
       </c>
       <c r="O19">
-        <v>53.42599411043155</v>
+        <v>53.03021533898538</v>
       </c>
       <c r="P19">
-        <v>162.2168738069365</v>
+        <v>161.0151742205808</v>
       </c>
       <c r="Q19">
-        <v>307.4168738069366</v>
+        <v>306.2151742205808</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09281096771610194</v>
+        <v>0.09326119747536346</v>
       </c>
       <c r="T19">
-        <v>0.863303274428772</v>
+        <v>0.8715712349558346</v>
       </c>
       <c r="U19">
         <v>0.061774105096747</v>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.940561148401986</v>
+        <v>8.443863306824095</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2882,22 +2882,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08483868021069624</v>
+        <v>0.08474445328506845</v>
       </c>
       <c r="C20">
-        <v>3131.976352894987</v>
+        <v>3114.075503830904</v>
       </c>
       <c r="D20">
-        <v>3289.556352894987</v>
+        <v>3297.515503830904</v>
       </c>
       <c r="E20">
-        <v>-1776.72</v>
+        <v>-1750.86</v>
       </c>
       <c r="F20">
-        <v>465.48</v>
+        <v>491.34</v>
       </c>
       <c r="G20">
         <v>307.9</v>
@@ -2918,28 +2918,28 @@
         <v>242.8</v>
       </c>
       <c r="M20">
-        <v>28.75461044043379</v>
+        <v>30.35208879823567</v>
       </c>
       <c r="N20">
-        <v>214.0453895595662</v>
+        <v>212.4479112017643</v>
       </c>
       <c r="O20">
-        <v>53.03021533898538</v>
+        <v>52.6344365675392</v>
       </c>
       <c r="P20">
-        <v>161.0151742205808</v>
+        <v>159.8134746342251</v>
       </c>
       <c r="Q20">
-        <v>306.2151742205808</v>
+        <v>305.0134746342251</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09326119747536346</v>
+        <v>0.09372254401880428</v>
       </c>
       <c r="T20">
-        <v>0.8715712349558346</v>
+        <v>0.880043342656405</v>
       </c>
       <c r="U20">
         <v>0.061774105096747</v>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.443863306824099</v>
+        <v>7.999449448570197</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2964,22 +2964,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08474445328506845</v>
+        <v>0.08465022635944065</v>
       </c>
       <c r="C21">
-        <v>3114.075503830904</v>
+        <v>3096.213262846804</v>
       </c>
       <c r="D21">
-        <v>3297.515503830904</v>
+        <v>3305.513262846804</v>
       </c>
       <c r="E21">
-        <v>-1750.86</v>
+        <v>-1725</v>
       </c>
       <c r="F21">
-        <v>491.34</v>
+        <v>517.2</v>
       </c>
       <c r="G21">
         <v>307.9</v>
@@ -3000,28 +3000,28 @@
         <v>242.8</v>
       </c>
       <c r="M21">
-        <v>30.35208879823567</v>
+        <v>31.94956715603755</v>
       </c>
       <c r="N21">
-        <v>212.4479112017643</v>
+        <v>210.8504328439625</v>
       </c>
       <c r="O21">
-        <v>52.6344365675392</v>
+        <v>52.23865779609304</v>
       </c>
       <c r="P21">
-        <v>159.8134746342251</v>
+        <v>158.6117750478694</v>
       </c>
       <c r="Q21">
-        <v>305.0134746342251</v>
+        <v>303.8117750478694</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09372254401880428</v>
+        <v>0.09419542422583112</v>
       </c>
       <c r="T21">
-        <v>0.880043342656405</v>
+        <v>0.8887272530494899</v>
       </c>
       <c r="U21">
         <v>0.061774105096747</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.999449448570197</v>
+        <v>7.599476976141688</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3046,22 +3046,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08465022635944065</v>
+        <v>0.08468237706485982</v>
       </c>
       <c r="C22">
-        <v>3096.213262846804</v>
+        <v>3067.620030179582</v>
       </c>
       <c r="D22">
-        <v>3305.513262846804</v>
+        <v>3302.780030179582</v>
       </c>
       <c r="E22">
-        <v>-1725</v>
+        <v>-1699.14</v>
       </c>
       <c r="F22">
-        <v>517.2</v>
+        <v>543.0600000000001</v>
       </c>
       <c r="G22">
         <v>307.9</v>
@@ -3082,45 +3082,45 @@
         <v>242.8</v>
       </c>
       <c r="M22">
-        <v>31.94956715603755</v>
+        <v>33.98149351383942</v>
       </c>
       <c r="N22">
-        <v>210.8504328439625</v>
+        <v>208.8185064861606</v>
       </c>
       <c r="O22">
-        <v>52.23865779609304</v>
+        <v>51.73524357853425</v>
       </c>
       <c r="P22">
-        <v>158.6117750478694</v>
+        <v>157.0832629076263</v>
       </c>
       <c r="Q22">
-        <v>303.8117750478694</v>
+        <v>302.2832629076263</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09419542422583112</v>
+        <v>0.09468027608366877</v>
       </c>
       <c r="T22">
-        <v>0.8887272530494899</v>
+        <v>0.897631009275311</v>
       </c>
       <c r="U22">
-        <v>0.061774105096747</v>
+        <v>0.06257410509674699</v>
       </c>
       <c r="V22">
         <v>0.2477521961491617</v>
       </c>
       <c r="W22">
-        <v>0.0464694348938788</v>
+        <v>0.04707123313695947</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.599476976141688</v>
+        <v>7.145065589925187</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3128,22 +3128,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08468237706485982</v>
+        <v>0.08459416812166284</v>
       </c>
       <c r="C23">
-        <v>3067.620030179582</v>
+        <v>3049.269786160444</v>
       </c>
       <c r="D23">
-        <v>3302.780030179582</v>
+        <v>3310.289786160444</v>
       </c>
       <c r="E23">
-        <v>-1699.14</v>
+        <v>-1673.28</v>
       </c>
       <c r="F23">
-        <v>543.0599999999999</v>
+        <v>568.92</v>
       </c>
       <c r="G23">
         <v>307.9</v>
@@ -3164,28 +3164,28 @@
         <v>242.8</v>
       </c>
       <c r="M23">
-        <v>33.98149351383942</v>
+        <v>35.59965987164129</v>
       </c>
       <c r="N23">
-        <v>208.8185064861606</v>
+        <v>207.2003401283587</v>
       </c>
       <c r="O23">
-        <v>51.73524357853426</v>
+        <v>51.33433930965415</v>
       </c>
       <c r="P23">
-        <v>157.0832629076263</v>
+        <v>155.8660008187046</v>
       </c>
       <c r="Q23">
-        <v>302.2832629076263</v>
+        <v>301.0660008187045</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09468027608366877</v>
+        <v>0.09517756004042534</v>
       </c>
       <c r="T23">
-        <v>0.897631009275311</v>
+        <v>0.9067630669428198</v>
       </c>
       <c r="U23">
         <v>0.06257410509674699</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.145065589925188</v>
+        <v>6.820289881292227</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3210,22 +3210,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08459416812166284</v>
+        <v>0.08450595917846587</v>
       </c>
       <c r="C24">
-        <v>3049.269786160444</v>
+        <v>3030.953770857131</v>
       </c>
       <c r="D24">
-        <v>3310.289786160444</v>
+        <v>3317.833770857131</v>
       </c>
       <c r="E24">
-        <v>-1673.28</v>
+        <v>-1647.42</v>
       </c>
       <c r="F24">
-        <v>568.92</v>
+        <v>594.78</v>
       </c>
       <c r="G24">
         <v>307.9</v>
@@ -3246,28 +3246,28 @@
         <v>242.8</v>
       </c>
       <c r="M24">
-        <v>35.59965987164129</v>
+        <v>37.21782622944318</v>
       </c>
       <c r="N24">
-        <v>207.2003401283587</v>
+        <v>205.5821737705568</v>
       </c>
       <c r="O24">
-        <v>51.33433930965415</v>
+        <v>50.93343504077404</v>
       </c>
       <c r="P24">
-        <v>155.8660008187046</v>
+        <v>154.6487387297828</v>
       </c>
       <c r="Q24">
-        <v>301.0660008187045</v>
+        <v>299.8487387297828</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09517756004042534</v>
+        <v>0.09568776046359116</v>
       </c>
       <c r="T24">
-        <v>0.9067630669428198</v>
+        <v>0.9161323209133808</v>
       </c>
       <c r="U24">
         <v>0.06257410509674699</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.820289881292227</v>
+        <v>6.523755538627346</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3292,22 +3292,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08450595917846587</v>
+        <v>0.08441775023526892</v>
       </c>
       <c r="C25">
-        <v>3030.953770857131</v>
+        <v>3012.672218820762</v>
       </c>
       <c r="D25">
-        <v>3317.833770857131</v>
+        <v>3325.412218820762</v>
       </c>
       <c r="E25">
-        <v>-1647.42</v>
+        <v>-1621.56</v>
       </c>
       <c r="F25">
-        <v>594.78</v>
+        <v>620.6400000000001</v>
       </c>
       <c r="G25">
         <v>307.9</v>
@@ -3328,28 +3328,28 @@
         <v>242.8</v>
       </c>
       <c r="M25">
-        <v>37.21782622944318</v>
+        <v>38.83599258724506</v>
       </c>
       <c r="N25">
-        <v>205.5821737705568</v>
+        <v>203.9640074127549</v>
       </c>
       <c r="O25">
-        <v>50.93343504077404</v>
+        <v>50.53253077189394</v>
       </c>
       <c r="P25">
-        <v>154.6487387297828</v>
+        <v>153.431476640861</v>
       </c>
       <c r="Q25">
-        <v>299.8487387297828</v>
+        <v>298.631476640861</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09568776046359116</v>
+        <v>0.09621138721368241</v>
       </c>
       <c r="T25">
-        <v>0.9161323209133808</v>
+        <v>0.9257481341989565</v>
       </c>
       <c r="U25">
         <v>0.06257410509674699</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.523755538627346</v>
+        <v>6.251932391184538</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3374,22 +3374,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08441775023526892</v>
+        <v>0.08451760324303463</v>
       </c>
       <c r="C26">
-        <v>3012.672218820762</v>
+        <v>2978.235954168589</v>
       </c>
       <c r="D26">
-        <v>3325.412218820762</v>
+        <v>3316.835954168589</v>
       </c>
       <c r="E26">
-        <v>-1621.56</v>
+        <v>-1595.7</v>
       </c>
       <c r="F26">
-        <v>620.64</v>
+        <v>646.5</v>
       </c>
       <c r="G26">
         <v>307.9</v>
@@ -3410,45 +3410,45 @@
         <v>242.8</v>
       </c>
       <c r="M26">
-        <v>38.83599258724505</v>
+        <v>41.10065894504693</v>
       </c>
       <c r="N26">
-        <v>203.964007412755</v>
+        <v>201.6993410549531</v>
       </c>
       <c r="O26">
-        <v>50.53253077189395</v>
+        <v>49.9714547082034</v>
       </c>
       <c r="P26">
-        <v>153.431476640861</v>
+        <v>151.7278863467497</v>
       </c>
       <c r="Q26">
-        <v>298.631476640861</v>
+        <v>296.9278863467497</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09621138721368241</v>
+        <v>0.09674897734377608</v>
       </c>
       <c r="T26">
-        <v>0.9257481341989565</v>
+        <v>0.9356203691721475</v>
       </c>
       <c r="U26">
-        <v>0.06257410509674699</v>
+        <v>0.06357410509674699</v>
       </c>
       <c r="V26">
         <v>0.2477521961491617</v>
       </c>
       <c r="W26">
-        <v>0.04707123313695947</v>
+        <v>0.04782348094081031</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.25193239118454</v>
+        <v>5.907447866581225</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3456,22 +3456,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08451760324303463</v>
+        <v>0.08443691677787617</v>
       </c>
       <c r="C27">
-        <v>2978.235954168589</v>
+        <v>2959.302587838426</v>
       </c>
       <c r="D27">
-        <v>3316.835954168589</v>
+        <v>3323.762587838426</v>
       </c>
       <c r="E27">
-        <v>-1595.7</v>
+        <v>-1569.84</v>
       </c>
       <c r="F27">
-        <v>646.5</v>
+        <v>672.36</v>
       </c>
       <c r="G27">
         <v>307.9</v>
@@ -3492,28 +3492,28 @@
         <v>242.8</v>
       </c>
       <c r="M27">
-        <v>41.10065894504693</v>
+        <v>42.74468530284881</v>
       </c>
       <c r="N27">
-        <v>201.6993410549531</v>
+        <v>200.0553146971512</v>
       </c>
       <c r="O27">
-        <v>49.9714547082034</v>
+        <v>49.56414356753088</v>
       </c>
       <c r="P27">
-        <v>151.7278863467497</v>
+        <v>150.4911711296203</v>
       </c>
       <c r="Q27">
-        <v>296.9278863467497</v>
+        <v>295.6911711296203</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09674897734377608</v>
+        <v>0.09730109693684526</v>
       </c>
       <c r="T27">
-        <v>0.9356203691721475</v>
+        <v>0.9457594213067763</v>
       </c>
       <c r="U27">
         <v>0.06357410509674699</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.907447866581225</v>
+        <v>5.680238333251177</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3538,22 +3538,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08443691677787617</v>
+        <v>0.0843562303127177</v>
       </c>
       <c r="C28">
-        <v>2959.302587838426</v>
+        <v>2940.398212184051</v>
       </c>
       <c r="D28">
-        <v>3323.762587838426</v>
+        <v>3330.718212184051</v>
       </c>
       <c r="E28">
-        <v>-1569.84</v>
+        <v>-1543.98</v>
       </c>
       <c r="F28">
-        <v>672.36</v>
+        <v>698.22</v>
       </c>
       <c r="G28">
         <v>307.9</v>
@@ -3574,28 +3574,28 @@
         <v>242.8</v>
       </c>
       <c r="M28">
-        <v>42.74468530284881</v>
+        <v>44.38871166065069</v>
       </c>
       <c r="N28">
-        <v>200.0553146971512</v>
+        <v>198.4112883393493</v>
       </c>
       <c r="O28">
-        <v>49.56414356753088</v>
+        <v>49.15683242685835</v>
       </c>
       <c r="P28">
-        <v>150.4911711296203</v>
+        <v>149.254455912491</v>
       </c>
       <c r="Q28">
-        <v>295.6911711296203</v>
+        <v>294.454455912491</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09730109693684526</v>
+        <v>0.09786834309410811</v>
       </c>
       <c r="T28">
-        <v>0.9457594213067763</v>
+        <v>0.9561762556916688</v>
       </c>
       <c r="U28">
         <v>0.06357410509674699</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.680238333251177</v>
+        <v>5.469859135723356</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3620,22 +3620,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0843562303127177</v>
+        <v>0.08427554384755924</v>
       </c>
       <c r="C29">
-        <v>2940.398212184051</v>
+        <v>2921.523009593148</v>
       </c>
       <c r="D29">
-        <v>3330.718212184051</v>
+        <v>3337.703009593148</v>
       </c>
       <c r="E29">
-        <v>-1543.98</v>
+        <v>-1518.12</v>
       </c>
       <c r="F29">
-        <v>698.22</v>
+        <v>724.08</v>
       </c>
       <c r="G29">
         <v>307.9</v>
@@ -3656,28 +3656,28 @@
         <v>242.8</v>
       </c>
       <c r="M29">
-        <v>44.38871166065069</v>
+        <v>46.03273801845256</v>
       </c>
       <c r="N29">
-        <v>198.4112883393493</v>
+        <v>196.7672619815474</v>
       </c>
       <c r="O29">
-        <v>49.15683242685835</v>
+        <v>48.74952128618583</v>
       </c>
       <c r="P29">
-        <v>149.254455912491</v>
+        <v>148.0177406953616</v>
       </c>
       <c r="Q29">
-        <v>294.454455912491</v>
+        <v>293.2177406953616</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09786834309410811</v>
+        <v>0.09845134608907272</v>
       </c>
       <c r="T29">
-        <v>0.9561762556916688</v>
+        <v>0.9668824465872526</v>
       </c>
       <c r="U29">
         <v>0.06357410509674699</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.469859135723356</v>
+        <v>5.274507023733237</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3702,22 +3702,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08427554384755924</v>
+        <v>0.08419485738240078</v>
       </c>
       <c r="C30">
-        <v>2921.523009593148</v>
+        <v>2902.677163986551</v>
       </c>
       <c r="D30">
-        <v>3337.703009593148</v>
+        <v>3344.717163986551</v>
       </c>
       <c r="E30">
-        <v>-1518.12</v>
+        <v>-1492.26</v>
       </c>
       <c r="F30">
-        <v>724.08</v>
+        <v>749.9400000000001</v>
       </c>
       <c r="G30">
         <v>307.9</v>
@@ -3738,28 +3738,28 @@
         <v>242.8</v>
       </c>
       <c r="M30">
-        <v>46.03273801845256</v>
+        <v>47.67676437625444</v>
       </c>
       <c r="N30">
-        <v>196.7672619815474</v>
+        <v>195.1232356237456</v>
       </c>
       <c r="O30">
-        <v>48.74952128618583</v>
+        <v>48.34221014551331</v>
       </c>
       <c r="P30">
-        <v>148.0177406953616</v>
+        <v>146.7810254782323</v>
       </c>
       <c r="Q30">
-        <v>293.2177406953616</v>
+        <v>291.9810254782323</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09845134608907272</v>
+        <v>0.09905077170361379</v>
       </c>
       <c r="T30">
-        <v>0.9668824465872526</v>
+        <v>0.9778902203249658</v>
       </c>
       <c r="U30">
         <v>0.06357410509674699</v>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.274507023733237</v>
+        <v>5.092627471190711</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3784,22 +3784,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08419485738240078</v>
+        <v>0.08411417091724231</v>
       </c>
       <c r="C31">
-        <v>2902.677163986551</v>
+        <v>2883.860860834378</v>
       </c>
       <c r="D31">
-        <v>3344.717163986551</v>
+        <v>3351.760860834378</v>
       </c>
       <c r="E31">
-        <v>-1492.26</v>
+        <v>-1466.4</v>
       </c>
       <c r="F31">
-        <v>749.9399999999999</v>
+        <v>775.8</v>
       </c>
       <c r="G31">
         <v>307.9</v>
@@ -3820,28 +3820,28 @@
         <v>242.8</v>
       </c>
       <c r="M31">
-        <v>47.67676437625443</v>
+        <v>49.32079073405631</v>
       </c>
       <c r="N31">
-        <v>195.1232356237456</v>
+        <v>193.4792092659437</v>
       </c>
       <c r="O31">
-        <v>48.34221014551331</v>
+        <v>47.93489900484079</v>
       </c>
       <c r="P31">
-        <v>146.7810254782323</v>
+        <v>145.5443102611029</v>
       </c>
       <c r="Q31">
-        <v>291.9810254782323</v>
+        <v>290.7443102611029</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09905077170361379</v>
+        <v>0.0996673237642846</v>
       </c>
       <c r="T31">
-        <v>0.9778902203249658</v>
+        <v>0.9892125018837563</v>
       </c>
       <c r="U31">
         <v>0.06357410509674699</v>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.092627471190712</v>
+        <v>4.922873222151021</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3866,22 +3866,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08411417091724231</v>
+        <v>0.08403348445208385</v>
       </c>
       <c r="C32">
-        <v>2883.860860834378</v>
+        <v>2865.074287172388</v>
       </c>
       <c r="D32">
-        <v>3351.760860834378</v>
+        <v>3358.834287172388</v>
       </c>
       <c r="E32">
-        <v>-1466.4</v>
+        <v>-1440.54</v>
       </c>
       <c r="F32">
-        <v>775.8</v>
+        <v>801.66</v>
       </c>
       <c r="G32">
         <v>307.9</v>
@@ -3902,28 +3902,28 @@
         <v>242.8</v>
       </c>
       <c r="M32">
-        <v>49.32079073405631</v>
+        <v>50.96481709185819</v>
       </c>
       <c r="N32">
-        <v>193.4792092659437</v>
+        <v>191.8351829081418</v>
       </c>
       <c r="O32">
-        <v>47.93489900484079</v>
+        <v>47.52758786416826</v>
       </c>
       <c r="P32">
-        <v>145.5443102611029</v>
+        <v>144.3075950439735</v>
       </c>
       <c r="Q32">
-        <v>290.7443102611029</v>
+        <v>289.5075950439735</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0996673237642846</v>
+        <v>0.1003017468991778</v>
       </c>
       <c r="T32">
-        <v>0.9892125018837563</v>
+        <v>1.000862965516715</v>
       </c>
       <c r="U32">
         <v>0.06357410509674699</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.922873222151021</v>
+        <v>4.764070860146148</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3948,22 +3948,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08403348445208385</v>
+        <v>0.08395279798692538</v>
       </c>
       <c r="C33">
-        <v>2865.074287172388</v>
+        <v>2846.317631618524</v>
       </c>
       <c r="D33">
-        <v>3358.834287172388</v>
+        <v>3365.937631618523</v>
       </c>
       <c r="E33">
-        <v>-1440.54</v>
+        <v>-1414.68</v>
       </c>
       <c r="F33">
-        <v>801.66</v>
+        <v>827.52</v>
       </c>
       <c r="G33">
         <v>307.9</v>
@@ -3984,28 +3984,28 @@
         <v>242.8</v>
       </c>
       <c r="M33">
-        <v>50.96481709185819</v>
+        <v>52.60884344966007</v>
       </c>
       <c r="N33">
-        <v>191.8351829081418</v>
+        <v>190.1911565503399</v>
       </c>
       <c r="O33">
-        <v>47.52758786416826</v>
+        <v>47.12027672349574</v>
       </c>
       <c r="P33">
-        <v>144.3075950439735</v>
+        <v>143.0708798268442</v>
       </c>
       <c r="Q33">
-        <v>289.5075950439735</v>
+        <v>288.2708798268442</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1003017468991778</v>
+        <v>0.1009548295380384</v>
       </c>
       <c r="T33">
-        <v>1.000862965516715</v>
+        <v>1.01285608984476</v>
       </c>
       <c r="U33">
         <v>0.06357410509674699</v>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.764070860146148</v>
+        <v>4.615193645766581</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4030,22 +4030,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08395279798692538</v>
+        <v>0.08449271595994384</v>
       </c>
       <c r="C34">
-        <v>2846.317631618524</v>
+        <v>2773.489354042677</v>
       </c>
       <c r="D34">
-        <v>3365.937631618523</v>
+        <v>3318.969354042677</v>
       </c>
       <c r="E34">
-        <v>-1414.68</v>
+        <v>-1388.82</v>
       </c>
       <c r="F34">
-        <v>827.52</v>
+        <v>853.38</v>
       </c>
       <c r="G34">
         <v>307.9</v>
@@ -4066,45 +4066,45 @@
         <v>242.8</v>
       </c>
       <c r="M34">
-        <v>52.60884344966007</v>
+        <v>56.38631980746195</v>
       </c>
       <c r="N34">
-        <v>190.1911565503399</v>
+        <v>186.4136801925381</v>
       </c>
       <c r="O34">
-        <v>47.12027672349574</v>
+        <v>46.18439865994879</v>
       </c>
       <c r="P34">
-        <v>143.0708798268442</v>
+        <v>140.2292815325893</v>
       </c>
       <c r="Q34">
-        <v>288.2708798268442</v>
+        <v>285.4292815325892</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1009548295380384</v>
+        <v>0.101627407181044</v>
       </c>
       <c r="T34">
-        <v>1.01285608984476</v>
+        <v>1.025207217884091</v>
       </c>
       <c r="U34">
-        <v>0.06357410509674699</v>
+        <v>0.06607410509674699</v>
       </c>
       <c r="V34">
         <v>0.2477521961491617</v>
       </c>
       <c r="W34">
-        <v>0.04782348094081031</v>
+        <v>0.0497041004504374</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.615193645766581</v>
+        <v>4.306008989930015</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4112,22 +4112,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08449271595994384</v>
+        <v>0.08443083568988165</v>
       </c>
       <c r="C35">
-        <v>2773.489354042677</v>
+        <v>2752.945799216295</v>
       </c>
       <c r="D35">
-        <v>3318.969354042677</v>
+        <v>3324.285799216295</v>
       </c>
       <c r="E35">
-        <v>-1388.82</v>
+        <v>-1362.96</v>
       </c>
       <c r="F35">
-        <v>853.38</v>
+        <v>879.24</v>
       </c>
       <c r="G35">
         <v>307.9</v>
@@ -4148,28 +4148,28 @@
         <v>242.8</v>
       </c>
       <c r="M35">
-        <v>56.38631980746195</v>
+        <v>58.09499616526383</v>
       </c>
       <c r="N35">
-        <v>186.4136801925381</v>
+        <v>184.7050038347362</v>
       </c>
       <c r="O35">
-        <v>46.18439865994879</v>
+        <v>45.76107033979522</v>
       </c>
       <c r="P35">
-        <v>140.2292815325893</v>
+        <v>138.9439334949409</v>
       </c>
       <c r="Q35">
-        <v>285.4292815325892</v>
+        <v>284.1439334949409</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.101627407181044</v>
+        <v>0.1023203659647469</v>
       </c>
       <c r="T35">
-        <v>1.025207217884091</v>
+        <v>1.037932622530674</v>
       </c>
       <c r="U35">
         <v>0.06607410509674699</v>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.306008989930015</v>
+        <v>4.179361666696779</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4194,22 +4194,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08443083568988165</v>
+        <v>0.08436895541981945</v>
       </c>
       <c r="C36">
-        <v>2752.945799216295</v>
+        <v>2732.419303864796</v>
       </c>
       <c r="D36">
-        <v>3324.285799216295</v>
+        <v>3329.619303864796</v>
       </c>
       <c r="E36">
-        <v>-1362.96</v>
+        <v>-1337.1</v>
       </c>
       <c r="F36">
-        <v>879.24</v>
+        <v>905.1000000000001</v>
       </c>
       <c r="G36">
         <v>307.9</v>
@@ -4230,28 +4230,28 @@
         <v>242.8</v>
       </c>
       <c r="M36">
-        <v>58.09499616526383</v>
+        <v>59.80367252306571</v>
       </c>
       <c r="N36">
-        <v>184.7050038347362</v>
+        <v>182.9963274769343</v>
       </c>
       <c r="O36">
-        <v>45.76107033979522</v>
+        <v>45.33774201964166</v>
       </c>
       <c r="P36">
-        <v>138.9439334949409</v>
+        <v>137.6585854572926</v>
       </c>
       <c r="Q36">
-        <v>284.1439334949409</v>
+        <v>282.8585854572926</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1023203659647469</v>
+        <v>0.103034646557179</v>
       </c>
       <c r="T36">
-        <v>1.037932622530674</v>
+        <v>1.051049578089459</v>
       </c>
       <c r="U36">
         <v>0.06607410509674699</v>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.179361666696779</v>
+        <v>4.059951333362585</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4276,22 +4276,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08436895541981945</v>
+        <v>0.08525490738260934</v>
       </c>
       <c r="C37">
-        <v>2732.419303864796</v>
+        <v>2631.793376042536</v>
       </c>
       <c r="D37">
-        <v>3329.619303864796</v>
+        <v>3254.853376042536</v>
       </c>
       <c r="E37">
-        <v>-1337.1</v>
+        <v>-1311.24</v>
       </c>
       <c r="F37">
-        <v>905.1000000000001</v>
+        <v>930.9600000000002</v>
       </c>
       <c r="G37">
         <v>307.9</v>
@@ -4312,45 +4312,45 @@
         <v>242.8</v>
       </c>
       <c r="M37">
-        <v>59.80367252306571</v>
+        <v>64.77070888086759</v>
       </c>
       <c r="N37">
-        <v>182.9963274769343</v>
+        <v>178.0292911191324</v>
       </c>
       <c r="O37">
-        <v>45.33774201964166</v>
+        <v>44.10714785364351</v>
       </c>
       <c r="P37">
-        <v>137.6585854572926</v>
+        <v>133.9221432654889</v>
       </c>
       <c r="Q37">
-        <v>282.8585854572926</v>
+        <v>279.1221432654889</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.103034646557179</v>
+        <v>0.1037712484181247</v>
       </c>
       <c r="T37">
-        <v>1.051049578089459</v>
+        <v>1.064576438509456</v>
       </c>
       <c r="U37">
-        <v>0.06607410509674699</v>
+        <v>0.069574105096747</v>
       </c>
       <c r="V37">
         <v>0.2477521961491617</v>
       </c>
       <c r="W37">
-        <v>0.0497041004504374</v>
+        <v>0.05233696776391534</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.059951333362585</v>
+        <v>3.748608038960647</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4358,22 +4358,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08525490738260932</v>
+        <v>0.08521935578568192</v>
       </c>
       <c r="C38">
-        <v>2631.793376042538</v>
+        <v>2608.868868847443</v>
       </c>
       <c r="D38">
-        <v>3254.853376042538</v>
+        <v>3257.788868847443</v>
       </c>
       <c r="E38">
-        <v>-1311.24</v>
+        <v>-1285.38</v>
       </c>
       <c r="F38">
-        <v>930.9599999999999</v>
+        <v>956.8199999999999</v>
       </c>
       <c r="G38">
         <v>307.9</v>
@@ -4394,28 +4394,28 @@
         <v>242.8</v>
       </c>
       <c r="M38">
-        <v>64.77070888086757</v>
+        <v>66.56989523866946</v>
       </c>
       <c r="N38">
-        <v>178.0292911191324</v>
+        <v>176.2301047613306</v>
       </c>
       <c r="O38">
-        <v>44.10714785364351</v>
+        <v>43.66139548221648</v>
       </c>
       <c r="P38">
-        <v>133.9221432654889</v>
+        <v>132.5687092791141</v>
       </c>
       <c r="Q38">
-        <v>279.1221432654889</v>
+        <v>277.7687092791141</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1037712484181247</v>
+        <v>0.1045312344651321</v>
       </c>
       <c r="T38">
-        <v>1.064576438509456</v>
+        <v>1.078532723069771</v>
       </c>
       <c r="U38">
         <v>0.069574105096747</v>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.748608038960648</v>
+        <v>3.647294308177927</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4440,22 +4440,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08521935578568192</v>
+        <v>0.0851838041887545</v>
       </c>
       <c r="C39">
-        <v>2608.868868847443</v>
+        <v>2585.949661366744</v>
       </c>
       <c r="D39">
-        <v>3257.788868847443</v>
+        <v>3260.729661366744</v>
       </c>
       <c r="E39">
-        <v>-1285.38</v>
+        <v>-1259.52</v>
       </c>
       <c r="F39">
-        <v>956.8199999999999</v>
+        <v>982.6800000000001</v>
       </c>
       <c r="G39">
         <v>307.9</v>
@@ -4476,28 +4476,28 @@
         <v>242.8</v>
       </c>
       <c r="M39">
-        <v>66.56989523866946</v>
+        <v>68.36908159647135</v>
       </c>
       <c r="N39">
-        <v>176.2301047613306</v>
+        <v>174.4309184035287</v>
       </c>
       <c r="O39">
-        <v>43.66139548221648</v>
+        <v>43.21564311078946</v>
       </c>
       <c r="P39">
-        <v>132.5687092791141</v>
+        <v>131.2152752927392</v>
       </c>
       <c r="Q39">
-        <v>277.7687092791141</v>
+        <v>276.4152752927392</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1045312344651321</v>
+        <v>0.1053157361910753</v>
       </c>
       <c r="T39">
-        <v>1.078532723069771</v>
+        <v>1.092939210357838</v>
       </c>
       <c r="U39">
         <v>0.069574105096747</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.647294308177927</v>
+        <v>3.55131287901535</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4522,22 +4522,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0851838041887545</v>
+        <v>0.0859697071936322</v>
       </c>
       <c r="C40">
-        <v>2585.949661366744</v>
+        <v>2496.294891178122</v>
       </c>
       <c r="D40">
-        <v>3260.729661366744</v>
+        <v>3196.934891178122</v>
       </c>
       <c r="E40">
-        <v>-1259.52</v>
+        <v>-1233.66</v>
       </c>
       <c r="F40">
-        <v>982.6800000000001</v>
+        <v>1008.54</v>
       </c>
       <c r="G40">
         <v>307.9</v>
@@ -4558,45 +4558,45 @@
         <v>242.8</v>
       </c>
       <c r="M40">
-        <v>68.36908159647135</v>
+        <v>72.99217995427321</v>
       </c>
       <c r="N40">
-        <v>174.4309184035287</v>
+        <v>169.8078200457268</v>
       </c>
       <c r="O40">
-        <v>43.21564311078946</v>
+        <v>42.07026033963046</v>
       </c>
       <c r="P40">
-        <v>131.2152752927392</v>
+        <v>127.7375597060963</v>
       </c>
       <c r="Q40">
-        <v>276.4152752927392</v>
+        <v>272.9375597060963</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1053157361910753</v>
+        <v>0.1061259592850821</v>
       </c>
       <c r="T40">
-        <v>1.092939210357838</v>
+        <v>1.107818041491415</v>
       </c>
       <c r="U40">
-        <v>0.069574105096747</v>
+        <v>0.07237410509674699</v>
       </c>
       <c r="V40">
         <v>0.2477521961491617</v>
       </c>
       <c r="W40">
-        <v>0.05233696776391534</v>
+        <v>0.05444326161469768</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.55131287901535</v>
+        <v>3.326383732505384</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4604,22 +4604,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0859697071936322</v>
+        <v>0.0859552185352126</v>
       </c>
       <c r="C41">
-        <v>2496.294891178122</v>
+        <v>2471.58839747986</v>
       </c>
       <c r="D41">
-        <v>3196.934891178122</v>
+        <v>3198.08839747986</v>
       </c>
       <c r="E41">
-        <v>-1233.66</v>
+        <v>-1207.8</v>
       </c>
       <c r="F41">
-        <v>1008.54</v>
+        <v>1034.4</v>
       </c>
       <c r="G41">
         <v>307.9</v>
@@ -4640,28 +4640,28 @@
         <v>242.8</v>
       </c>
       <c r="M41">
-        <v>72.99217995427321</v>
+        <v>74.86377431207509</v>
       </c>
       <c r="N41">
-        <v>169.8078200457268</v>
+        <v>167.9362256879249</v>
       </c>
       <c r="O41">
-        <v>42.07026033963046</v>
+        <v>41.60656872718467</v>
       </c>
       <c r="P41">
-        <v>127.7375597060963</v>
+        <v>126.3296569607403</v>
       </c>
       <c r="Q41">
-        <v>272.9375597060963</v>
+        <v>271.5296569607402</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1061259592850821</v>
+        <v>0.1069631898155559</v>
       </c>
       <c r="T41">
-        <v>1.107818041491415</v>
+        <v>1.123192833662778</v>
       </c>
       <c r="U41">
         <v>0.07237410509674699</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.326383732505384</v>
+        <v>3.243224139192749</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4686,22 +4686,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0859552185352126</v>
+        <v>0.08594072987679302</v>
       </c>
       <c r="C42">
-        <v>2471.58839747986</v>
+        <v>2446.882736489861</v>
       </c>
       <c r="D42">
-        <v>3198.08839747986</v>
+        <v>3199.24273648986</v>
       </c>
       <c r="E42">
-        <v>-1207.8</v>
+        <v>-1181.94</v>
       </c>
       <c r="F42">
-        <v>1034.4</v>
+        <v>1060.26</v>
       </c>
       <c r="G42">
         <v>307.9</v>
@@ -4722,28 +4722,28 @@
         <v>242.8</v>
       </c>
       <c r="M42">
-        <v>74.86377431207509</v>
+        <v>76.73536866987696</v>
       </c>
       <c r="N42">
-        <v>167.9362256879249</v>
+        <v>166.0646313301231</v>
       </c>
       <c r="O42">
-        <v>41.60656872718467</v>
+        <v>41.14287711473887</v>
       </c>
       <c r="P42">
-        <v>126.3296569607403</v>
+        <v>124.9217542153842</v>
       </c>
       <c r="Q42">
-        <v>271.5296569607402</v>
+        <v>270.1217542153842</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1069631898155559</v>
+        <v>0.1078288010419779</v>
       </c>
       <c r="T42">
-        <v>1.123192833662778</v>
+        <v>1.139088805229781</v>
       </c>
       <c r="U42">
         <v>0.07237410509674699</v>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.243224139192749</v>
+        <v>3.164121111407561</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4768,22 +4768,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08594072987679302</v>
+        <v>0.08592624121837343</v>
       </c>
       <c r="C43">
-        <v>2446.882736489861</v>
+        <v>2422.177909110143</v>
       </c>
       <c r="D43">
-        <v>3199.24273648986</v>
+        <v>3200.397909110144</v>
       </c>
       <c r="E43">
-        <v>-1181.94</v>
+        <v>-1156.08</v>
       </c>
       <c r="F43">
-        <v>1060.26</v>
+        <v>1086.12</v>
       </c>
       <c r="G43">
         <v>307.9</v>
@@ -4804,28 +4804,28 @@
         <v>242.8</v>
       </c>
       <c r="M43">
-        <v>76.73536866987696</v>
+        <v>78.60696302767886</v>
       </c>
       <c r="N43">
-        <v>166.0646313301231</v>
+        <v>164.1930369723212</v>
       </c>
       <c r="O43">
-        <v>41.14287711473887</v>
+        <v>40.67918550229307</v>
       </c>
       <c r="P43">
-        <v>124.9217542153842</v>
+        <v>123.5138514700281</v>
       </c>
       <c r="Q43">
-        <v>270.1217542153842</v>
+        <v>268.7138514700281</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1078288010419779</v>
+        <v>0.10872426093138</v>
       </c>
       <c r="T43">
-        <v>1.139088805229781</v>
+        <v>1.15553291374737</v>
       </c>
       <c r="U43">
         <v>0.07237410509674699</v>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.164121111407561</v>
+        <v>3.088784894469285</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4850,22 +4850,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08592624121837343</v>
+        <v>0.08591175255995384</v>
       </c>
       <c r="C44">
-        <v>2422.177909110144</v>
+        <v>2397.473916244027</v>
       </c>
       <c r="D44">
-        <v>3200.397909110144</v>
+        <v>3201.553916244027</v>
       </c>
       <c r="E44">
-        <v>-1156.08</v>
+        <v>-1130.22</v>
       </c>
       <c r="F44">
-        <v>1086.12</v>
+        <v>1111.98</v>
       </c>
       <c r="G44">
         <v>307.9</v>
@@ -4886,28 +4886,28 @@
         <v>242.8</v>
       </c>
       <c r="M44">
-        <v>78.60696302767883</v>
+        <v>80.47855738548073</v>
       </c>
       <c r="N44">
-        <v>164.1930369723212</v>
+        <v>162.3214426145193</v>
       </c>
       <c r="O44">
-        <v>40.67918550229308</v>
+        <v>40.21549388984728</v>
       </c>
       <c r="P44">
-        <v>123.5138514700281</v>
+        <v>122.105948724672</v>
       </c>
       <c r="Q44">
-        <v>268.7138514700281</v>
+        <v>267.305948724672</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.10872426093138</v>
+        <v>0.1096511404660243</v>
       </c>
       <c r="T44">
-        <v>1.15553291374737</v>
+        <v>1.172554008528734</v>
       </c>
       <c r="U44">
         <v>0.07237410509674699</v>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.088784894469286</v>
+        <v>3.016952687621163</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4932,22 +4932,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08591175255995384</v>
+        <v>0.08847897836435033</v>
       </c>
       <c r="C45">
-        <v>2397.473916244027</v>
+        <v>2179.03405273882</v>
       </c>
       <c r="D45">
-        <v>3201.553916244027</v>
+        <v>3008.974052738819</v>
       </c>
       <c r="E45">
-        <v>-1130.22</v>
+        <v>-1104.36</v>
       </c>
       <c r="F45">
-        <v>1111.98</v>
+        <v>1137.84</v>
       </c>
       <c r="G45">
         <v>307.9</v>
@@ -4968,45 +4968,45 @@
         <v>242.8</v>
       </c>
       <c r="M45">
-        <v>80.47855738548073</v>
+        <v>91.22530374328259</v>
       </c>
       <c r="N45">
-        <v>162.3214426145193</v>
+        <v>151.5746962567174</v>
       </c>
       <c r="O45">
-        <v>40.21549388984728</v>
+        <v>37.55296387824386</v>
       </c>
       <c r="P45">
-        <v>122.105948724672</v>
+        <v>114.0217323784735</v>
       </c>
       <c r="Q45">
-        <v>267.305948724672</v>
+        <v>259.2217323784735</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1096511404660243</v>
+        <v>0.1106111228411915</v>
       </c>
       <c r="T45">
-        <v>1.172554008528734</v>
+        <v>1.190182999552289</v>
       </c>
       <c r="U45">
-        <v>0.07237410509674699</v>
+        <v>0.08017410509674699</v>
       </c>
       <c r="V45">
         <v>0.2477521961491617</v>
       </c>
       <c r="W45">
-        <v>0.05444326161469768</v>
+        <v>0.06031079448473423</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.016952687621163</v>
+        <v>2.661542248006805</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5014,22 +5014,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08847897836435033</v>
+        <v>0.08852316503463112</v>
       </c>
       <c r="C46">
-        <v>2179.03405273882</v>
+        <v>2150.062004643974</v>
       </c>
       <c r="D46">
-        <v>3008.974052738819</v>
+        <v>3005.862004643973</v>
       </c>
       <c r="E46">
-        <v>-1104.36</v>
+        <v>-1078.5</v>
       </c>
       <c r="F46">
-        <v>1137.84</v>
+        <v>1163.7</v>
       </c>
       <c r="G46">
         <v>307.9</v>
@@ -5050,28 +5050,28 @@
         <v>242.8</v>
       </c>
       <c r="M46">
-        <v>91.22530374328259</v>
+        <v>93.29860610108449</v>
       </c>
       <c r="N46">
-        <v>151.5746962567174</v>
+        <v>149.5013938989155</v>
       </c>
       <c r="O46">
-        <v>37.55296387824386</v>
+        <v>37.03929866581721</v>
       </c>
       <c r="P46">
-        <v>114.0217323784735</v>
+        <v>112.4620952330983</v>
       </c>
       <c r="Q46">
-        <v>259.2217323784735</v>
+        <v>257.6620952330983</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1106111228411915</v>
+        <v>0.1116060136663649</v>
       </c>
       <c r="T46">
-        <v>1.190182999552289</v>
+        <v>1.208453044794883</v>
       </c>
       <c r="U46">
         <v>0.08017410509674699</v>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.661542248006805</v>
+        <v>2.602396864717765</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08852316503463112</v>
+        <v>0.08856735170491188</v>
       </c>
       <c r="C47">
-        <v>2150.062004643974</v>
+        <v>2121.096387204177</v>
       </c>
       <c r="D47">
-        <v>3005.862004643973</v>
+        <v>3002.756387204177</v>
       </c>
       <c r="E47">
-        <v>-1078.5</v>
+        <v>-1052.64</v>
       </c>
       <c r="F47">
-        <v>1163.7</v>
+        <v>1189.56</v>
       </c>
       <c r="G47">
         <v>307.9</v>
@@ -5132,28 +5132,28 @@
         <v>242.8</v>
       </c>
       <c r="M47">
-        <v>93.29860610108449</v>
+        <v>95.37190845888635</v>
       </c>
       <c r="N47">
-        <v>149.5013938989155</v>
+        <v>147.4280915411136</v>
       </c>
       <c r="O47">
-        <v>37.03929866581721</v>
+        <v>36.52563345339055</v>
       </c>
       <c r="P47">
-        <v>112.4620952330983</v>
+        <v>110.9024580877231</v>
       </c>
       <c r="Q47">
-        <v>257.6620952330983</v>
+        <v>256.1024580877231</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1116060136663649</v>
+        <v>0.112637752299878</v>
       </c>
       <c r="T47">
-        <v>1.208453044794883</v>
+        <v>1.227399758379795</v>
       </c>
       <c r="U47">
         <v>0.08017410509674699</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.602396864717765</v>
+        <v>2.545823019832596</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5178,22 +5178,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08856735170491188</v>
+        <v>0.08999040859965123</v>
       </c>
       <c r="C48">
-        <v>2121.096387204177</v>
+        <v>1998.539087599049</v>
       </c>
       <c r="D48">
-        <v>3002.756387204177</v>
+        <v>2906.059087599049</v>
       </c>
       <c r="E48">
-        <v>-1052.64</v>
+        <v>-1026.78</v>
       </c>
       <c r="F48">
-        <v>1189.56</v>
+        <v>1215.42</v>
       </c>
       <c r="G48">
         <v>307.9</v>
@@ -5214,45 +5214,45 @@
         <v>242.8</v>
       </c>
       <c r="M48">
-        <v>95.37190845888635</v>
+        <v>102.1853488166882</v>
       </c>
       <c r="N48">
-        <v>147.4280915411136</v>
+        <v>140.6146511833118</v>
       </c>
       <c r="O48">
-        <v>36.52563345339055</v>
+        <v>34.83758864141381</v>
       </c>
       <c r="P48">
-        <v>110.9024580877231</v>
+        <v>105.7770625418979</v>
       </c>
       <c r="Q48">
-        <v>256.1024580877231</v>
+        <v>250.9770625418979</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.112637752299878</v>
+        <v>0.1137084244667312</v>
       </c>
       <c r="T48">
-        <v>1.227399758379795</v>
+        <v>1.247061442288667</v>
       </c>
       <c r="U48">
-        <v>0.08017410509674699</v>
+        <v>0.084074105096747</v>
       </c>
       <c r="V48">
         <v>0.2477521961491617</v>
       </c>
       <c r="W48">
-        <v>0.06031079448473423</v>
+        <v>0.06324456091975249</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.545823019832596</v>
+        <v>2.376074484372142</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5260,22 +5260,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08999040859965123</v>
+        <v>0.09006393293428219</v>
       </c>
       <c r="C49">
-        <v>1998.539087599049</v>
+        <v>1967.851995954679</v>
       </c>
       <c r="D49">
-        <v>2906.059087599049</v>
+        <v>2901.231995954679</v>
       </c>
       <c r="E49">
-        <v>-1026.78</v>
+        <v>-1000.92</v>
       </c>
       <c r="F49">
-        <v>1215.42</v>
+        <v>1241.28</v>
       </c>
       <c r="G49">
         <v>307.9</v>
@@ -5296,28 +5296,28 @@
         <v>242.8</v>
       </c>
       <c r="M49">
-        <v>102.1853488166882</v>
+        <v>104.3595051744901</v>
       </c>
       <c r="N49">
-        <v>140.6146511833118</v>
+        <v>138.4404948255099</v>
       </c>
       <c r="O49">
-        <v>34.83758864141381</v>
+        <v>34.29893662899674</v>
       </c>
       <c r="P49">
-        <v>105.7770625418979</v>
+        <v>104.1415581965132</v>
       </c>
       <c r="Q49">
-        <v>250.9770625418979</v>
+        <v>249.3415581965131</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1137084244667312</v>
+        <v>0.1148202763323096</v>
       </c>
       <c r="T49">
-        <v>1.247061442288667</v>
+        <v>1.267479344809417</v>
       </c>
       <c r="U49">
         <v>0.084074105096747</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.376074484372142</v>
+        <v>2.326572932614389</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5342,22 +5342,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09006393293428219</v>
+        <v>0.09013745726891315</v>
       </c>
       <c r="C50">
-        <v>1967.85199595468</v>
+        <v>1937.180913739955</v>
       </c>
       <c r="D50">
-        <v>2901.231995954679</v>
+        <v>2896.420913739955</v>
       </c>
       <c r="E50">
-        <v>-1000.92</v>
+        <v>-975.0599999999999</v>
       </c>
       <c r="F50">
-        <v>1241.28</v>
+        <v>1267.14</v>
       </c>
       <c r="G50">
         <v>307.9</v>
@@ -5378,28 +5378,28 @@
         <v>242.8</v>
       </c>
       <c r="M50">
-        <v>104.3595051744901</v>
+        <v>106.533661532292</v>
       </c>
       <c r="N50">
-        <v>138.4404948255099</v>
+        <v>136.266338467708</v>
       </c>
       <c r="O50">
-        <v>34.29893662899674</v>
+        <v>33.76028461657966</v>
       </c>
       <c r="P50">
-        <v>104.1415581965132</v>
+        <v>102.5060538511284</v>
       </c>
       <c r="Q50">
-        <v>249.3415581965132</v>
+        <v>247.7060538511284</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1148202763323096</v>
+        <v>0.1159757302318322</v>
       </c>
       <c r="T50">
-        <v>1.267479344809417</v>
+        <v>1.288697949389805</v>
       </c>
       <c r="U50">
         <v>0.084074105096747</v>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.32657293261439</v>
+        <v>2.279091852356953</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5424,22 +5424,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09013745726891315</v>
+        <v>0.0902109816035441</v>
       </c>
       <c r="C51">
-        <v>1937.180913739955</v>
+        <v>1906.525761441927</v>
       </c>
       <c r="D51">
-        <v>2896.420913739955</v>
+        <v>2891.625761441927</v>
       </c>
       <c r="E51">
-        <v>-975.0599999999999</v>
+        <v>-949.1999999999998</v>
       </c>
       <c r="F51">
-        <v>1267.14</v>
+        <v>1293</v>
       </c>
       <c r="G51">
         <v>307.9</v>
@@ -5460,28 +5460,28 @@
         <v>242.8</v>
       </c>
       <c r="M51">
-        <v>106.533661532292</v>
+        <v>108.7078178900939</v>
       </c>
       <c r="N51">
-        <v>136.266338467708</v>
+        <v>134.0921821099062</v>
       </c>
       <c r="O51">
-        <v>33.76028461657966</v>
+        <v>33.22163260416259</v>
       </c>
       <c r="P51">
-        <v>102.5060538511284</v>
+        <v>100.8705495057436</v>
       </c>
       <c r="Q51">
-        <v>247.7060538511284</v>
+        <v>246.0705495057436</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1159757302318322</v>
+        <v>0.1171774022873357</v>
       </c>
       <c r="T51">
-        <v>1.288697949389805</v>
+        <v>1.310765298153409</v>
       </c>
       <c r="U51">
         <v>0.084074105096747</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.279091852356953</v>
+        <v>2.233510015309814</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5506,22 +5506,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0902109816035441</v>
+        <v>0.09028450593817507</v>
       </c>
       <c r="C52">
-        <v>1906.525761441927</v>
+        <v>1875.886460073327</v>
       </c>
       <c r="D52">
-        <v>2891.625761441927</v>
+        <v>2886.846460073327</v>
       </c>
       <c r="E52">
-        <v>-949.1999999999998</v>
+        <v>-923.3399999999997</v>
       </c>
       <c r="F52">
-        <v>1293</v>
+        <v>1318.86</v>
       </c>
       <c r="G52">
         <v>307.9</v>
@@ -5542,28 +5542,28 @@
         <v>242.8</v>
       </c>
       <c r="M52">
-        <v>108.7078178900939</v>
+        <v>110.8819742478958</v>
       </c>
       <c r="N52">
-        <v>134.0921821099062</v>
+        <v>131.9180257521043</v>
       </c>
       <c r="O52">
-        <v>33.22163260416259</v>
+        <v>32.6829805917455</v>
       </c>
       <c r="P52">
-        <v>100.8705495057436</v>
+        <v>99.23504516035877</v>
       </c>
       <c r="Q52">
-        <v>246.0705495057436</v>
+        <v>244.4350451603588</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1171774022873357</v>
+        <v>0.1184281221818394</v>
       </c>
       <c r="T52">
-        <v>1.310765298153409</v>
+        <v>1.333733355029813</v>
       </c>
       <c r="U52">
         <v>0.084074105096747</v>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.233510015309814</v>
+        <v>2.189715701284131</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5588,22 +5588,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09028450593817507</v>
+        <v>0.09035803027280601</v>
       </c>
       <c r="C53">
-        <v>1875.886460073327</v>
+        <v>1845.262931168233</v>
       </c>
       <c r="D53">
-        <v>2886.846460073327</v>
+        <v>2882.082931168233</v>
       </c>
       <c r="E53">
-        <v>-923.3399999999997</v>
+        <v>-897.4799999999998</v>
       </c>
       <c r="F53">
-        <v>1318.86</v>
+        <v>1344.72</v>
       </c>
       <c r="G53">
         <v>307.9</v>
@@ -5624,28 +5624,28 @@
         <v>242.8</v>
       </c>
       <c r="M53">
-        <v>110.8819742478958</v>
+        <v>113.0561306056976</v>
       </c>
       <c r="N53">
-        <v>131.9180257521043</v>
+        <v>129.7438693943024</v>
       </c>
       <c r="O53">
-        <v>32.6829805917455</v>
+        <v>32.14432857932843</v>
       </c>
       <c r="P53">
-        <v>99.23504516035877</v>
+        <v>97.59954081497398</v>
       </c>
       <c r="Q53">
-        <v>244.4350451603588</v>
+        <v>242.799540814974</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1184281221818394</v>
+        <v>0.1197309554052807</v>
       </c>
       <c r="T53">
-        <v>1.333733355029813</v>
+        <v>1.357658414276067</v>
       </c>
       <c r="U53">
         <v>0.084074105096747</v>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.189715701284131</v>
+        <v>2.147605783951744</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5670,22 +5670,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09035803027280601</v>
+        <v>0.09043155460743696</v>
       </c>
       <c r="C54">
-        <v>1845.262931168233</v>
+        <v>1814.655096777762</v>
       </c>
       <c r="D54">
-        <v>2882.082931168233</v>
+        <v>2877.335096777762</v>
       </c>
       <c r="E54">
-        <v>-897.4799999999998</v>
+        <v>-871.6199999999997</v>
       </c>
       <c r="F54">
-        <v>1344.72</v>
+        <v>1370.58</v>
       </c>
       <c r="G54">
         <v>307.9</v>
@@ -5706,28 +5706,28 @@
         <v>242.8</v>
       </c>
       <c r="M54">
-        <v>113.0561306056976</v>
+        <v>115.2302869634995</v>
       </c>
       <c r="N54">
-        <v>129.7438693943024</v>
+        <v>127.5697130365005</v>
       </c>
       <c r="O54">
-        <v>32.14432857932843</v>
+        <v>31.60567656691135</v>
       </c>
       <c r="P54">
-        <v>97.59954081497398</v>
+        <v>95.96403646958916</v>
       </c>
       <c r="Q54">
-        <v>242.799540814974</v>
+        <v>241.1640364695891</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1197309554052807</v>
+        <v>0.1210892283403578</v>
       </c>
       <c r="T54">
-        <v>1.357658414276067</v>
+        <v>1.382601561149821</v>
       </c>
       <c r="U54">
         <v>0.084074105096747</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.147605783951744</v>
+        <v>2.107084920103598</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5752,22 +5752,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09043155460743696</v>
+        <v>0.09050507894206791</v>
       </c>
       <c r="C55">
-        <v>1814.655096777762</v>
+        <v>1784.062879465832</v>
       </c>
       <c r="D55">
-        <v>2877.335096777762</v>
+        <v>2872.602879465832</v>
       </c>
       <c r="E55">
-        <v>-871.6199999999997</v>
+        <v>-845.7599999999998</v>
       </c>
       <c r="F55">
-        <v>1370.58</v>
+        <v>1396.44</v>
       </c>
       <c r="G55">
         <v>307.9</v>
@@ -5788,28 +5788,28 @@
         <v>242.8</v>
       </c>
       <c r="M55">
-        <v>115.2302869634995</v>
+        <v>117.4044433213014</v>
       </c>
       <c r="N55">
-        <v>127.5697130365005</v>
+        <v>125.3955566786986</v>
       </c>
       <c r="O55">
-        <v>31.60567656691135</v>
+        <v>31.06702455449427</v>
       </c>
       <c r="P55">
-        <v>95.96403646958916</v>
+        <v>94.32853212420436</v>
       </c>
       <c r="Q55">
-        <v>241.1640364695891</v>
+        <v>239.5285321242043</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1210892283403578</v>
+        <v>0.1225065566204382</v>
       </c>
       <c r="T55">
-        <v>1.382601561149821</v>
+        <v>1.40862919267026</v>
       </c>
       <c r="U55">
         <v>0.084074105096747</v>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.107084920103598</v>
+        <v>2.068064828990568</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5834,22 +5834,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09050507894206791</v>
+        <v>0.09057860327669889</v>
       </c>
       <c r="C56">
-        <v>1784.062879465832</v>
+        <v>1753.486202304942</v>
       </c>
       <c r="D56">
-        <v>2872.602879465832</v>
+        <v>2867.886202304942</v>
       </c>
       <c r="E56">
-        <v>-845.7599999999998</v>
+        <v>-819.8999999999996</v>
       </c>
       <c r="F56">
-        <v>1396.44</v>
+        <v>1422.3</v>
       </c>
       <c r="G56">
         <v>307.9</v>
@@ -5870,28 +5870,28 @@
         <v>242.8</v>
       </c>
       <c r="M56">
-        <v>117.4044433213014</v>
+        <v>119.5785996791033</v>
       </c>
       <c r="N56">
-        <v>125.3955566786986</v>
+        <v>123.2214003208967</v>
       </c>
       <c r="O56">
-        <v>31.06702455449427</v>
+        <v>30.52837254207719</v>
       </c>
       <c r="P56">
-        <v>94.32853212420436</v>
+        <v>92.69302777881956</v>
       </c>
       <c r="Q56">
-        <v>239.5285321242043</v>
+        <v>237.8930277788195</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1225065566204382</v>
+        <v>0.1239868772685223</v>
       </c>
       <c r="T56">
-        <v>1.40862919267026</v>
+        <v>1.43581360781383</v>
       </c>
       <c r="U56">
         <v>0.084074105096747</v>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.068064828990568</v>
+        <v>2.030463650281649</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5916,22 +5916,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09057860327669889</v>
+        <v>0.0966340021475517</v>
       </c>
       <c r="C57">
-        <v>1753.486202304942</v>
+        <v>1386.000634033447</v>
       </c>
       <c r="D57">
-        <v>2867.886202304942</v>
+        <v>2526.260634033447</v>
       </c>
       <c r="E57">
-        <v>-819.8999999999996</v>
+        <v>-794.0399999999997</v>
       </c>
       <c r="F57">
-        <v>1422.3</v>
+        <v>1448.16</v>
       </c>
       <c r="G57">
         <v>307.9</v>
@@ -5952,45 +5952,45 @@
         <v>242.8</v>
       </c>
       <c r="M57">
-        <v>119.5785996791033</v>
+        <v>142.3166280369051</v>
       </c>
       <c r="N57">
-        <v>123.2214003208967</v>
+        <v>100.4833719630949</v>
       </c>
       <c r="O57">
-        <v>30.52837254207719</v>
+        <v>24.89497608032986</v>
       </c>
       <c r="P57">
-        <v>92.69302777881956</v>
+        <v>75.58839588276501</v>
       </c>
       <c r="Q57">
-        <v>237.8930277788195</v>
+        <v>220.788395882765</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1239868772685223</v>
+        <v>0.1255344852187919</v>
       </c>
       <c r="T57">
-        <v>1.43581360781383</v>
+        <v>1.464233678191198</v>
       </c>
       <c r="U57">
-        <v>0.084074105096747</v>
+        <v>0.098274105096747</v>
       </c>
       <c r="V57">
         <v>0.2477521961491617</v>
       </c>
       <c r="W57">
-        <v>0.06324456091975249</v>
+        <v>0.07392647973443439</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.030463650281649</v>
+        <v>1.706055036218521</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5998,22 +5998,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0966340021475517</v>
+        <v>0.09681434567032948</v>
       </c>
       <c r="C58">
-        <v>1386.000634033447</v>
+        <v>1351.209915895052</v>
       </c>
       <c r="D58">
-        <v>2526.260634033447</v>
+        <v>2517.329915895052</v>
       </c>
       <c r="E58">
-        <v>-794.0399999999997</v>
+        <v>-768.1799999999996</v>
       </c>
       <c r="F58">
-        <v>1448.16</v>
+        <v>1474.02</v>
       </c>
       <c r="G58">
         <v>307.9</v>
@@ -6034,28 +6034,28 @@
         <v>242.8</v>
       </c>
       <c r="M58">
-        <v>142.3166280369051</v>
+        <v>144.857996394707</v>
       </c>
       <c r="N58">
-        <v>100.4833719630949</v>
+        <v>97.94200360529297</v>
       </c>
       <c r="O58">
-        <v>24.89497608032986</v>
+        <v>24.26534648846045</v>
       </c>
       <c r="P58">
-        <v>75.58839588276501</v>
+        <v>73.67665711683252</v>
       </c>
       <c r="Q58">
-        <v>220.788395882765</v>
+        <v>218.8766571168325</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1255344852187919</v>
+        <v>0.1271540749341904</v>
       </c>
       <c r="T58">
-        <v>1.464233678191198</v>
+        <v>1.493975612307049</v>
       </c>
       <c r="U58">
         <v>0.098274105096747</v>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.706055036218521</v>
+        <v>1.676124246109424</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6080,22 +6080,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09681434567032948</v>
+        <v>0.09699468919310726</v>
       </c>
       <c r="C59">
-        <v>1351.209915895052</v>
+        <v>1316.482118235142</v>
       </c>
       <c r="D59">
-        <v>2517.329915895052</v>
+        <v>2508.462118235142</v>
       </c>
       <c r="E59">
-        <v>-768.1799999999996</v>
+        <v>-742.3199999999997</v>
       </c>
       <c r="F59">
-        <v>1474.02</v>
+        <v>1499.88</v>
       </c>
       <c r="G59">
         <v>307.9</v>
@@ -6116,28 +6116,28 @@
         <v>242.8</v>
       </c>
       <c r="M59">
-        <v>144.857996394707</v>
+        <v>147.3993647525089</v>
       </c>
       <c r="N59">
-        <v>97.94200360529297</v>
+        <v>95.40063524749112</v>
       </c>
       <c r="O59">
-        <v>24.26534648846045</v>
+        <v>23.63571689659105</v>
       </c>
       <c r="P59">
-        <v>73.67665711683252</v>
+        <v>71.76491835090007</v>
       </c>
       <c r="Q59">
-        <v>218.8766571168325</v>
+        <v>216.9649183509001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1271540749341904</v>
+        <v>0.1288507879693698</v>
       </c>
       <c r="T59">
-        <v>1.493975612307049</v>
+        <v>1.525133828999844</v>
       </c>
       <c r="U59">
         <v>0.098274105096747</v>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.676124246109424</v>
+        <v>1.647225552210986</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6162,22 +6162,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09699468919310725</v>
+        <v>0.09717503271588504</v>
       </c>
       <c r="C60">
-        <v>1316.482118235144</v>
+        <v>1281.816578438041</v>
       </c>
       <c r="D60">
-        <v>2508.462118235143</v>
+        <v>2499.65657843804</v>
       </c>
       <c r="E60">
-        <v>-742.3199999999999</v>
+        <v>-716.4599999999998</v>
       </c>
       <c r="F60">
-        <v>1499.88</v>
+        <v>1525.74</v>
       </c>
       <c r="G60">
         <v>307.9</v>
@@ -6198,28 +6198,28 @@
         <v>242.8</v>
       </c>
       <c r="M60">
-        <v>147.3993647525089</v>
+        <v>149.9407331103108</v>
       </c>
       <c r="N60">
-        <v>95.40063524749112</v>
+        <v>92.85926688968925</v>
       </c>
       <c r="O60">
-        <v>23.63571689659105</v>
+        <v>23.00608730472165</v>
       </c>
       <c r="P60">
-        <v>71.76491835090007</v>
+        <v>69.85317958496761</v>
       </c>
       <c r="Q60">
-        <v>216.9649183509001</v>
+        <v>215.0531795849676</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1288507879693698</v>
+        <v>0.1306302674940701</v>
       </c>
       <c r="T60">
-        <v>1.525133828999844</v>
+        <v>1.557811958702044</v>
       </c>
       <c r="U60">
         <v>0.098274105096747</v>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.647225552210986</v>
+        <v>1.619306475054868</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6244,22 +6244,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09717503271588504</v>
+        <v>0.09735537623866282</v>
       </c>
       <c r="C61">
-        <v>1281.816578438041</v>
+        <v>1247.21264315953</v>
       </c>
       <c r="D61">
-        <v>2499.65657843804</v>
+        <v>2490.91264315953</v>
       </c>
       <c r="E61">
-        <v>-716.4599999999998</v>
+        <v>-690.5999999999999</v>
       </c>
       <c r="F61">
-        <v>1525.74</v>
+        <v>1551.6</v>
       </c>
       <c r="G61">
         <v>307.9</v>
@@ -6280,28 +6280,28 @@
         <v>242.8</v>
       </c>
       <c r="M61">
-        <v>149.9407331103108</v>
+        <v>152.4821014681126</v>
       </c>
       <c r="N61">
-        <v>92.85926688968925</v>
+        <v>90.31789853188738</v>
       </c>
       <c r="O61">
-        <v>23.00608730472165</v>
+        <v>22.37645771285225</v>
       </c>
       <c r="P61">
-        <v>69.85317958496761</v>
+        <v>67.94144081903514</v>
       </c>
       <c r="Q61">
-        <v>215.0531795849676</v>
+        <v>213.1414408190351</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1306302674940701</v>
+        <v>0.1324987209950055</v>
       </c>
       <c r="T61">
-        <v>1.557811958702044</v>
+        <v>1.592123994889355</v>
       </c>
       <c r="U61">
         <v>0.098274105096747</v>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.619306475054868</v>
+        <v>1.592318033803953</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6326,22 +6326,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09735537623866282</v>
+        <v>0.09753571976144058</v>
       </c>
       <c r="C62">
-        <v>1247.21264315953</v>
+        <v>1212.669668165261</v>
       </c>
       <c r="D62">
-        <v>2490.91264315953</v>
+        <v>2482.229668165261</v>
       </c>
       <c r="E62">
-        <v>-690.5999999999999</v>
+        <v>-664.7399999999998</v>
       </c>
       <c r="F62">
-        <v>1551.6</v>
+        <v>1577.46</v>
       </c>
       <c r="G62">
         <v>307.9</v>
@@ -6362,28 +6362,28 @@
         <v>242.8</v>
       </c>
       <c r="M62">
-        <v>152.4821014681126</v>
+        <v>155.0234698259145</v>
       </c>
       <c r="N62">
-        <v>90.31789853188738</v>
+        <v>87.77653017408548</v>
       </c>
       <c r="O62">
-        <v>22.37645771285225</v>
+        <v>21.74682812098284</v>
       </c>
       <c r="P62">
-        <v>67.94144081903514</v>
+        <v>66.02970205310264</v>
       </c>
       <c r="Q62">
-        <v>213.1414408190351</v>
+        <v>211.2297020531026</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1324987209950055</v>
+        <v>0.1344629926241939</v>
       </c>
       <c r="T62">
-        <v>1.592123994889355</v>
+        <v>1.628195622676015</v>
       </c>
       <c r="U62">
         <v>0.098274105096747</v>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.592318033803953</v>
+        <v>1.566214459479298</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6408,22 +6408,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09753571976144058</v>
+        <v>0.09771606328421836</v>
       </c>
       <c r="C63">
-        <v>1212.669668165261</v>
+        <v>1178.187018172527</v>
       </c>
       <c r="D63">
-        <v>2482.229668165261</v>
+        <v>2473.607018172527</v>
       </c>
       <c r="E63">
-        <v>-664.7399999999998</v>
+        <v>-638.8799999999999</v>
       </c>
       <c r="F63">
-        <v>1577.46</v>
+        <v>1603.32</v>
       </c>
       <c r="G63">
         <v>307.9</v>
@@ -6444,28 +6444,28 @@
         <v>242.8</v>
       </c>
       <c r="M63">
-        <v>155.0234698259145</v>
+        <v>157.5648381837164</v>
       </c>
       <c r="N63">
-        <v>87.77653017408548</v>
+        <v>85.23516181628361</v>
       </c>
       <c r="O63">
-        <v>21.74682812098284</v>
+        <v>21.11719852911343</v>
       </c>
       <c r="P63">
-        <v>66.02970205310264</v>
+        <v>64.11796328717017</v>
       </c>
       <c r="Q63">
-        <v>211.2297020531026</v>
+        <v>209.3179632871702</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1344629926241939</v>
+        <v>0.136530646970708</v>
       </c>
       <c r="T63">
-        <v>1.628195622676015</v>
+        <v>1.666165757188288</v>
       </c>
       <c r="U63">
         <v>0.098274105096747</v>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.566214459479298</v>
+        <v>1.540952935939309</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6490,22 +6490,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09771606328421836</v>
+        <v>0.09789640680699614</v>
       </c>
       <c r="C64">
-        <v>1178.187018172527</v>
+        <v>1143.764066695322</v>
       </c>
       <c r="D64">
-        <v>2473.607018172527</v>
+        <v>2465.044066695322</v>
       </c>
       <c r="E64">
-        <v>-638.8799999999999</v>
+        <v>-613.0199999999998</v>
       </c>
       <c r="F64">
-        <v>1603.32</v>
+        <v>1629.18</v>
       </c>
       <c r="G64">
         <v>307.9</v>
@@ -6526,28 +6526,28 @@
         <v>242.8</v>
       </c>
       <c r="M64">
-        <v>157.5648381837164</v>
+        <v>160.1062065415183</v>
       </c>
       <c r="N64">
-        <v>85.23516181628361</v>
+        <v>82.69379345848174</v>
       </c>
       <c r="O64">
-        <v>21.11719852911343</v>
+        <v>20.48756893724403</v>
       </c>
       <c r="P64">
-        <v>64.11796328717017</v>
+        <v>62.2062245212377</v>
       </c>
       <c r="Q64">
-        <v>209.3179632871702</v>
+        <v>207.4062245212377</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.136530646970708</v>
+        <v>0.1387100664170337</v>
       </c>
       <c r="T64">
-        <v>1.666165757188288</v>
+        <v>1.706188331403928</v>
       </c>
       <c r="U64">
         <v>0.098274105096747</v>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.540952935939309</v>
+        <v>1.516493365527575</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6572,22 +6572,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09789640680699614</v>
+        <v>0.1270983792921679</v>
       </c>
       <c r="C65">
-        <v>1143.764066695322</v>
+        <v>232.47252873467</v>
       </c>
       <c r="D65">
-        <v>2465.044066695322</v>
+        <v>1579.61252873467</v>
       </c>
       <c r="E65">
-        <v>-613.0199999999998</v>
+        <v>-587.1599999999999</v>
       </c>
       <c r="F65">
-        <v>1629.18</v>
+        <v>1655.04</v>
       </c>
       <c r="G65">
         <v>307.9</v>
@@ -6608,45 +6608,45 @@
         <v>242.8</v>
       </c>
       <c r="M65">
-        <v>160.1062065415183</v>
+        <v>256.6538468993202</v>
       </c>
       <c r="N65">
-        <v>82.69379345848174</v>
+        <v>-13.85384689932016</v>
       </c>
       <c r="O65">
-        <v>20.48756893724403</v>
+        <v>-3.432320994420824</v>
       </c>
       <c r="P65">
-        <v>62.2062245212377</v>
+        <v>-10.42152590489934</v>
       </c>
       <c r="Q65">
-        <v>207.4062245212377</v>
+        <v>134.7784740951006</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1387100664170337</v>
+        <v>0.1419790272141041</v>
       </c>
       <c r="T65">
-        <v>1.706188331403928</v>
+        <v>1.766219100758279</v>
       </c>
       <c r="U65">
-        <v>0.098274105096747</v>
+        <v>0.155074105096747</v>
       </c>
       <c r="V65">
-        <v>0.2477521961491617</v>
+        <v>0.2343788489896031</v>
       </c>
       <c r="W65">
-        <v>0.07392647973443439</v>
+        <v>0.1187280148360787</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.516493365527575</v>
+        <v>0.9460212770364018</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6654,22 +6654,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1270983792921679</v>
+        <v>0.1281911203431353</v>
       </c>
       <c r="C66">
-        <v>232.47252873467</v>
+        <v>185.6623650813276</v>
       </c>
       <c r="D66">
-        <v>1579.61252873467</v>
+        <v>1558.662365081328</v>
       </c>
       <c r="E66">
-        <v>-587.1599999999999</v>
+        <v>-561.2999999999997</v>
       </c>
       <c r="F66">
-        <v>1655.04</v>
+        <v>1680.9</v>
       </c>
       <c r="G66">
         <v>307.9</v>
@@ -6690,37 +6690,37 @@
         <v>242.8</v>
       </c>
       <c r="M66">
-        <v>256.6538468993202</v>
+        <v>260.6640632571221</v>
       </c>
       <c r="N66">
-        <v>-13.85384689932016</v>
+        <v>-17.86406325712204</v>
       </c>
       <c r="O66">
-        <v>-3.432320994420824</v>
+        <v>-4.425860904099532</v>
       </c>
       <c r="P66">
-        <v>-10.42152590489934</v>
+        <v>-13.43820235302251</v>
       </c>
       <c r="Q66">
-        <v>134.7784740951006</v>
+        <v>131.7617976469775</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1419790272141041</v>
+        <v>0.1447269994202214</v>
       </c>
       <c r="T66">
-        <v>1.766219100758279</v>
+        <v>1.816682503637087</v>
       </c>
       <c r="U66">
         <v>0.155074105096747</v>
       </c>
       <c r="V66">
-        <v>0.2343788489896031</v>
+        <v>0.2307730205436092</v>
       </c>
       <c r="W66">
-        <v>0.1187280148360787</v>
+        <v>0.1192871854554736</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9460212770364018</v>
+        <v>0.931467103543534</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6736,22 +6736,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1281911203431353</v>
+        <v>0.1292838613941028</v>
       </c>
       <c r="C67">
-        <v>185.6623650813276</v>
+        <v>139.4006452461365</v>
       </c>
       <c r="D67">
-        <v>1558.662365081328</v>
+        <v>1538.260645246136</v>
       </c>
       <c r="E67">
-        <v>-561.2999999999997</v>
+        <v>-535.4399999999998</v>
       </c>
       <c r="F67">
-        <v>1680.9</v>
+        <v>1706.76</v>
       </c>
       <c r="G67">
         <v>307.9</v>
@@ -6772,37 +6772,37 @@
         <v>242.8</v>
       </c>
       <c r="M67">
-        <v>260.6640632571221</v>
+        <v>264.6742796149239</v>
       </c>
       <c r="N67">
-        <v>-17.86406325712204</v>
+        <v>-21.87427961492392</v>
       </c>
       <c r="O67">
-        <v>-4.425860904099532</v>
+        <v>-5.419400813778241</v>
       </c>
       <c r="P67">
-        <v>-13.43820235302251</v>
+        <v>-16.45487880114568</v>
       </c>
       <c r="Q67">
-        <v>131.7617976469775</v>
+        <v>128.7451211988543</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1447269994202214</v>
+        <v>0.1476366170502279</v>
       </c>
       <c r="T67">
-        <v>1.816682503637087</v>
+        <v>1.870114341979354</v>
       </c>
       <c r="U67">
         <v>0.155074105096747</v>
       </c>
       <c r="V67">
-        <v>0.2307730205436092</v>
+        <v>0.2272764596262818</v>
       </c>
       <c r="W67">
-        <v>0.1192871854554736</v>
+        <v>0.1198294115106444</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.931467103543534</v>
+        <v>0.9173539656110562</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6818,22 +6818,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1292838613941028</v>
+        <v>0.1303766024450703</v>
       </c>
       <c r="C68">
-        <v>139.4006452461365</v>
+        <v>93.66611132595585</v>
       </c>
       <c r="D68">
-        <v>1538.260645246136</v>
+        <v>1518.386111325956</v>
       </c>
       <c r="E68">
-        <v>-535.4399999999998</v>
+        <v>-509.5799999999997</v>
       </c>
       <c r="F68">
-        <v>1706.76</v>
+        <v>1732.62</v>
       </c>
       <c r="G68">
         <v>307.9</v>
@@ -6854,37 +6854,37 @@
         <v>242.8</v>
       </c>
       <c r="M68">
-        <v>264.6742796149239</v>
+        <v>268.6844959727258</v>
       </c>
       <c r="N68">
-        <v>-21.87427961492392</v>
+        <v>-25.8844959727258</v>
       </c>
       <c r="O68">
-        <v>-5.419400813778241</v>
+        <v>-6.412940723456949</v>
       </c>
       <c r="P68">
-        <v>-16.45487880114568</v>
+        <v>-19.47155524926885</v>
       </c>
       <c r="Q68">
-        <v>128.7451211988543</v>
+        <v>125.7284447507311</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1476366170502279</v>
+        <v>0.150722575142659</v>
       </c>
       <c r="T68">
-        <v>1.870114341979354</v>
+        <v>1.926784473554486</v>
       </c>
       <c r="U68">
         <v>0.155074105096747</v>
       </c>
       <c r="V68">
-        <v>0.2272764596262818</v>
+        <v>0.2238842736617104</v>
       </c>
       <c r="W68">
-        <v>0.1198294115106444</v>
+        <v>0.1203554517134221</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9173539656110562</v>
+        <v>0.9036621153780554</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6900,22 +6900,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1303766024450703</v>
+        <v>0.1314693434960377</v>
       </c>
       <c r="C69">
-        <v>93.66611132595585</v>
+        <v>48.43859002422641</v>
       </c>
       <c r="D69">
-        <v>1518.386111325956</v>
+        <v>1499.018590024226</v>
       </c>
       <c r="E69">
-        <v>-509.5799999999997</v>
+        <v>-483.7199999999998</v>
       </c>
       <c r="F69">
-        <v>1732.62</v>
+        <v>1758.48</v>
       </c>
       <c r="G69">
         <v>307.9</v>
@@ -6936,37 +6936,37 @@
         <v>242.8</v>
       </c>
       <c r="M69">
-        <v>268.6844959727258</v>
+        <v>272.6947123305277</v>
       </c>
       <c r="N69">
-        <v>-25.8844959727258</v>
+        <v>-29.89471233052768</v>
       </c>
       <c r="O69">
-        <v>-6.412940723456949</v>
+        <v>-7.406480633135658</v>
       </c>
       <c r="P69">
-        <v>-19.47155524926885</v>
+        <v>-22.48823169739202</v>
       </c>
       <c r="Q69">
-        <v>125.7284447507311</v>
+        <v>122.711768302608</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.150722575142659</v>
+        <v>0.1540014056158671</v>
       </c>
       <c r="T69">
-        <v>1.926784473554486</v>
+        <v>1.986996488353064</v>
       </c>
       <c r="U69">
         <v>0.155074105096747</v>
       </c>
       <c r="V69">
-        <v>0.2238842736617104</v>
+        <v>0.2205918578725676</v>
       </c>
       <c r="W69">
-        <v>0.1203554517134221</v>
+        <v>0.1208660201455298</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9036621153780554</v>
+        <v>0.8903729666224958</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6982,22 +6982,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1314693434960377</v>
+        <v>0.1325620845470052</v>
       </c>
       <c r="C70">
-        <v>48.43859002422641</v>
+        <v>3.698924349579556</v>
       </c>
       <c r="D70">
-        <v>1499.018590024226</v>
+        <v>1480.13892434958</v>
       </c>
       <c r="E70">
-        <v>-483.7199999999998</v>
+        <v>-457.8599999999997</v>
       </c>
       <c r="F70">
-        <v>1758.48</v>
+        <v>1784.34</v>
       </c>
       <c r="G70">
         <v>307.9</v>
@@ -7018,37 +7018,37 @@
         <v>242.8</v>
       </c>
       <c r="M70">
-        <v>272.6947123305277</v>
+        <v>276.7049286883296</v>
       </c>
       <c r="N70">
-        <v>-29.89471233052768</v>
+        <v>-33.90492868832956</v>
       </c>
       <c r="O70">
-        <v>-7.406480633135658</v>
+        <v>-8.400020542814365</v>
       </c>
       <c r="P70">
-        <v>-22.48823169739202</v>
+        <v>-25.50490814551519</v>
       </c>
       <c r="Q70">
-        <v>122.711768302608</v>
+        <v>119.6950918544848</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1540014056158671</v>
+        <v>0.1574917735389596</v>
       </c>
       <c r="T70">
-        <v>1.986996488353064</v>
+        <v>2.051093149267679</v>
       </c>
       <c r="U70">
         <v>0.155074105096747</v>
       </c>
       <c r="V70">
-        <v>0.2205918578725676</v>
+        <v>0.2173948744251391</v>
       </c>
       <c r="W70">
-        <v>0.1208660201455298</v>
+        <v>0.1213617894926489</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8903729666224958</v>
+        <v>0.8774690105844886</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7064,22 +7064,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1325620845470052</v>
+        <v>0.1336548255979727</v>
       </c>
       <c r="C71">
-        <v>3.698924349579556</v>
+        <v>-40.57108958833351</v>
       </c>
       <c r="D71">
-        <v>1480.13892434958</v>
+        <v>1461.728910411667</v>
       </c>
       <c r="E71">
-        <v>-457.8599999999997</v>
+        <v>-431.9999999999995</v>
       </c>
       <c r="F71">
-        <v>1784.34</v>
+        <v>1810.2</v>
       </c>
       <c r="G71">
         <v>307.9</v>
@@ -7100,37 +7100,37 @@
         <v>242.8</v>
       </c>
       <c r="M71">
-        <v>276.7049286883296</v>
+        <v>280.7151450461315</v>
       </c>
       <c r="N71">
-        <v>-33.90492868832956</v>
+        <v>-37.9151450461315</v>
       </c>
       <c r="O71">
-        <v>-8.400020542814365</v>
+        <v>-9.393560452493089</v>
       </c>
       <c r="P71">
-        <v>-25.50490814551519</v>
+        <v>-28.52158459363841</v>
       </c>
       <c r="Q71">
-        <v>119.6950918544848</v>
+        <v>116.6784154063616</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1574917735389596</v>
+        <v>0.1612148326569249</v>
       </c>
       <c r="T71">
-        <v>2.051093149267679</v>
+        <v>2.119462920909935</v>
       </c>
       <c r="U71">
         <v>0.155074105096747</v>
       </c>
       <c r="V71">
-        <v>0.2173948744251391</v>
+        <v>0.2142892333619227</v>
       </c>
       <c r="W71">
-        <v>0.1213617894926489</v>
+        <v>0.1218433940012789</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8774690105844886</v>
+        <v>0.8649337390047099</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7146,22 +7146,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1336548255979727</v>
+        <v>0.1347475666489402</v>
       </c>
       <c r="C72">
-        <v>-40.57108958833351</v>
+        <v>-84.38876112416096</v>
       </c>
       <c r="D72">
-        <v>1461.728910411667</v>
+        <v>1443.771238875839</v>
       </c>
       <c r="E72">
-        <v>-431.9999999999995</v>
+        <v>-406.1399999999996</v>
       </c>
       <c r="F72">
-        <v>1810.2</v>
+        <v>1836.06</v>
       </c>
       <c r="G72">
         <v>307.9</v>
@@ -7182,37 +7182,37 @@
         <v>242.8</v>
       </c>
       <c r="M72">
-        <v>280.7151450461315</v>
+        <v>284.7253614039333</v>
       </c>
       <c r="N72">
-        <v>-37.9151450461315</v>
+        <v>-41.92536140393332</v>
       </c>
       <c r="O72">
-        <v>-9.393560452493089</v>
+        <v>-10.38710036217178</v>
       </c>
       <c r="P72">
-        <v>-28.52158459363841</v>
+        <v>-31.53826104176154</v>
       </c>
       <c r="Q72">
-        <v>116.6784154063616</v>
+        <v>113.6617389582384</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1612148326569249</v>
+        <v>0.165194654472681</v>
       </c>
       <c r="T72">
-        <v>2.119462920909935</v>
+        <v>2.192547849217175</v>
       </c>
       <c r="U72">
         <v>0.155074105096747</v>
       </c>
       <c r="V72">
-        <v>0.2142892333619227</v>
+        <v>0.2112710751455577</v>
       </c>
       <c r="W72">
-        <v>0.1218433940012789</v>
+        <v>0.1223114321857221</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8649337390047099</v>
+        <v>0.8527515736666156</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7228,22 +7228,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1347475666489401</v>
+        <v>0.1358403076999076</v>
       </c>
       <c r="C73">
-        <v>-84.38876112416028</v>
+        <v>-127.7705593190756</v>
       </c>
       <c r="D73">
-        <v>1443.77123887584</v>
+        <v>1426.249440680924</v>
       </c>
       <c r="E73">
-        <v>-406.1399999999999</v>
+        <v>-380.28</v>
       </c>
       <c r="F73">
-        <v>1836.06</v>
+        <v>1861.92</v>
       </c>
       <c r="G73">
         <v>307.9</v>
@@ -7264,37 +7264,37 @@
         <v>242.8</v>
       </c>
       <c r="M73">
-        <v>284.7253614039333</v>
+        <v>288.7355777617352</v>
       </c>
       <c r="N73">
-        <v>-41.92536140393332</v>
+        <v>-45.93557776173515</v>
       </c>
       <c r="O73">
-        <v>-10.38710036217178</v>
+        <v>-11.38064027185048</v>
       </c>
       <c r="P73">
-        <v>-31.53826104176154</v>
+        <v>-34.55493748988467</v>
       </c>
       <c r="Q73">
-        <v>113.6617389582384</v>
+        <v>110.6450625101153</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1651946544726809</v>
+        <v>0.1694587492752767</v>
       </c>
       <c r="T73">
-        <v>2.192547849217173</v>
+        <v>2.270853129546358</v>
       </c>
       <c r="U73">
         <v>0.155074105096747</v>
       </c>
       <c r="V73">
-        <v>0.2112710751455577</v>
+        <v>0.208336754657425</v>
       </c>
       <c r="W73">
-        <v>0.1223114321857221</v>
+        <v>0.1227664693094863</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8527515736666156</v>
+        <v>0.840907801810135</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1358403076999076</v>
+        <v>0.1369330487508751</v>
       </c>
       <c r="C74">
-        <v>-127.7705593190756</v>
+        <v>-170.7321633377435</v>
       </c>
       <c r="D74">
-        <v>1426.249440680924</v>
+        <v>1409.147836662257</v>
       </c>
       <c r="E74">
-        <v>-380.28</v>
+        <v>-354.4199999999998</v>
       </c>
       <c r="F74">
-        <v>1861.92</v>
+        <v>1887.78</v>
       </c>
       <c r="G74">
         <v>307.9</v>
@@ -7346,37 +7346,37 @@
         <v>242.8</v>
       </c>
       <c r="M74">
-        <v>288.7355777617352</v>
+        <v>292.7457941195371</v>
       </c>
       <c r="N74">
-        <v>-45.93557776173515</v>
+        <v>-49.94579411953708</v>
       </c>
       <c r="O74">
-        <v>-11.38064027185048</v>
+        <v>-12.3741801815292</v>
       </c>
       <c r="P74">
-        <v>-34.55493748988467</v>
+        <v>-37.57161393800789</v>
       </c>
       <c r="Q74">
-        <v>110.6450625101153</v>
+        <v>107.6283860619921</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1694587492752767</v>
+        <v>0.1740387029521388</v>
       </c>
       <c r="T74">
-        <v>2.270853129546358</v>
+        <v>2.354958801011038</v>
       </c>
       <c r="U74">
         <v>0.155074105096747</v>
       </c>
       <c r="V74">
-        <v>0.208336754657425</v>
+        <v>0.2054828265114328</v>
       </c>
       <c r="W74">
-        <v>0.1227664693094863</v>
+        <v>0.1232090396627365</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.840907801810135</v>
+        <v>0.8293885168538316</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7392,22 +7392,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1369330487508751</v>
+        <v>0.1380257898018425</v>
       </c>
       <c r="C75">
-        <v>-170.7321633377435</v>
+        <v>-213.2885092439301</v>
       </c>
       <c r="D75">
-        <v>1409.147836662257</v>
+        <v>1392.45149075607</v>
       </c>
       <c r="E75">
-        <v>-354.4199999999998</v>
+        <v>-328.5599999999999</v>
       </c>
       <c r="F75">
-        <v>1887.78</v>
+        <v>1913.64</v>
       </c>
       <c r="G75">
         <v>307.9</v>
@@ -7428,37 +7428,37 @@
         <v>242.8</v>
       </c>
       <c r="M75">
-        <v>292.7457941195371</v>
+        <v>296.7560104773389</v>
       </c>
       <c r="N75">
-        <v>-49.94579411953708</v>
+        <v>-53.95601047733891</v>
       </c>
       <c r="O75">
-        <v>-12.3741801815292</v>
+        <v>-13.36772009120789</v>
       </c>
       <c r="P75">
-        <v>-37.57161393800789</v>
+        <v>-40.58829038613101</v>
       </c>
       <c r="Q75">
-        <v>107.6283860619921</v>
+        <v>104.611709613869</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1740387029521388</v>
+        <v>0.1789709607579903</v>
       </c>
       <c r="T75">
-        <v>2.354958801011038</v>
+        <v>2.445534139511463</v>
       </c>
       <c r="U75">
         <v>0.155074105096747</v>
       </c>
       <c r="V75">
-        <v>0.2054828265114328</v>
+        <v>0.2027060315585756</v>
       </c>
       <c r="W75">
-        <v>0.1232090396627365</v>
+        <v>0.1236396486550879</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8293885168538316</v>
+        <v>0.8181805639233746</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7474,22 +7474,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1380257898018425</v>
+        <v>0.13911853085281</v>
       </c>
       <c r="C76">
-        <v>-213.2885092439301</v>
+        <v>-255.4538335083039</v>
       </c>
       <c r="D76">
-        <v>1392.45149075607</v>
+        <v>1376.146166491696</v>
       </c>
       <c r="E76">
-        <v>-328.5599999999999</v>
+        <v>-302.6999999999998</v>
       </c>
       <c r="F76">
-        <v>1913.64</v>
+        <v>1939.5</v>
       </c>
       <c r="G76">
         <v>307.9</v>
@@ -7510,37 +7510,37 @@
         <v>242.8</v>
       </c>
       <c r="M76">
-        <v>296.7560104773389</v>
+        <v>300.7662268351409</v>
       </c>
       <c r="N76">
-        <v>-53.95601047733891</v>
+        <v>-57.96622683514084</v>
       </c>
       <c r="O76">
-        <v>-13.36772009120789</v>
+        <v>-14.36126000088662</v>
       </c>
       <c r="P76">
-        <v>-40.58829038613101</v>
+        <v>-43.60496683425423</v>
       </c>
       <c r="Q76">
-        <v>104.611709613869</v>
+        <v>101.5950331657458</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1789709607579903</v>
+        <v>0.1842977991883099</v>
       </c>
       <c r="T76">
-        <v>2.445534139511463</v>
+        <v>2.543355505091922</v>
       </c>
       <c r="U76">
         <v>0.155074105096747</v>
       </c>
       <c r="V76">
-        <v>0.2027060315585756</v>
+        <v>0.2000032844711279</v>
       </c>
       <c r="W76">
-        <v>0.1236396486550879</v>
+        <v>0.1240587747409767</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8181805639233746</v>
+        <v>0.8072714897377294</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7556,22 +7556,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.13911853085281</v>
+        <v>0.1828294540219931</v>
       </c>
       <c r="C77">
-        <v>-255.4538335083039</v>
+        <v>-720.2896710930463</v>
       </c>
       <c r="D77">
-        <v>1376.146166491696</v>
+        <v>937.170328906954</v>
       </c>
       <c r="E77">
-        <v>-302.6999999999998</v>
+        <v>-276.8399999999997</v>
       </c>
       <c r="F77">
-        <v>1939.5</v>
+        <v>1965.36</v>
       </c>
       <c r="G77">
         <v>307.9</v>
@@ -7592,45 +7592,45 @@
         <v>242.8</v>
       </c>
       <c r="M77">
-        <v>300.7662268351409</v>
+        <v>410.9058831929427</v>
       </c>
       <c r="N77">
-        <v>-57.96622683514084</v>
+        <v>-168.1058831929427</v>
       </c>
       <c r="O77">
-        <v>-14.36126000088662</v>
+        <v>-41.64860174664601</v>
       </c>
       <c r="P77">
-        <v>-43.60496683425423</v>
+        <v>-126.4572814462967</v>
       </c>
       <c r="Q77">
-        <v>101.5950331657458</v>
+        <v>18.74271855370328</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1842977991883099</v>
+        <v>0.1966442996470545</v>
       </c>
       <c r="T77">
-        <v>2.543355505091922</v>
+        <v>2.770085027830925</v>
       </c>
       <c r="U77">
-        <v>0.155074105096747</v>
+        <v>0.209074105096747</v>
       </c>
       <c r="V77">
-        <v>0.2000032844711279</v>
+        <v>0.1463941882690708</v>
       </c>
       <c r="W77">
-        <v>0.1240587747409767</v>
+        <v>0.1784668711930263</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.8072714897377294</v>
+        <v>0.590889568465955</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7638,22 +7638,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1828294540219931</v>
+        <v>0.1844621950729605</v>
       </c>
       <c r="C78">
-        <v>-720.2896710930463</v>
+        <v>-757.1848091633033</v>
       </c>
       <c r="D78">
-        <v>937.170328906954</v>
+        <v>926.1351908366968</v>
       </c>
       <c r="E78">
-        <v>-276.8399999999997</v>
+        <v>-250.9799999999998</v>
       </c>
       <c r="F78">
-        <v>1965.36</v>
+        <v>1991.22</v>
       </c>
       <c r="G78">
         <v>307.9</v>
@@ -7674,37 +7674,37 @@
         <v>242.8</v>
       </c>
       <c r="M78">
-        <v>410.9058831929427</v>
+        <v>416.3125395507446</v>
       </c>
       <c r="N78">
-        <v>-168.1058831929427</v>
+        <v>-173.5125395507446</v>
       </c>
       <c r="O78">
-        <v>-41.64860174664601</v>
+        <v>-42.98811273311525</v>
       </c>
       <c r="P78">
-        <v>-126.4572814462967</v>
+        <v>-130.5244268176293</v>
       </c>
       <c r="Q78">
-        <v>18.74271855370328</v>
+        <v>14.67557318237067</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1966442996470545</v>
+        <v>0.203202747457796</v>
       </c>
       <c r="T78">
-        <v>2.770085027830925</v>
+        <v>2.890523507301835</v>
       </c>
       <c r="U78">
         <v>0.209074105096747</v>
       </c>
       <c r="V78">
-        <v>0.1463941882690708</v>
+        <v>0.1444929650447971</v>
       </c>
       <c r="W78">
-        <v>0.1784668711930263</v>
+        <v>0.1788643677372305</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.590889568465955</v>
+        <v>0.5832156779663971</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7720,22 +7720,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1844621950729605</v>
+        <v>0.186094936123928</v>
       </c>
       <c r="C79">
-        <v>-757.1848091633033</v>
+        <v>-793.8230951556714</v>
       </c>
       <c r="D79">
-        <v>926.1351908366968</v>
+        <v>915.3569048443289</v>
       </c>
       <c r="E79">
-        <v>-250.9799999999998</v>
+        <v>-225.1199999999997</v>
       </c>
       <c r="F79">
-        <v>1991.22</v>
+        <v>2017.08</v>
       </c>
       <c r="G79">
         <v>307.9</v>
@@ -7756,37 +7756,37 @@
         <v>242.8</v>
       </c>
       <c r="M79">
-        <v>416.3125395507446</v>
+        <v>421.7191959085465</v>
       </c>
       <c r="N79">
-        <v>-173.5125395507446</v>
+        <v>-178.9191959085465</v>
       </c>
       <c r="O79">
-        <v>-42.98811273311525</v>
+        <v>-44.32762371958451</v>
       </c>
       <c r="P79">
-        <v>-130.5244268176293</v>
+        <v>-134.591572188962</v>
       </c>
       <c r="Q79">
-        <v>14.67557318237067</v>
+        <v>10.60842781103798</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.203202747457796</v>
+        <v>0.2103574177967867</v>
       </c>
       <c r="T79">
-        <v>2.890523507301835</v>
+        <v>3.021910939451919</v>
       </c>
       <c r="U79">
         <v>0.209074105096747</v>
       </c>
       <c r="V79">
-        <v>0.1444929650447971</v>
+        <v>0.1426404911339664</v>
       </c>
       <c r="W79">
-        <v>0.1788643677372305</v>
+        <v>0.1792516720623525</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5832156779663971</v>
+        <v>0.5757385538899047</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7802,22 +7802,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.186094936123928</v>
+        <v>0.1877276771748955</v>
       </c>
       <c r="C80">
-        <v>-793.8230951556714</v>
+        <v>-830.2133935764939</v>
       </c>
       <c r="D80">
-        <v>915.3569048443289</v>
+        <v>904.8266064235062</v>
       </c>
       <c r="E80">
-        <v>-225.1199999999997</v>
+        <v>-199.2599999999998</v>
       </c>
       <c r="F80">
-        <v>2017.08</v>
+        <v>2042.94</v>
       </c>
       <c r="G80">
         <v>307.9</v>
@@ -7838,37 +7838,37 @@
         <v>242.8</v>
       </c>
       <c r="M80">
-        <v>421.7191959085465</v>
+        <v>427.1258522663484</v>
       </c>
       <c r="N80">
-        <v>-178.9191959085465</v>
+        <v>-184.3258522663484</v>
       </c>
       <c r="O80">
-        <v>-44.32762371958451</v>
+        <v>-45.66713470605374</v>
       </c>
       <c r="P80">
-        <v>-134.591572188962</v>
+        <v>-138.6587175602946</v>
       </c>
       <c r="Q80">
-        <v>10.60842781103798</v>
+        <v>6.541282439705356</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2103574177967867</v>
+        <v>0.2181934853109194</v>
       </c>
       <c r="T80">
-        <v>3.021910939451919</v>
+        <v>3.165811460378201</v>
       </c>
       <c r="U80">
         <v>0.209074105096747</v>
       </c>
       <c r="V80">
-        <v>0.1426404911339664</v>
+        <v>0.1408349152968276</v>
       </c>
       <c r="W80">
-        <v>0.1792516720623525</v>
+        <v>0.1796291712146866</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5757385538899047</v>
+        <v>0.56845072409383</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7884,22 +7884,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1877276771748955</v>
+        <v>0.189360418225863</v>
       </c>
       <c r="C81">
-        <v>-830.2133935764939</v>
+        <v>-866.3641656609759</v>
       </c>
       <c r="D81">
-        <v>904.8266064235062</v>
+        <v>894.5358343390243</v>
       </c>
       <c r="E81">
-        <v>-199.2599999999998</v>
+        <v>-173.3999999999996</v>
       </c>
       <c r="F81">
-        <v>2042.94</v>
+        <v>2068.8</v>
       </c>
       <c r="G81">
         <v>307.9</v>
@@ -7920,37 +7920,37 @@
         <v>242.8</v>
       </c>
       <c r="M81">
-        <v>427.1258522663484</v>
+        <v>432.5325086241502</v>
       </c>
       <c r="N81">
-        <v>-184.3258522663484</v>
+        <v>-189.7325086241502</v>
       </c>
       <c r="O81">
-        <v>-45.66713470605374</v>
+        <v>-47.00664569252299</v>
       </c>
       <c r="P81">
-        <v>-138.6587175602946</v>
+        <v>-142.7258629316272</v>
       </c>
       <c r="Q81">
-        <v>6.541282439705356</v>
+        <v>2.474137068372755</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2181934853109194</v>
+        <v>0.2268131595764654</v>
       </c>
       <c r="T81">
-        <v>3.165811460378201</v>
+        <v>3.324102033397111</v>
       </c>
       <c r="U81">
         <v>0.209074105096747</v>
       </c>
       <c r="V81">
-        <v>0.1408349152968276</v>
+        <v>0.1390744788556172</v>
       </c>
       <c r="W81">
-        <v>0.1796291712146866</v>
+        <v>0.1799972328882124</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.56845072409383</v>
+        <v>0.5613450900426572</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7966,22 +7966,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.189360418225863</v>
+        <v>0.1909931592768304</v>
       </c>
       <c r="C82">
-        <v>-866.3641656609759</v>
+        <v>-902.2834920477105</v>
       </c>
       <c r="D82">
-        <v>894.5358343390243</v>
+        <v>884.4765079522898</v>
       </c>
       <c r="E82">
-        <v>-173.3999999999996</v>
+        <v>-147.5399999999995</v>
       </c>
       <c r="F82">
-        <v>2068.8</v>
+        <v>2094.66</v>
       </c>
       <c r="G82">
         <v>307.9</v>
@@ -8002,37 +8002,37 @@
         <v>242.8</v>
       </c>
       <c r="M82">
-        <v>432.5325086241502</v>
+        <v>437.9391649819522</v>
       </c>
       <c r="N82">
-        <v>-189.7325086241502</v>
+        <v>-195.1391649819521</v>
       </c>
       <c r="O82">
-        <v>-47.00664569252299</v>
+        <v>-48.34615667899224</v>
       </c>
       <c r="P82">
-        <v>-142.7258629316272</v>
+        <v>-146.7930083029599</v>
       </c>
       <c r="Q82">
-        <v>2.474137068372755</v>
+        <v>-1.59300830295993</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2268131595764654</v>
+        <v>0.2363401679752267</v>
       </c>
       <c r="T82">
-        <v>3.324102033397111</v>
+        <v>3.499054771996959</v>
       </c>
       <c r="U82">
         <v>0.209074105096747</v>
       </c>
       <c r="V82">
-        <v>0.1390744788556172</v>
+        <v>0.1373575099808566</v>
       </c>
       <c r="W82">
-        <v>0.1799972328882124</v>
+        <v>0.1803562066191819</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5613450900426572</v>
+        <v>0.5544149037458341</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8048,22 +8048,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1909931592768304</v>
+        <v>0.1926259003277979</v>
       </c>
       <c r="C83">
-        <v>-902.2834920477105</v>
+        <v>-937.9790939403326</v>
       </c>
       <c r="D83">
-        <v>884.4765079522898</v>
+        <v>874.6409060596674</v>
       </c>
       <c r="E83">
-        <v>-147.5399999999995</v>
+        <v>-121.6799999999998</v>
       </c>
       <c r="F83">
-        <v>2094.66</v>
+        <v>2120.52</v>
       </c>
       <c r="G83">
         <v>307.9</v>
@@ -8084,37 +8084,37 @@
         <v>242.8</v>
       </c>
       <c r="M83">
-        <v>437.9391649819522</v>
+        <v>443.345821339754</v>
       </c>
       <c r="N83">
-        <v>-195.1391649819521</v>
+        <v>-200.545821339754</v>
       </c>
       <c r="O83">
-        <v>-48.34615667899224</v>
+        <v>-49.68566766546147</v>
       </c>
       <c r="P83">
-        <v>-146.7930083029599</v>
+        <v>-150.8601536742925</v>
       </c>
       <c r="Q83">
-        <v>-1.59300830295993</v>
+        <v>-5.660153674292502</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2363401679752267</v>
+        <v>0.2469257328627393</v>
       </c>
       <c r="T83">
-        <v>3.499054771996959</v>
+        <v>3.693446703774568</v>
       </c>
       <c r="U83">
         <v>0.209074105096747</v>
       </c>
       <c r="V83">
-        <v>0.1373575099808566</v>
+        <v>0.1356824183957241</v>
       </c>
       <c r="W83">
-        <v>0.1803562066191819</v>
+        <v>0.1807064248932986</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5544149037458341</v>
+        <v>0.5476537463830802</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8130,22 +8130,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1926259003277979</v>
+        <v>0.1942586413787654</v>
       </c>
       <c r="C84">
-        <v>-937.9790939403326</v>
+        <v>-973.4583528727621</v>
       </c>
       <c r="D84">
-        <v>874.6409060596674</v>
+        <v>865.0216471272381</v>
       </c>
       <c r="E84">
-        <v>-121.6799999999998</v>
+        <v>-95.81999999999971</v>
       </c>
       <c r="F84">
-        <v>2120.52</v>
+        <v>2146.38</v>
       </c>
       <c r="G84">
         <v>307.9</v>
@@ -8166,37 +8166,37 @@
         <v>242.8</v>
       </c>
       <c r="M84">
-        <v>443.345821339754</v>
+        <v>448.7524776975559</v>
       </c>
       <c r="N84">
-        <v>-200.545821339754</v>
+        <v>-205.9524776975559</v>
       </c>
       <c r="O84">
-        <v>-49.68566766546147</v>
+        <v>-51.02517865193072</v>
       </c>
       <c r="P84">
-        <v>-150.8601536742925</v>
+        <v>-154.9272990456251</v>
       </c>
       <c r="Q84">
-        <v>-5.660153674292502</v>
+        <v>-9.727299045625159</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2469257328627393</v>
+        <v>0.2587566583252535</v>
       </c>
       <c r="T84">
-        <v>3.693446703774568</v>
+        <v>3.910708274584838</v>
       </c>
       <c r="U84">
         <v>0.209074105096747</v>
       </c>
       <c r="V84">
-        <v>0.1356824183957241</v>
+        <v>0.1340476904632456</v>
       </c>
       <c r="W84">
-        <v>0.1807064248932986</v>
+        <v>0.1810482041728582</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5476537463830802</v>
+        <v>0.5410555084748503</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8212,22 +8212,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1942586413787654</v>
+        <v>0.1958913824297329</v>
       </c>
       <c r="C85">
-        <v>-973.4583528727621</v>
+        <v>-1008.728329184369</v>
       </c>
       <c r="D85">
-        <v>865.0216471272381</v>
+        <v>855.6116708156312</v>
       </c>
       <c r="E85">
-        <v>-95.81999999999971</v>
+        <v>-69.95999999999958</v>
       </c>
       <c r="F85">
-        <v>2146.38</v>
+        <v>2172.24</v>
       </c>
       <c r="G85">
         <v>307.9</v>
@@ -8248,37 +8248,37 @@
         <v>242.8</v>
       </c>
       <c r="M85">
-        <v>448.7524776975559</v>
+        <v>454.1591340553578</v>
       </c>
       <c r="N85">
-        <v>-205.9524776975559</v>
+        <v>-211.3591340553577</v>
       </c>
       <c r="O85">
-        <v>-51.02517865193072</v>
+        <v>-52.36468963839996</v>
       </c>
       <c r="P85">
-        <v>-154.9272990456251</v>
+        <v>-158.9944444169578</v>
       </c>
       <c r="Q85">
-        <v>-9.727299045625159</v>
+        <v>-13.79444441695779</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2587566583252535</v>
+        <v>0.2720664494705818</v>
       </c>
       <c r="T85">
-        <v>3.910708274584838</v>
+        <v>4.15512754174639</v>
       </c>
       <c r="U85">
         <v>0.209074105096747</v>
       </c>
       <c r="V85">
-        <v>0.1340476904632456</v>
+        <v>0.1324518846243974</v>
       </c>
       <c r="W85">
-        <v>0.1810482041728582</v>
+        <v>0.1813818458505236</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5410555084748503</v>
+        <v>0.5346143714691973</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8294,22 +8294,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1958913824297329</v>
+        <v>0.1975241234807003</v>
       </c>
       <c r="C86">
-        <v>-1008.728329184369</v>
+        <v>-1043.795779302248</v>
       </c>
       <c r="D86">
-        <v>855.6116708156312</v>
+        <v>846.4042206977516</v>
       </c>
       <c r="E86">
-        <v>-69.96000000000004</v>
+        <v>-44.09999999999991</v>
       </c>
       <c r="F86">
-        <v>2172.24</v>
+        <v>2198.1</v>
       </c>
       <c r="G86">
         <v>307.9</v>
@@ -8330,37 +8330,37 @@
         <v>242.8</v>
       </c>
       <c r="M86">
-        <v>454.1591340553577</v>
+        <v>459.5657904131596</v>
       </c>
       <c r="N86">
-        <v>-211.3591340553577</v>
+        <v>-216.7657904131596</v>
       </c>
       <c r="O86">
-        <v>-52.36468963839994</v>
+        <v>-53.70420062486918</v>
       </c>
       <c r="P86">
-        <v>-158.9944444169577</v>
+        <v>-163.0615897882904</v>
       </c>
       <c r="Q86">
-        <v>-13.79444441695776</v>
+        <v>-17.86158978829039</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2720664494705817</v>
+        <v>0.2871508794352871</v>
       </c>
       <c r="T86">
-        <v>4.155127541746388</v>
+        <v>4.43213604452948</v>
       </c>
       <c r="U86">
         <v>0.209074105096747</v>
       </c>
       <c r="V86">
-        <v>0.1324518846243974</v>
+        <v>0.130893627158228</v>
       </c>
       <c r="W86">
-        <v>0.1813818458505236</v>
+        <v>0.1817076371357732</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5346143714691973</v>
+        <v>0.5283247906283833</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8376,22 +8376,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1975241234807003</v>
+        <v>0.1991568645316678</v>
       </c>
       <c r="C87">
-        <v>-1043.795779302248</v>
+        <v>-1078.667171919499</v>
       </c>
       <c r="D87">
-        <v>846.4042206977516</v>
+        <v>837.3928280805012</v>
       </c>
       <c r="E87">
-        <v>-44.09999999999991</v>
+        <v>-18.23999999999978</v>
       </c>
       <c r="F87">
-        <v>2198.1</v>
+        <v>2223.96</v>
       </c>
       <c r="G87">
         <v>307.9</v>
@@ -8412,37 +8412,37 @@
         <v>242.8</v>
       </c>
       <c r="M87">
-        <v>459.5657904131596</v>
+        <v>464.9724467709615</v>
       </c>
       <c r="N87">
-        <v>-216.7657904131596</v>
+        <v>-222.1724467709615</v>
       </c>
       <c r="O87">
-        <v>-53.70420062486918</v>
+        <v>-55.04371161133844</v>
       </c>
       <c r="P87">
-        <v>-163.0615897882904</v>
+        <v>-167.128735159623</v>
       </c>
       <c r="Q87">
-        <v>-17.86158978829039</v>
+        <v>-21.92873515962305</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2871508794352871</v>
+        <v>0.3043902279663791</v>
       </c>
       <c r="T87">
-        <v>4.43213604452948</v>
+        <v>4.748717190567301</v>
       </c>
       <c r="U87">
         <v>0.209074105096747</v>
       </c>
       <c r="V87">
-        <v>0.130893627158228</v>
+        <v>0.1293716082377835</v>
       </c>
       <c r="W87">
-        <v>0.1817076371357732</v>
+        <v>0.1820258518795055</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5283247906283833</v>
+        <v>0.5221814791094486</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8458,22 +8458,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1991568645316678</v>
+        <v>0.2007896055826353</v>
       </c>
       <c r="C88">
-        <v>-1078.667171919499</v>
+        <v>-1113.34870315092</v>
       </c>
       <c r="D88">
-        <v>837.3928280805012</v>
+        <v>828.5712968490805</v>
       </c>
       <c r="E88">
-        <v>-18.23999999999978</v>
+        <v>7.620000000000346</v>
       </c>
       <c r="F88">
-        <v>2223.96</v>
+        <v>2249.82</v>
       </c>
       <c r="G88">
         <v>307.9</v>
@@ -8494,37 +8494,37 @@
         <v>242.8</v>
       </c>
       <c r="M88">
-        <v>464.9724467709615</v>
+        <v>470.3791031287634</v>
       </c>
       <c r="N88">
-        <v>-222.1724467709615</v>
+        <v>-227.5791031287634</v>
       </c>
       <c r="O88">
-        <v>-55.04371161133844</v>
+        <v>-56.38322259780769</v>
       </c>
       <c r="P88">
-        <v>-167.128735159623</v>
+        <v>-171.1958805309557</v>
       </c>
       <c r="Q88">
-        <v>-21.92873515962305</v>
+        <v>-25.9958805309557</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3043902279663791</v>
+        <v>0.3242817839637928</v>
       </c>
       <c r="T88">
-        <v>4.748717190567301</v>
+        <v>5.114003128303247</v>
       </c>
       <c r="U88">
         <v>0.209074105096747</v>
       </c>
       <c r="V88">
-        <v>0.1293716082377835</v>
+        <v>0.1278845782580388</v>
       </c>
       <c r="W88">
-        <v>0.1820258518795055</v>
+        <v>0.1823367513417726</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5221814791094486</v>
+        <v>0.5161793931426732</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8540,22 +8540,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2007896055826353</v>
+        <v>0.2024223466336027</v>
       </c>
       <c r="C89">
-        <v>-1113.34870315092</v>
+        <v>-1147.846310740746</v>
       </c>
       <c r="D89">
-        <v>828.5712968490805</v>
+        <v>819.933689259254</v>
       </c>
       <c r="E89">
-        <v>7.620000000000346</v>
+        <v>33.48000000000002</v>
       </c>
       <c r="F89">
-        <v>2249.82</v>
+        <v>2275.68</v>
       </c>
       <c r="G89">
         <v>307.9</v>
@@ -8576,37 +8576,37 @@
         <v>242.8</v>
       </c>
       <c r="M89">
-        <v>470.3791031287634</v>
+        <v>475.7857594865652</v>
       </c>
       <c r="N89">
-        <v>-227.5791031287634</v>
+        <v>-232.9857594865652</v>
       </c>
       <c r="O89">
-        <v>-56.38322259780769</v>
+        <v>-57.72273358427692</v>
       </c>
       <c r="P89">
-        <v>-171.1958805309557</v>
+        <v>-175.2630259022883</v>
       </c>
       <c r="Q89">
-        <v>-25.9958805309557</v>
+        <v>-30.0630259022883</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3242817839637928</v>
+        <v>0.3474885992941089</v>
       </c>
       <c r="T89">
-        <v>5.114003128303247</v>
+        <v>5.540170055661851</v>
       </c>
       <c r="U89">
         <v>0.209074105096747</v>
       </c>
       <c r="V89">
-        <v>0.1278845782580388</v>
+        <v>0.1264313444141975</v>
       </c>
       <c r="W89">
-        <v>0.1823367513417726</v>
+        <v>0.1826405849071701</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5161793931426732</v>
+        <v>0.5103137182205975</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8622,22 +8622,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2024223466336027</v>
+        <v>0.2040550876845702</v>
       </c>
       <c r="C90">
-        <v>-1147.846310740746</v>
+        <v>-1182.165687390886</v>
       </c>
       <c r="D90">
-        <v>819.933689259254</v>
+        <v>811.4743126091136</v>
       </c>
       <c r="E90">
-        <v>33.48000000000002</v>
+        <v>59.34000000000015</v>
       </c>
       <c r="F90">
-        <v>2275.68</v>
+        <v>2301.54</v>
       </c>
       <c r="G90">
         <v>307.9</v>
@@ -8658,37 +8658,37 @@
         <v>242.8</v>
       </c>
       <c r="M90">
-        <v>475.7857594865652</v>
+        <v>481.1924158443671</v>
       </c>
       <c r="N90">
-        <v>-232.9857594865652</v>
+        <v>-238.3924158443671</v>
       </c>
       <c r="O90">
-        <v>-57.72273358427692</v>
+        <v>-59.06224457074616</v>
       </c>
       <c r="P90">
-        <v>-175.2630259022883</v>
+        <v>-179.3301712736209</v>
       </c>
       <c r="Q90">
-        <v>-30.0630259022883</v>
+        <v>-34.13017127362093</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3474885992941089</v>
+        <v>0.3749148355935734</v>
       </c>
       <c r="T90">
-        <v>5.540170055661851</v>
+        <v>6.043821878903837</v>
       </c>
       <c r="U90">
         <v>0.209074105096747</v>
       </c>
       <c r="V90">
-        <v>0.1264313444141975</v>
+        <v>0.1250107675106672</v>
       </c>
       <c r="W90">
-        <v>0.1826405849071701</v>
+        <v>0.1829375907519968</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5103137182205975</v>
+        <v>0.504579856218119</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8704,22 +8704,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2040550876845702</v>
+        <v>0.2378377323925509</v>
       </c>
       <c r="C91">
-        <v>-1182.165687390886</v>
+        <v>-1350.777572923929</v>
       </c>
       <c r="D91">
-        <v>811.4743126091136</v>
+        <v>668.7224270760707</v>
       </c>
       <c r="E91">
-        <v>59.34000000000015</v>
+        <v>85.20000000000027</v>
       </c>
       <c r="F91">
-        <v>2301.54</v>
+        <v>2327.4</v>
       </c>
       <c r="G91">
         <v>307.9</v>
@@ -8740,45 +8740,45 @@
         <v>242.8</v>
       </c>
       <c r="M91">
-        <v>481.1924158443671</v>
+        <v>568.058072202169</v>
       </c>
       <c r="N91">
-        <v>-238.3924158443671</v>
+        <v>-325.258072202169</v>
       </c>
       <c r="O91">
-        <v>-59.06224457074616</v>
+        <v>-80.58340170332998</v>
       </c>
       <c r="P91">
-        <v>-179.3301712736209</v>
+        <v>-244.674670498839</v>
       </c>
       <c r="Q91">
-        <v>-34.13017127362093</v>
+        <v>-99.47467049883903</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3749148355935734</v>
+        <v>0.4143253557230632</v>
       </c>
       <c r="T91">
-        <v>6.043821878903837</v>
+        <v>6.767551525998002</v>
       </c>
       <c r="U91">
-        <v>0.209074105096747</v>
+        <v>0.244074105096747</v>
       </c>
       <c r="V91">
-        <v>0.1250107675106672</v>
+        <v>0.1058945135517903</v>
       </c>
       <c r="W91">
-        <v>0.1829375907519968</v>
+        <v>0.2182279964669384</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.504579856218119</v>
+        <v>0.4274210892888936</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8786,22 +8786,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2378377323925509</v>
+        <v>0.2398204734435184</v>
       </c>
       <c r="C92">
-        <v>-1350.777572923929</v>
+        <v>-1383.471405376422</v>
       </c>
       <c r="D92">
-        <v>668.7224270760707</v>
+        <v>661.8885946235778</v>
       </c>
       <c r="E92">
-        <v>85.20000000000027</v>
+        <v>111.0600000000004</v>
       </c>
       <c r="F92">
-        <v>2327.4</v>
+        <v>2353.26</v>
       </c>
       <c r="G92">
         <v>307.9</v>
@@ -8822,37 +8822,37 @@
         <v>242.8</v>
       </c>
       <c r="M92">
-        <v>568.058072202169</v>
+        <v>574.369828559971</v>
       </c>
       <c r="N92">
-        <v>-325.258072202169</v>
+        <v>-331.569828559971</v>
       </c>
       <c r="O92">
-        <v>-80.58340170332998</v>
+        <v>-82.14715320253386</v>
       </c>
       <c r="P92">
-        <v>-244.674670498839</v>
+        <v>-249.4226753574371</v>
       </c>
       <c r="Q92">
-        <v>-99.47467049883903</v>
+        <v>-104.2226753574371</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4143253557230632</v>
+        <v>0.4552726174700703</v>
       </c>
       <c r="T92">
-        <v>6.767551525998002</v>
+        <v>7.519501695553337</v>
       </c>
       <c r="U92">
         <v>0.244074105096747</v>
       </c>
       <c r="V92">
-        <v>0.1058945135517903</v>
+        <v>0.1047308375786937</v>
       </c>
       <c r="W92">
-        <v>0.2182279964669384</v>
+        <v>0.2185120196386946</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4274210892888936</v>
+        <v>0.4227241542417628</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8868,22 +8868,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2398204734435184</v>
+        <v>0.2418032144944859</v>
       </c>
       <c r="C93">
-        <v>-1383.471405376422</v>
+        <v>-1416.026977646051</v>
       </c>
       <c r="D93">
-        <v>661.8885946235778</v>
+        <v>655.1930223539492</v>
       </c>
       <c r="E93">
-        <v>111.0600000000004</v>
+        <v>136.9200000000001</v>
       </c>
       <c r="F93">
-        <v>2353.26</v>
+        <v>2379.12</v>
       </c>
       <c r="G93">
         <v>307.9</v>
@@ -8904,37 +8904,37 @@
         <v>242.8</v>
       </c>
       <c r="M93">
-        <v>574.369828559971</v>
+        <v>580.6815849177727</v>
       </c>
       <c r="N93">
-        <v>-331.569828559971</v>
+        <v>-337.8815849177727</v>
       </c>
       <c r="O93">
-        <v>-82.14715320253386</v>
+        <v>-83.71090470173768</v>
       </c>
       <c r="P93">
-        <v>-249.4226753574371</v>
+        <v>-254.1706802160351</v>
       </c>
       <c r="Q93">
-        <v>-104.2226753574371</v>
+        <v>-108.9706802160351</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4552726174700703</v>
+        <v>0.5064566946538291</v>
       </c>
       <c r="T93">
-        <v>7.519501695553337</v>
+        <v>8.459439407497506</v>
       </c>
       <c r="U93">
         <v>0.244074105096747</v>
       </c>
       <c r="V93">
-        <v>0.1047308375786937</v>
+        <v>0.1035924589093601</v>
       </c>
       <c r="W93">
-        <v>0.2185120196386946</v>
+        <v>0.2187898683936734</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4227241542417628</v>
+        <v>0.4181293264782654</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8950,22 +8950,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2418032144944859</v>
+        <v>0.2437859555454533</v>
       </c>
       <c r="C94">
-        <v>-1416.026977646051</v>
+        <v>-1448.448443575034</v>
       </c>
       <c r="D94">
-        <v>655.1930223539492</v>
+        <v>648.6315564249663</v>
       </c>
       <c r="E94">
-        <v>136.9200000000001</v>
+        <v>162.7800000000002</v>
       </c>
       <c r="F94">
-        <v>2379.12</v>
+        <v>2404.98</v>
       </c>
       <c r="G94">
         <v>307.9</v>
@@ -8986,37 +8986,37 @@
         <v>242.8</v>
       </c>
       <c r="M94">
-        <v>580.6815849177727</v>
+        <v>586.9933412755746</v>
       </c>
       <c r="N94">
-        <v>-337.8815849177727</v>
+        <v>-344.1933412755746</v>
       </c>
       <c r="O94">
-        <v>-83.71090470173768</v>
+        <v>-85.27465620094152</v>
       </c>
       <c r="P94">
-        <v>-254.1706802160351</v>
+        <v>-258.9186850746331</v>
       </c>
       <c r="Q94">
-        <v>-108.9706802160351</v>
+        <v>-113.7186850746331</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5064566946538291</v>
+        <v>0.5722647938900907</v>
       </c>
       <c r="T94">
-        <v>8.459439407497506</v>
+        <v>9.667930751425724</v>
       </c>
       <c r="U94">
         <v>0.244074105096747</v>
       </c>
       <c r="V94">
-        <v>0.1035924589093601</v>
+        <v>0.1024785615017326</v>
       </c>
       <c r="W94">
-        <v>0.2187898683936734</v>
+        <v>0.2190617419066097</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4181293264782654</v>
+        <v>0.4136333122150583</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9032,22 +9032,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2437859555454533</v>
+        <v>0.2457686965964208</v>
       </c>
       <c r="C95">
-        <v>-1448.448443575034</v>
+        <v>-1480.739792259935</v>
       </c>
       <c r="D95">
-        <v>648.6315564249663</v>
+        <v>642.2002077400655</v>
       </c>
       <c r="E95">
-        <v>162.7800000000002</v>
+        <v>188.6400000000003</v>
       </c>
       <c r="F95">
-        <v>2404.98</v>
+        <v>2430.84</v>
       </c>
       <c r="G95">
         <v>307.9</v>
@@ -9068,37 +9068,37 @@
         <v>242.8</v>
       </c>
       <c r="M95">
-        <v>586.9933412755746</v>
+        <v>593.3050976333766</v>
       </c>
       <c r="N95">
-        <v>-344.1933412755746</v>
+        <v>-350.5050976333766</v>
       </c>
       <c r="O95">
-        <v>-85.27465620094152</v>
+        <v>-86.8384077001454</v>
       </c>
       <c r="P95">
-        <v>-258.9186850746331</v>
+        <v>-263.6666899332312</v>
       </c>
       <c r="Q95">
-        <v>-113.7186850746331</v>
+        <v>-118.4666899332312</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5722647938900907</v>
+        <v>0.6600089262051059</v>
       </c>
       <c r="T95">
-        <v>9.667930751425724</v>
+        <v>11.27925254333001</v>
       </c>
       <c r="U95">
         <v>0.244074105096747</v>
       </c>
       <c r="V95">
-        <v>0.1024785615017326</v>
+        <v>0.1013883640389482</v>
       </c>
       <c r="W95">
-        <v>0.2190617419066097</v>
+        <v>0.2193278308767175</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4136333122150583</v>
+        <v>0.4092329578297916</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9114,22 +9114,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2457686965964208</v>
+        <v>0.2477514376473883</v>
       </c>
       <c r="C96">
-        <v>-1480.739792259935</v>
+        <v>-1512.904856138951</v>
       </c>
       <c r="D96">
-        <v>642.2002077400655</v>
+        <v>635.8951438610488</v>
       </c>
       <c r="E96">
-        <v>188.6400000000003</v>
+        <v>214.5000000000005</v>
       </c>
       <c r="F96">
-        <v>2430.84</v>
+        <v>2456.7</v>
       </c>
       <c r="G96">
         <v>307.9</v>
@@ -9150,37 +9150,37 @@
         <v>242.8</v>
       </c>
       <c r="M96">
-        <v>593.3050976333766</v>
+        <v>599.6168539911785</v>
       </c>
       <c r="N96">
-        <v>-350.5050976333766</v>
+        <v>-356.8168539911784</v>
       </c>
       <c r="O96">
-        <v>-86.8384077001454</v>
+        <v>-88.40215919934924</v>
       </c>
       <c r="P96">
-        <v>-263.6666899332312</v>
+        <v>-268.4146947918292</v>
       </c>
       <c r="Q96">
-        <v>-118.4666899332312</v>
+        <v>-123.2146947918292</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6600089262051059</v>
+        <v>0.7828507114461274</v>
       </c>
       <c r="T96">
-        <v>11.27925254333001</v>
+        <v>13.53510305199602</v>
       </c>
       <c r="U96">
         <v>0.244074105096747</v>
       </c>
       <c r="V96">
-        <v>0.1013883640389482</v>
+        <v>0.1003211181016961</v>
       </c>
       <c r="W96">
-        <v>0.2193278308767175</v>
+        <v>0.2195883179737705</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4092329578297916</v>
+        <v>0.4049252424842149</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9196,22 +9196,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2477514376473883</v>
+        <v>0.2497341786983557</v>
       </c>
       <c r="C97">
-        <v>-1512.904856138951</v>
+        <v>-1544.947318607438</v>
       </c>
       <c r="D97">
-        <v>635.8951438610488</v>
+        <v>629.7126813925624</v>
       </c>
       <c r="E97">
-        <v>214.5000000000005</v>
+        <v>240.3600000000006</v>
       </c>
       <c r="F97">
-        <v>2456.7</v>
+        <v>2482.56</v>
       </c>
       <c r="G97">
         <v>307.9</v>
@@ -9232,37 +9232,37 @@
         <v>242.8</v>
       </c>
       <c r="M97">
-        <v>599.6168539911785</v>
+        <v>605.9286103489803</v>
       </c>
       <c r="N97">
-        <v>-356.8168539911784</v>
+        <v>-363.1286103489803</v>
       </c>
       <c r="O97">
-        <v>-88.40215919934924</v>
+        <v>-89.96591069855309</v>
       </c>
       <c r="P97">
-        <v>-268.4146947918292</v>
+        <v>-273.1626996504272</v>
       </c>
       <c r="Q97">
-        <v>-123.2146947918292</v>
+        <v>-127.9626996504272</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7828507114461274</v>
+        <v>0.9671133893076596</v>
       </c>
       <c r="T97">
-        <v>13.53510305199602</v>
+        <v>16.91887881499503</v>
       </c>
       <c r="U97">
         <v>0.244074105096747</v>
       </c>
       <c r="V97">
-        <v>0.1003211181016961</v>
+        <v>0.09927610645480342</v>
       </c>
       <c r="W97">
-        <v>0.2195883179737705</v>
+        <v>0.2198433782563015</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4049252424842149</v>
+        <v>0.4007072712083376</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9278,22 +9278,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2497341786983557</v>
+        <v>0.2517169197493232</v>
       </c>
       <c r="C98">
-        <v>-1544.947318607437</v>
+        <v>-1576.87072119345</v>
       </c>
       <c r="D98">
-        <v>629.7126813925624</v>
+        <v>623.6492788065498</v>
       </c>
       <c r="E98">
-        <v>240.3600000000001</v>
+        <v>266.2200000000003</v>
       </c>
       <c r="F98">
-        <v>2482.56</v>
+        <v>2508.42</v>
       </c>
       <c r="G98">
         <v>307.9</v>
@@ -9314,37 +9314,37 @@
         <v>242.8</v>
       </c>
       <c r="M98">
-        <v>605.9286103489802</v>
+        <v>612.2403667067822</v>
       </c>
       <c r="N98">
-        <v>-363.1286103489802</v>
+        <v>-369.4403667067822</v>
       </c>
       <c r="O98">
-        <v>-89.96591069855306</v>
+        <v>-91.52966219775693</v>
       </c>
       <c r="P98">
-        <v>-273.1626996504272</v>
+        <v>-277.9107045090253</v>
       </c>
       <c r="Q98">
-        <v>-127.9626996504272</v>
+        <v>-132.7107045090253</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9671133893076572</v>
+        <v>1.27421785241021</v>
       </c>
       <c r="T98">
-        <v>16.91887881499499</v>
+        <v>22.55850508665998</v>
       </c>
       <c r="U98">
         <v>0.244074105096747</v>
       </c>
       <c r="V98">
-        <v>0.09927610645480342</v>
+        <v>0.09825264143980544</v>
       </c>
       <c r="W98">
-        <v>0.2198433782563015</v>
+        <v>0.2200931795639349</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4007072712083377</v>
+        <v>0.3965762684123754</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9360,22 +9360,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2517169197493232</v>
+        <v>0.2536996608002907</v>
       </c>
       <c r="C99">
-        <v>-1576.87072119345</v>
+        <v>-1608.678470322699</v>
       </c>
       <c r="D99">
-        <v>623.6492788065498</v>
+        <v>617.7015296773011</v>
       </c>
       <c r="E99">
-        <v>266.2200000000003</v>
+        <v>292.0799999999999</v>
       </c>
       <c r="F99">
-        <v>2508.42</v>
+        <v>2534.28</v>
       </c>
       <c r="G99">
         <v>307.9</v>
@@ -9396,37 +9396,37 @@
         <v>242.8</v>
       </c>
       <c r="M99">
-        <v>612.2403667067822</v>
+        <v>618.552123064584</v>
       </c>
       <c r="N99">
-        <v>-369.4403667067822</v>
+        <v>-375.7521230645839</v>
       </c>
       <c r="O99">
-        <v>-91.52966219775693</v>
+        <v>-93.09341369696075</v>
       </c>
       <c r="P99">
-        <v>-277.9107045090253</v>
+        <v>-282.6587093676232</v>
       </c>
       <c r="Q99">
-        <v>-132.7107045090253</v>
+        <v>-137.4587093676232</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.27421785241021</v>
+        <v>1.888426778615315</v>
       </c>
       <c r="T99">
-        <v>22.55850508665998</v>
+        <v>33.83775762998998</v>
       </c>
       <c r="U99">
         <v>0.244074105096747</v>
       </c>
       <c r="V99">
-        <v>0.09825264143980544</v>
+        <v>0.09725006346592989</v>
       </c>
       <c r="W99">
-        <v>0.2200931795639349</v>
+        <v>0.2203378828856983</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3965762684123754</v>
+        <v>0.3925295717959227</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9442,22 +9442,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2536996608002907</v>
+        <v>0.2556824018512581</v>
       </c>
       <c r="C100">
-        <v>-1608.678470322699</v>
+        <v>-1640.373843700046</v>
       </c>
       <c r="D100">
-        <v>617.7015296773011</v>
+        <v>611.8661562999537</v>
       </c>
       <c r="E100">
-        <v>292.0799999999999</v>
+        <v>317.9400000000001</v>
       </c>
       <c r="F100">
-        <v>2534.28</v>
+        <v>2560.14</v>
       </c>
       <c r="G100">
         <v>307.9</v>
@@ -9478,37 +9478,37 @@
         <v>242.8</v>
       </c>
       <c r="M100">
-        <v>618.552123064584</v>
+        <v>624.8638794223858</v>
       </c>
       <c r="N100">
-        <v>-375.7521230645839</v>
+        <v>-382.0638794223858</v>
       </c>
       <c r="O100">
-        <v>-93.09341369696075</v>
+        <v>-94.6571651961646</v>
       </c>
       <c r="P100">
-        <v>-282.6587093676232</v>
+        <v>-287.4067142262212</v>
       </c>
       <c r="Q100">
-        <v>-137.4587093676232</v>
+        <v>-142.2067142262212</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.888426778615315</v>
+        <v>3.731053557230629</v>
       </c>
       <c r="T100">
-        <v>33.83775762998998</v>
+        <v>67.67551525997996</v>
       </c>
       <c r="U100">
         <v>0.244074105096747</v>
       </c>
       <c r="V100">
-        <v>0.09725006346592989</v>
+        <v>0.09626773959253666</v>
       </c>
       <c r="W100">
-        <v>0.2203378828856983</v>
+        <v>0.220577642706012</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9516,91 +9516,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3925295717959227</v>
+        <v>0.3885646266262669</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2556824018512581</v>
-      </c>
-      <c r="C101">
-        <v>-1640.373843700046</v>
-      </c>
-      <c r="D101">
-        <v>611.8661562999537</v>
-      </c>
-      <c r="E101">
-        <v>317.9400000000001</v>
-      </c>
-      <c r="F101">
-        <v>2560.14</v>
-      </c>
-      <c r="G101">
-        <v>307.9</v>
-      </c>
-      <c r="H101">
-        <v>343.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>388</v>
-      </c>
-      <c r="K101">
-        <v>145.2</v>
-      </c>
-      <c r="L101">
-        <v>242.8</v>
-      </c>
-      <c r="M101">
-        <v>624.8638794223858</v>
-      </c>
-      <c r="N101">
-        <v>-382.0638794223858</v>
-      </c>
-      <c r="O101">
-        <v>-94.6571651961646</v>
-      </c>
-      <c r="P101">
-        <v>-287.4067142262212</v>
-      </c>
-      <c r="Q101">
-        <v>-142.2067142262212</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.731053557230629</v>
-      </c>
-      <c r="T101">
-        <v>67.67551525997996</v>
-      </c>
-      <c r="U101">
-        <v>0.244074105096747</v>
-      </c>
-      <c r="V101">
-        <v>0.09626773959253666</v>
-      </c>
-      <c r="W101">
-        <v>0.220577642706012</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3885646266262669</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
